--- a/results/02_taxa_assemblage/Wards_LDA/classifier_prediction/artifacts/02_predicted_data.xlsx
+++ b/results/02_taxa_assemblage/Wards_LDA/classifier_prediction/artifacts/02_predicted_data.xlsx
@@ -528,13 +528,13 @@
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>0.5073685238818063</v>
+        <v>0.5226359306546439</v>
       </c>
       <c r="E5" t="n">
-        <v>0.2997829812845733</v>
+        <v>0.2291364728044516</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1928484948336203</v>
+        <v>0.2482275965409045</v>
       </c>
     </row>
     <row r="6">
@@ -566,13 +566,13 @@
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0102933807089218</v>
+        <v>0.01489446812401716</v>
       </c>
       <c r="E7" t="n">
-        <v>0.77062701696433</v>
+        <v>0.807751158072272</v>
       </c>
       <c r="F7" t="n">
-        <v>0.2190796023267482</v>
+        <v>0.1773543738037108</v>
       </c>
     </row>
     <row r="8">
@@ -588,13 +588,13 @@
         <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>0.2775701360630699</v>
+        <v>0.2111124066140017</v>
       </c>
       <c r="E8" t="n">
-        <v>0.2560692412532764</v>
+        <v>0.3000021257156584</v>
       </c>
       <c r="F8" t="n">
-        <v>0.4663606226836537</v>
+        <v>0.48888546767034</v>
       </c>
     </row>
     <row r="9">
@@ -604,19 +604,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C9" t="n">
         <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>0.247242435443253</v>
+        <v>0.5059118442986229</v>
       </c>
       <c r="E9" t="n">
-        <v>0.4324268767196354</v>
+        <v>0.1524629023762065</v>
       </c>
       <c r="F9" t="n">
-        <v>0.3203306878371116</v>
+        <v>0.3416252533251706</v>
       </c>
     </row>
     <row r="10">
@@ -632,13 +632,13 @@
         <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>0.08745155349563659</v>
+        <v>0.1249447267327093</v>
       </c>
       <c r="E10" t="n">
-        <v>0.5934981534145384</v>
+        <v>0.5404418832510692</v>
       </c>
       <c r="F10" t="n">
-        <v>0.319050293089825</v>
+        <v>0.3346133900162214</v>
       </c>
     </row>
     <row r="11">
@@ -686,13 +686,13 @@
         <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>0.02449948026171636</v>
+        <v>0.0827645530778482</v>
       </c>
       <c r="E13" t="n">
-        <v>0.4462068566620115</v>
+        <v>0.3248219099972258</v>
       </c>
       <c r="F13" t="n">
-        <v>0.5292936630762721</v>
+        <v>0.592413536924926</v>
       </c>
     </row>
     <row r="14">
@@ -708,13 +708,13 @@
         <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>0.006539953960818361</v>
+        <v>0.02021428015156124</v>
       </c>
       <c r="E14" t="n">
-        <v>0.5378031033091036</v>
+        <v>0.5132173807569668</v>
       </c>
       <c r="F14" t="n">
-        <v>0.455656942730078</v>
+        <v>0.466568339091472</v>
       </c>
     </row>
     <row r="15">
@@ -730,13 +730,13 @@
         <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>0.7188506781155711</v>
+        <v>0.7326345398313907</v>
       </c>
       <c r="E15" t="n">
-        <v>0.076555352294773</v>
+        <v>0.03909903428440185</v>
       </c>
       <c r="F15" t="n">
-        <v>0.2045939695896559</v>
+        <v>0.2282664258842075</v>
       </c>
     </row>
     <row r="16">
@@ -752,13 +752,13 @@
         <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>0.419909698534198</v>
+        <v>0.5063247691605232</v>
       </c>
       <c r="E16" t="n">
-        <v>0.2467889079684346</v>
+        <v>0.132191629908915</v>
       </c>
       <c r="F16" t="n">
-        <v>0.3333013934973675</v>
+        <v>0.3614836009305619</v>
       </c>
     </row>
     <row r="17">
@@ -771,11 +771,17 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>1</v>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0.005104641533208437</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.8440637273157225</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.150831631151069</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
@@ -790,13 +796,13 @@
         <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>0.03213824507397448</v>
+        <v>0.06501900502098358</v>
       </c>
       <c r="E18" t="n">
-        <v>0.4590137085357885</v>
+        <v>0.421434070455503</v>
       </c>
       <c r="F18" t="n">
-        <v>0.5088480463902371</v>
+        <v>0.5135469245235135</v>
       </c>
     </row>
     <row r="19">
@@ -822,14 +828,20 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C20" t="n">
-        <v>1</v>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0.02271201776655765</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.6226961647750711</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.3545918174583714</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
@@ -844,13 +856,13 @@
         <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>0.9898548110345695</v>
+        <v>0.9770271432156691</v>
       </c>
       <c r="E21" t="n">
-        <v>0.003692842349694251</v>
+        <v>0.003278422550466856</v>
       </c>
       <c r="F21" t="n">
-        <v>0.00645234661573625</v>
+        <v>0.01969443423386409</v>
       </c>
     </row>
     <row r="22">
@@ -866,13 +878,13 @@
         <v>0</v>
       </c>
       <c r="D22" t="n">
-        <v>0.9279973596270267</v>
+        <v>0.839918057419032</v>
       </c>
       <c r="E22" t="n">
-        <v>0.01819037974617862</v>
+        <v>0.03375867393986022</v>
       </c>
       <c r="F22" t="n">
-        <v>0.05381226062679466</v>
+        <v>0.1263232686411078</v>
       </c>
     </row>
     <row r="23">
@@ -888,13 +900,13 @@
         <v>0</v>
       </c>
       <c r="D23" t="n">
-        <v>0.002193452552434163</v>
+        <v>0.00180886925189019</v>
       </c>
       <c r="E23" t="n">
-        <v>0.7436781621974885</v>
+        <v>0.8860539714385011</v>
       </c>
       <c r="F23" t="n">
-        <v>0.2541283852500773</v>
+        <v>0.1121371593096087</v>
       </c>
     </row>
     <row r="24">
@@ -910,13 +922,13 @@
         <v>0</v>
       </c>
       <c r="D24" t="n">
-        <v>0.2087991694507481</v>
+        <v>0.2494046438815222</v>
       </c>
       <c r="E24" t="n">
-        <v>0.2259744854215399</v>
+        <v>0.1372357056035454</v>
       </c>
       <c r="F24" t="n">
-        <v>0.5652263451277121</v>
+        <v>0.6133596505149324</v>
       </c>
     </row>
     <row r="25">
@@ -926,14 +938,20 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C25" t="n">
-        <v>1</v>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr"/>
-      <c r="F25" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="D25" t="n">
+        <v>0.0002023030387739087</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.9160878484073041</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0.08370984855392208</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
@@ -964,13 +982,13 @@
         <v>0</v>
       </c>
       <c r="D27" t="n">
-        <v>0.9442582790607047</v>
+        <v>0.8203715372380513</v>
       </c>
       <c r="E27" t="n">
-        <v>0.01398324185815189</v>
+        <v>0.05724280986039346</v>
       </c>
       <c r="F27" t="n">
-        <v>0.04175847908114332</v>
+        <v>0.1223856529015552</v>
       </c>
     </row>
     <row r="28">
@@ -986,13 +1004,13 @@
         <v>0</v>
       </c>
       <c r="D28" t="n">
-        <v>0.9443397967320976</v>
+        <v>0.9158763859346821</v>
       </c>
       <c r="E28" t="n">
-        <v>0.0194074805426379</v>
+        <v>0.01632040409598928</v>
       </c>
       <c r="F28" t="n">
-        <v>0.03625272272526445</v>
+        <v>0.06780320996932852</v>
       </c>
     </row>
     <row r="29">
@@ -1024,13 +1042,13 @@
         <v>0</v>
       </c>
       <c r="D30" t="n">
-        <v>0.9504508443706841</v>
+        <v>0.8985309978098602</v>
       </c>
       <c r="E30" t="n">
-        <v>0.02953645794353877</v>
+        <v>0.02665473089908258</v>
       </c>
       <c r="F30" t="n">
-        <v>0.0200126976857771</v>
+        <v>0.07481427129105707</v>
       </c>
     </row>
     <row r="31">
@@ -1056,19 +1074,19 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C32" t="n">
         <v>0</v>
       </c>
       <c r="D32" t="n">
-        <v>0.004734150351743777</v>
+        <v>0.01007278726379384</v>
       </c>
       <c r="E32" t="n">
-        <v>0.850911129224742</v>
+        <v>0.428368076402425</v>
       </c>
       <c r="F32" t="n">
-        <v>0.1443547204235143</v>
+        <v>0.5615591363337812</v>
       </c>
     </row>
     <row r="33">
@@ -1116,13 +1134,13 @@
         <v>0</v>
       </c>
       <c r="D35" t="n">
-        <v>0.9805465137411071</v>
+        <v>0.9537058750726779</v>
       </c>
       <c r="E35" t="n">
-        <v>0.002781182735034983</v>
+        <v>0.002356190242546467</v>
       </c>
       <c r="F35" t="n">
-        <v>0.01667230352385769</v>
+        <v>0.04393793468477569</v>
       </c>
     </row>
     <row r="36">
@@ -1138,13 +1156,13 @@
         <v>0</v>
       </c>
       <c r="D36" t="n">
-        <v>1.745817472975902e-05</v>
+        <v>2.142789665453652e-05</v>
       </c>
       <c r="E36" t="n">
-        <v>0.7579384365093567</v>
+        <v>0.8287253505211895</v>
       </c>
       <c r="F36" t="n">
-        <v>0.2420441053159137</v>
+        <v>0.1712532215821559</v>
       </c>
     </row>
     <row r="37">
@@ -1176,13 +1194,13 @@
         <v>0</v>
       </c>
       <c r="D38" t="n">
-        <v>0.005501618118523257</v>
+        <v>0.005477664647062149</v>
       </c>
       <c r="E38" t="n">
-        <v>0.7061001263487523</v>
+        <v>0.8298238588686576</v>
       </c>
       <c r="F38" t="n">
-        <v>0.2883982555327245</v>
+        <v>0.1646984764842803</v>
       </c>
     </row>
     <row r="39">
@@ -1198,13 +1216,13 @@
         <v>0</v>
       </c>
       <c r="D39" t="n">
-        <v>0.000549855876237044</v>
+        <v>0.0005806711841481914</v>
       </c>
       <c r="E39" t="n">
-        <v>0.7049728930121296</v>
+        <v>0.8505282872214055</v>
       </c>
       <c r="F39" t="n">
-        <v>0.2944772511116334</v>
+        <v>0.1488910415944464</v>
       </c>
     </row>
     <row r="40">
@@ -1220,13 +1238,13 @@
         <v>0</v>
       </c>
       <c r="D40" t="n">
-        <v>0.9270301487269978</v>
+        <v>0.7945098509383258</v>
       </c>
       <c r="E40" t="n">
-        <v>0.03774752702564872</v>
+        <v>0.09979410300063118</v>
       </c>
       <c r="F40" t="n">
-        <v>0.03522232424735336</v>
+        <v>0.105696046061043</v>
       </c>
     </row>
     <row r="41">
@@ -1242,13 +1260,13 @@
         <v>0</v>
       </c>
       <c r="D41" t="n">
-        <v>0.9797708677192216</v>
+        <v>0.9611066422232786</v>
       </c>
       <c r="E41" t="n">
-        <v>0.005238005514209557</v>
+        <v>0.005145844642839795</v>
       </c>
       <c r="F41" t="n">
-        <v>0.01499112676656879</v>
+        <v>0.03374751313388157</v>
       </c>
     </row>
     <row r="42">
@@ -1264,13 +1282,13 @@
         <v>0</v>
       </c>
       <c r="D42" t="n">
-        <v>0.9538620481715404</v>
+        <v>0.8766703868104359</v>
       </c>
       <c r="E42" t="n">
-        <v>0.01889194296261798</v>
+        <v>0.02658766038610999</v>
       </c>
       <c r="F42" t="n">
-        <v>0.02724600886584173</v>
+        <v>0.09674195280345425</v>
       </c>
     </row>
     <row r="43">
@@ -1280,19 +1298,19 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C43" t="n">
         <v>0</v>
       </c>
       <c r="D43" t="n">
-        <v>0.01588142567025003</v>
+        <v>0.02816565502994422</v>
       </c>
       <c r="E43" t="n">
-        <v>0.6766220228021547</v>
+        <v>0.459029209380788</v>
       </c>
       <c r="F43" t="n">
-        <v>0.3074965515275954</v>
+        <v>0.5128051355892678</v>
       </c>
     </row>
     <row r="44">
@@ -1308,13 +1326,13 @@
         <v>0</v>
       </c>
       <c r="D44" t="n">
-        <v>0.06203008442925949</v>
+        <v>0.02044684171431072</v>
       </c>
       <c r="E44" t="n">
-        <v>0.5772020329530028</v>
+        <v>0.7983207340606485</v>
       </c>
       <c r="F44" t="n">
-        <v>0.3607678826177377</v>
+        <v>0.1812324242250408</v>
       </c>
     </row>
     <row r="45">
@@ -1330,13 +1348,13 @@
         <v>0</v>
       </c>
       <c r="D45" t="n">
-        <v>0.9887367282203344</v>
+        <v>0.9817363061662057</v>
       </c>
       <c r="E45" t="n">
-        <v>0.004634297578368161</v>
+        <v>0.002490860399666152</v>
       </c>
       <c r="F45" t="n">
-        <v>0.006628974201297422</v>
+        <v>0.01577283343412834</v>
       </c>
     </row>
     <row r="46">
@@ -1349,11 +1367,17 @@
         <v>1</v>
       </c>
       <c r="C46" t="n">
-        <v>1</v>
-      </c>
-      <c r="D46" t="inlineStr"/>
-      <c r="E46" t="inlineStr"/>
-      <c r="F46" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="D46" t="n">
+        <v>0.896243561138075</v>
+      </c>
+      <c r="E46" t="n">
+        <v>0.02620781381622551</v>
+      </c>
+      <c r="F46" t="n">
+        <v>0.07754862504569944</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
@@ -1384,13 +1408,13 @@
         <v>0</v>
       </c>
       <c r="D48" t="n">
-        <v>0.0009513772648169174</v>
+        <v>0.0007210691321569237</v>
       </c>
       <c r="E48" t="n">
-        <v>0.6248867992099142</v>
+        <v>0.8655117886699846</v>
       </c>
       <c r="F48" t="n">
-        <v>0.3741618235252689</v>
+        <v>0.1337671421978586</v>
       </c>
     </row>
     <row r="49">
@@ -1470,13 +1494,13 @@
         <v>0</v>
       </c>
       <c r="D53" t="n">
-        <v>0.0004201559009436775</v>
+        <v>0.0007235402654585954</v>
       </c>
       <c r="E53" t="n">
-        <v>0.6419065488856434</v>
+        <v>0.7727405686472834</v>
       </c>
       <c r="F53" t="n">
-        <v>0.3576732952134131</v>
+        <v>0.2265358910872581</v>
       </c>
     </row>
     <row r="54">
@@ -1502,19 +1526,19 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C55" t="n">
         <v>0</v>
       </c>
       <c r="D55" t="n">
-        <v>0.0009728467123534318</v>
+        <v>0.004053038309609303</v>
       </c>
       <c r="E55" t="n">
-        <v>0.5006490729223475</v>
+        <v>0.4564669378998824</v>
       </c>
       <c r="F55" t="n">
-        <v>0.4983780803652991</v>
+        <v>0.5394800237905083</v>
       </c>
     </row>
     <row r="56">
@@ -1530,13 +1554,13 @@
         <v>0</v>
       </c>
       <c r="D56" t="n">
-        <v>0.0003142587270437907</v>
+        <v>0.0006180764159351133</v>
       </c>
       <c r="E56" t="n">
-        <v>0.6342235666103402</v>
+        <v>0.7633332640439305</v>
       </c>
       <c r="F56" t="n">
-        <v>0.365462174662616</v>
+        <v>0.2360486595401343</v>
       </c>
     </row>
     <row r="57">
@@ -1568,13 +1592,13 @@
         <v>0</v>
       </c>
       <c r="D58" t="n">
-        <v>0.01738095900947974</v>
+        <v>0.07050149504096148</v>
       </c>
       <c r="E58" t="n">
-        <v>0.4806969537443958</v>
+        <v>0.304347398431815</v>
       </c>
       <c r="F58" t="n">
-        <v>0.5019220872461245</v>
+        <v>0.6251511065272235</v>
       </c>
     </row>
     <row r="59">
@@ -1600,19 +1624,19 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C60" t="n">
         <v>0</v>
       </c>
       <c r="D60" t="n">
-        <v>0.001909869157090863</v>
+        <v>0.00819532238724963</v>
       </c>
       <c r="E60" t="n">
-        <v>0.5494674416041253</v>
+        <v>0.4098525099015186</v>
       </c>
       <c r="F60" t="n">
-        <v>0.4486226892387838</v>
+        <v>0.5819521677112318</v>
       </c>
     </row>
     <row r="61">
@@ -1628,13 +1652,13 @@
         <v>0</v>
       </c>
       <c r="D61" t="n">
-        <v>0.2358509850973537</v>
+        <v>0.3328784315304523</v>
       </c>
       <c r="E61" t="n">
-        <v>0.3110431952337548</v>
+        <v>0.1688011806896332</v>
       </c>
       <c r="F61" t="n">
-        <v>0.4531058196688916</v>
+        <v>0.4983203877799144</v>
       </c>
     </row>
     <row r="62">
@@ -1650,13 +1674,13 @@
         <v>0</v>
       </c>
       <c r="D62" t="n">
-        <v>0.002639611300331367</v>
+        <v>0.009718299724848197</v>
       </c>
       <c r="E62" t="n">
-        <v>0.4630335857662598</v>
+        <v>0.3129103881415125</v>
       </c>
       <c r="F62" t="n">
-        <v>0.5343268029334088</v>
+        <v>0.6773713121336393</v>
       </c>
     </row>
     <row r="63">
@@ -1682,14 +1706,20 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C64" t="n">
-        <v>1</v>
-      </c>
-      <c r="D64" t="inlineStr"/>
-      <c r="E64" t="inlineStr"/>
-      <c r="F64" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="D64" t="n">
+        <v>0.05462561552569862</v>
+      </c>
+      <c r="E64" t="n">
+        <v>0.3418612991495027</v>
+      </c>
+      <c r="F64" t="n">
+        <v>0.6035130853247987</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
@@ -1704,13 +1734,13 @@
         <v>0</v>
       </c>
       <c r="D65" t="n">
-        <v>2.845592036950367e-05</v>
+        <v>3.083778982781321e-05</v>
       </c>
       <c r="E65" t="n">
-        <v>0.7637522294491441</v>
+        <v>0.9115570945033933</v>
       </c>
       <c r="F65" t="n">
-        <v>0.2362193146304865</v>
+        <v>0.08841206770677883</v>
       </c>
     </row>
     <row r="66">
@@ -1726,13 +1756,13 @@
         <v>0</v>
       </c>
       <c r="D66" t="n">
-        <v>0.0001108966328405456</v>
+        <v>5.485985531454837e-05</v>
       </c>
       <c r="E66" t="n">
-        <v>0.8200417857440896</v>
+        <v>0.9596386265763165</v>
       </c>
       <c r="F66" t="n">
-        <v>0.1798473176230699</v>
+        <v>0.04030651356836887</v>
       </c>
     </row>
     <row r="67">
@@ -1748,13 +1778,13 @@
         <v>0</v>
       </c>
       <c r="D67" t="n">
-        <v>0.01406583045211261</v>
+        <v>0.05105410043668133</v>
       </c>
       <c r="E67" t="n">
-        <v>0.4478631659842503</v>
+        <v>0.2591283411888629</v>
       </c>
       <c r="F67" t="n">
-        <v>0.5380710035636371</v>
+        <v>0.6898175583744557</v>
       </c>
     </row>
     <row r="68">
@@ -1770,13 +1800,13 @@
         <v>0</v>
       </c>
       <c r="D68" t="n">
-        <v>0.0002999775445393279</v>
+        <v>0.0001752578040481906</v>
       </c>
       <c r="E68" t="n">
-        <v>0.7382103083205234</v>
+        <v>0.9141094283081692</v>
       </c>
       <c r="F68" t="n">
-        <v>0.2614897141349374</v>
+        <v>0.08571531388778268</v>
       </c>
     </row>
     <row r="69">
@@ -1792,13 +1822,13 @@
         <v>0</v>
       </c>
       <c r="D69" t="n">
-        <v>0.9170218028764717</v>
+        <v>0.864503225955499</v>
       </c>
       <c r="E69" t="n">
-        <v>0.041833361656018</v>
+        <v>0.04347786841769356</v>
       </c>
       <c r="F69" t="n">
-        <v>0.04114483546751018</v>
+        <v>0.09201890562680728</v>
       </c>
     </row>
     <row r="70">
@@ -1814,13 +1844,13 @@
         <v>0</v>
       </c>
       <c r="D70" t="n">
-        <v>0.0007105793455738375</v>
+        <v>0.0005290790476988852</v>
       </c>
       <c r="E70" t="n">
-        <v>0.7647856734941266</v>
+        <v>0.9039921795838798</v>
       </c>
       <c r="F70" t="n">
-        <v>0.2345037471602996</v>
+        <v>0.09547874136842131</v>
       </c>
     </row>
     <row r="71">
@@ -1836,13 +1866,13 @@
         <v>0</v>
       </c>
       <c r="D71" t="n">
-        <v>0.004045722889411826</v>
+        <v>0.003125046753655084</v>
       </c>
       <c r="E71" t="n">
-        <v>0.7168879128187928</v>
+        <v>0.8565540705588657</v>
       </c>
       <c r="F71" t="n">
-        <v>0.2790663642917953</v>
+        <v>0.1403208826874792</v>
       </c>
     </row>
     <row r="72">
@@ -1858,13 +1888,13 @@
         <v>0</v>
       </c>
       <c r="D72" t="n">
-        <v>0.004523582346655121</v>
+        <v>0.003713560465625775</v>
       </c>
       <c r="E72" t="n">
-        <v>0.7160421333928669</v>
+        <v>0.8476333938088463</v>
       </c>
       <c r="F72" t="n">
-        <v>0.2794342842604779</v>
+        <v>0.1486530457255278</v>
       </c>
     </row>
     <row r="73">
@@ -1880,13 +1910,13 @@
         <v>0</v>
       </c>
       <c r="D73" t="n">
-        <v>0.9477270237998447</v>
+        <v>0.9373667605099781</v>
       </c>
       <c r="E73" t="n">
-        <v>0.008764608535337825</v>
+        <v>0.001660263575088163</v>
       </c>
       <c r="F73" t="n">
-        <v>0.0435083676648173</v>
+        <v>0.06097297591493354</v>
       </c>
     </row>
     <row r="74">
@@ -1902,13 +1932,13 @@
         <v>0</v>
       </c>
       <c r="D74" t="n">
-        <v>0.0002383670690347012</v>
+        <v>0.0001937317755229256</v>
       </c>
       <c r="E74" t="n">
-        <v>0.7879090479667746</v>
+        <v>0.9132952285982988</v>
       </c>
       <c r="F74" t="n">
-        <v>0.2118525849641907</v>
+        <v>0.0865110396261783</v>
       </c>
     </row>
     <row r="75">
@@ -1924,13 +1954,13 @@
         <v>0</v>
       </c>
       <c r="D75" t="n">
-        <v>0.998780439727892</v>
+        <v>0.9979422524357064</v>
       </c>
       <c r="E75" t="n">
-        <v>0.0001947918252710585</v>
+        <v>2.953299747249403e-05</v>
       </c>
       <c r="F75" t="n">
-        <v>0.001024768446837103</v>
+        <v>0.002028214566821061</v>
       </c>
     </row>
     <row r="76">
@@ -1946,13 +1976,13 @@
         <v>0</v>
       </c>
       <c r="D76" t="n">
-        <v>0.0002526203674968322</v>
+        <v>0.0006456952010762668</v>
       </c>
       <c r="E76" t="n">
-        <v>0.7468727358176048</v>
+        <v>0.7505381108874264</v>
       </c>
       <c r="F76" t="n">
-        <v>0.2528746438148983</v>
+        <v>0.2488161939114974</v>
       </c>
     </row>
     <row r="77">
@@ -1968,13 +1998,13 @@
         <v>0</v>
       </c>
       <c r="D77" t="n">
-        <v>0.004286539399092327</v>
+        <v>0.004426741616751683</v>
       </c>
       <c r="E77" t="n">
-        <v>0.7012853313521551</v>
+        <v>0.8193104789957325</v>
       </c>
       <c r="F77" t="n">
-        <v>0.2944281292487525</v>
+        <v>0.1762627793875157</v>
       </c>
     </row>
     <row r="78">
@@ -1990,13 +2020,13 @@
         <v>0</v>
       </c>
       <c r="D78" t="n">
-        <v>0.567455133743394</v>
+        <v>0.7772444951454648</v>
       </c>
       <c r="E78" t="n">
-        <v>0.1097803661719901</v>
+        <v>0.01139369204458552</v>
       </c>
       <c r="F78" t="n">
-        <v>0.3227645000846158</v>
+        <v>0.2113618128099498</v>
       </c>
     </row>
     <row r="79">
@@ -2028,13 +2058,13 @@
         <v>0</v>
       </c>
       <c r="D80" t="n">
-        <v>0.003557658081305094</v>
+        <v>0.003517930746702923</v>
       </c>
       <c r="E80" t="n">
-        <v>0.7128055363170829</v>
+        <v>0.8522036843746639</v>
       </c>
       <c r="F80" t="n">
-        <v>0.283636805601612</v>
+        <v>0.1442783848786331</v>
       </c>
     </row>
     <row r="81">
@@ -2050,13 +2080,13 @@
         <v>0</v>
       </c>
       <c r="D81" t="n">
-        <v>0.001239755365556141</v>
+        <v>0.0009337733786778985</v>
       </c>
       <c r="E81" t="n">
-        <v>0.7032300881294367</v>
+        <v>0.8766811712241706</v>
       </c>
       <c r="F81" t="n">
-        <v>0.2955301565050071</v>
+        <v>0.1223850553971517</v>
       </c>
     </row>
     <row r="82">
@@ -2104,13 +2134,13 @@
         <v>0</v>
       </c>
       <c r="D84" t="n">
-        <v>0.0009973612522007269</v>
+        <v>0.001472929436446006</v>
       </c>
       <c r="E84" t="n">
-        <v>0.7360606479788077</v>
+        <v>0.8152451008245123</v>
       </c>
       <c r="F84" t="n">
-        <v>0.2629419907689918</v>
+        <v>0.1832819697390417</v>
       </c>
     </row>
     <row r="85">
@@ -2126,13 +2156,13 @@
         <v>0</v>
       </c>
       <c r="D85" t="n">
-        <v>0.003675296585885394</v>
+        <v>0.003060821216489918</v>
       </c>
       <c r="E85" t="n">
-        <v>0.7156536696835483</v>
+        <v>0.853871540695966</v>
       </c>
       <c r="F85" t="n">
-        <v>0.2806710337305664</v>
+        <v>0.143067638087544</v>
       </c>
     </row>
     <row r="86">
@@ -2148,13 +2178,13 @@
         <v>0</v>
       </c>
       <c r="D86" t="n">
-        <v>0.0001965948184535149</v>
+        <v>0.000421307979369978</v>
       </c>
       <c r="E86" t="n">
-        <v>0.6866510864229529</v>
+        <v>0.7715673493321499</v>
       </c>
       <c r="F86" t="n">
-        <v>0.3131523187585934</v>
+        <v>0.2280113426884801</v>
       </c>
     </row>
     <row r="87">
@@ -2170,13 +2200,13 @@
         <v>0</v>
       </c>
       <c r="D87" t="n">
-        <v>0.02179289339336987</v>
+        <v>0.05515574370145446</v>
       </c>
       <c r="E87" t="n">
-        <v>0.7112973390563961</v>
+        <v>0.617987572448749</v>
       </c>
       <c r="F87" t="n">
-        <v>0.266909767550234</v>
+        <v>0.3268566838497964</v>
       </c>
     </row>
     <row r="88">
@@ -2192,13 +2222,13 @@
         <v>0</v>
       </c>
       <c r="D88" t="n">
-        <v>0.004675886236180335</v>
+        <v>0.004945117846483969</v>
       </c>
       <c r="E88" t="n">
-        <v>0.7206806871750954</v>
+        <v>0.8381302530711638</v>
       </c>
       <c r="F88" t="n">
-        <v>0.2746434265887243</v>
+        <v>0.1569246290823523</v>
       </c>
     </row>
     <row r="89">
@@ -2208,19 +2238,19 @@
         </is>
       </c>
       <c r="B89" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C89" t="n">
         <v>0</v>
       </c>
       <c r="D89" t="n">
-        <v>0.2048331728280169</v>
+        <v>0.2331855651124553</v>
       </c>
       <c r="E89" t="n">
-        <v>0.4256253463157023</v>
+        <v>0.3519909906348873</v>
       </c>
       <c r="F89" t="n">
-        <v>0.3695414808562809</v>
+        <v>0.4148234442526574</v>
       </c>
     </row>
     <row r="90">
@@ -2236,13 +2266,13 @@
         <v>0</v>
       </c>
       <c r="D90" t="n">
-        <v>0.0005413360750741331</v>
+        <v>0.0004750690565556648</v>
       </c>
       <c r="E90" t="n">
-        <v>0.6683472489108007</v>
+        <v>0.8557782652030248</v>
       </c>
       <c r="F90" t="n">
-        <v>0.3311114150141252</v>
+        <v>0.1437466657404196</v>
       </c>
     </row>
     <row r="91">
@@ -2252,19 +2282,19 @@
         </is>
       </c>
       <c r="B91" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C91" t="n">
         <v>0</v>
       </c>
       <c r="D91" t="n">
-        <v>0.009243603985753402</v>
+        <v>0.01349642535602927</v>
       </c>
       <c r="E91" t="n">
-        <v>0.4658662459019031</v>
+        <v>0.5981582549964327</v>
       </c>
       <c r="F91" t="n">
-        <v>0.5248901501123434</v>
+        <v>0.3883453196475382</v>
       </c>
     </row>
     <row r="92">
@@ -2280,13 +2310,13 @@
         <v>0</v>
       </c>
       <c r="D92" t="n">
-        <v>0.0005464189168275489</v>
+        <v>0.0006727949649865781</v>
       </c>
       <c r="E92" t="n">
-        <v>0.6339907136355575</v>
+        <v>0.8061233697291238</v>
       </c>
       <c r="F92" t="n">
-        <v>0.3654628674476149</v>
+        <v>0.1932038353058896</v>
       </c>
     </row>
     <row r="93">
@@ -2302,13 +2332,13 @@
         <v>0</v>
       </c>
       <c r="D93" t="n">
-        <v>0.0004673209117547102</v>
+        <v>0.00101403861383066</v>
       </c>
       <c r="E93" t="n">
-        <v>0.6214964629668025</v>
+        <v>0.6979009430942837</v>
       </c>
       <c r="F93" t="n">
-        <v>0.3780362161214428</v>
+        <v>0.3010850182918857</v>
       </c>
     </row>
     <row r="94">
@@ -2356,13 +2386,13 @@
         <v>0</v>
       </c>
       <c r="D96" t="n">
-        <v>0.04853566828612008</v>
+        <v>0.04413911539510598</v>
       </c>
       <c r="E96" t="n">
-        <v>0.6731738951228748</v>
+        <v>0.7120541700111769</v>
       </c>
       <c r="F96" t="n">
-        <v>0.2782904365910051</v>
+        <v>0.2438067145937171</v>
       </c>
     </row>
     <row r="97">
@@ -2375,11 +2405,17 @@
         <v>2</v>
       </c>
       <c r="C97" t="n">
-        <v>1</v>
-      </c>
-      <c r="D97" t="inlineStr"/>
-      <c r="E97" t="inlineStr"/>
-      <c r="F97" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="D97" t="n">
+        <v>0.037179693335226</v>
+      </c>
+      <c r="E97" t="n">
+        <v>0.678839677769554</v>
+      </c>
+      <c r="F97" t="n">
+        <v>0.28398062889522</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="1" t="inlineStr">
@@ -2394,13 +2430,13 @@
         <v>0</v>
       </c>
       <c r="D98" t="n">
-        <v>0.002704187902324861</v>
+        <v>0.007793192301721256</v>
       </c>
       <c r="E98" t="n">
-        <v>0.6046571235604988</v>
+        <v>0.6182927995401172</v>
       </c>
       <c r="F98" t="n">
-        <v>0.3926386885371762</v>
+        <v>0.3739140081581617</v>
       </c>
     </row>
     <row r="99">
@@ -2416,13 +2452,13 @@
         <v>0</v>
       </c>
       <c r="D99" t="n">
-        <v>0.01832429415435691</v>
+        <v>0.02514751171959442</v>
       </c>
       <c r="E99" t="n">
-        <v>0.738354903898774</v>
+        <v>0.7483022208776379</v>
       </c>
       <c r="F99" t="n">
-        <v>0.2433208019468691</v>
+        <v>0.2265502674027678</v>
       </c>
     </row>
     <row r="100">
@@ -2435,11 +2471,17 @@
         <v>2</v>
       </c>
       <c r="C100" t="n">
-        <v>1</v>
-      </c>
-      <c r="D100" t="inlineStr"/>
-      <c r="E100" t="inlineStr"/>
-      <c r="F100" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="D100" t="n">
+        <v>0.08544147363357721</v>
+      </c>
+      <c r="E100" t="n">
+        <v>0.5868283460139794</v>
+      </c>
+      <c r="F100" t="n">
+        <v>0.3277301803524433</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="1" t="inlineStr">
@@ -2454,13 +2496,13 @@
         <v>0</v>
       </c>
       <c r="D101" t="n">
-        <v>0.05893728144162884</v>
+        <v>0.07468099432222131</v>
       </c>
       <c r="E101" t="n">
-        <v>0.640675738457953</v>
+        <v>0.5565653316180164</v>
       </c>
       <c r="F101" t="n">
-        <v>0.3003869801004182</v>
+        <v>0.3687536740597622</v>
       </c>
     </row>
     <row r="102">
@@ -2476,13 +2518,13 @@
         <v>0</v>
       </c>
       <c r="D102" t="n">
-        <v>0.002413965491485799</v>
+        <v>0.001954041972127674</v>
       </c>
       <c r="E102" t="n">
-        <v>0.6694420261102795</v>
+        <v>0.8468037140799585</v>
       </c>
       <c r="F102" t="n">
-        <v>0.3281440083982347</v>
+        <v>0.151242243947914</v>
       </c>
     </row>
     <row r="103">
@@ -2530,13 +2572,13 @@
         <v>0</v>
       </c>
       <c r="D105" t="n">
-        <v>0.005466524672425883</v>
+        <v>0.004461907287384504</v>
       </c>
       <c r="E105" t="n">
-        <v>0.5914772205822405</v>
+        <v>0.7079364522288883</v>
       </c>
       <c r="F105" t="n">
-        <v>0.4030562547453335</v>
+        <v>0.2876016404837271</v>
       </c>
     </row>
     <row r="106">
@@ -2552,13 +2594,13 @@
         <v>0</v>
       </c>
       <c r="D106" t="n">
-        <v>0.01006158742579939</v>
+        <v>0.01119031268289366</v>
       </c>
       <c r="E106" t="n">
-        <v>0.5263522652940902</v>
+        <v>0.5998677708815472</v>
       </c>
       <c r="F106" t="n">
-        <v>0.4635861472801105</v>
+        <v>0.3889419164355592</v>
       </c>
     </row>
     <row r="107">
@@ -2584,19 +2626,19 @@
         </is>
       </c>
       <c r="B108" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C108" t="n">
         <v>0</v>
       </c>
       <c r="D108" t="n">
-        <v>0.009015517126771925</v>
+        <v>0.017109858366055</v>
       </c>
       <c r="E108" t="n">
-        <v>0.4904319619398506</v>
+        <v>0.5550572851856269</v>
       </c>
       <c r="F108" t="n">
-        <v>0.5005525209333774</v>
+        <v>0.4278328564483181</v>
       </c>
     </row>
     <row r="109">
@@ -2612,13 +2654,13 @@
         <v>0</v>
       </c>
       <c r="D109" t="n">
-        <v>0.008437646363168195</v>
+        <v>0.007329412109380988</v>
       </c>
       <c r="E109" t="n">
-        <v>0.6378904994712763</v>
+        <v>0.7723039889432153</v>
       </c>
       <c r="F109" t="n">
-        <v>0.3536718541655556</v>
+        <v>0.2203665989474038</v>
       </c>
     </row>
     <row r="110">
@@ -2634,13 +2676,13 @@
         <v>0</v>
       </c>
       <c r="D110" t="n">
-        <v>0.004673687122073637</v>
+        <v>0.01009970330900376</v>
       </c>
       <c r="E110" t="n">
-        <v>0.6338865442930793</v>
+        <v>0.6857423323208712</v>
       </c>
       <c r="F110" t="n">
-        <v>0.3614397685848469</v>
+        <v>0.304157964370125</v>
       </c>
     </row>
     <row r="111">
@@ -2650,19 +2692,19 @@
         </is>
       </c>
       <c r="B111" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C111" t="n">
         <v>0</v>
       </c>
       <c r="D111" t="n">
-        <v>0.08820914810636428</v>
+        <v>0.2009366662283203</v>
       </c>
       <c r="E111" t="n">
-        <v>0.5701389320106203</v>
+        <v>0.3685997683148823</v>
       </c>
       <c r="F111" t="n">
-        <v>0.3416519198830155</v>
+        <v>0.4304635654567974</v>
       </c>
     </row>
     <row r="112">
@@ -2672,19 +2714,19 @@
         </is>
       </c>
       <c r="B112" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C112" t="n">
         <v>0</v>
       </c>
       <c r="D112" t="n">
-        <v>0.004309373754093143</v>
+        <v>0.01232784534982507</v>
       </c>
       <c r="E112" t="n">
-        <v>0.5237579126383517</v>
+        <v>0.4859373573029658</v>
       </c>
       <c r="F112" t="n">
-        <v>0.4719327136075552</v>
+        <v>0.5017347973472092</v>
       </c>
     </row>
     <row r="113">
@@ -2700,13 +2742,13 @@
         <v>0</v>
       </c>
       <c r="D113" t="n">
-        <v>0.008747106001286226</v>
+        <v>0.02132888138551817</v>
       </c>
       <c r="E113" t="n">
-        <v>0.4671172388023658</v>
+        <v>0.4006855635816408</v>
       </c>
       <c r="F113" t="n">
-        <v>0.524135655196348</v>
+        <v>0.5779855550328411</v>
       </c>
     </row>
     <row r="114">
@@ -2722,13 +2764,13 @@
         <v>0</v>
       </c>
       <c r="D114" t="n">
-        <v>0.01761756222882795</v>
+        <v>0.03635960641284908</v>
       </c>
       <c r="E114" t="n">
-        <v>0.7466260223578436</v>
+        <v>0.7138793483344235</v>
       </c>
       <c r="F114" t="n">
-        <v>0.2357564154133286</v>
+        <v>0.2497610452527275</v>
       </c>
     </row>
     <row r="115">
@@ -2738,7 +2780,7 @@
         </is>
       </c>
       <c r="B115" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C115" t="n">
         <v>1</v>
@@ -2760,13 +2802,13 @@
         <v>0</v>
       </c>
       <c r="D116" t="n">
-        <v>0.01348960230463322</v>
+        <v>0.03426322300592603</v>
       </c>
       <c r="E116" t="n">
-        <v>0.7124221863713767</v>
+        <v>0.6582207055116334</v>
       </c>
       <c r="F116" t="n">
-        <v>0.2740882113239901</v>
+        <v>0.3075160714824406</v>
       </c>
     </row>
     <row r="117">
@@ -2782,13 +2824,13 @@
         <v>0</v>
       </c>
       <c r="D117" t="n">
-        <v>0.003167748574145796</v>
+        <v>0.009054925023791183</v>
       </c>
       <c r="E117" t="n">
-        <v>0.6316734786586193</v>
+        <v>0.6164126126747811</v>
       </c>
       <c r="F117" t="n">
-        <v>0.3651587727672349</v>
+        <v>0.3745324623014277</v>
       </c>
     </row>
     <row r="118">
@@ -2804,13 +2846,13 @@
         <v>0</v>
       </c>
       <c r="D118" t="n">
-        <v>0.02846231401597824</v>
+        <v>0.1386766637517812</v>
       </c>
       <c r="E118" t="n">
-        <v>0.4599911872381441</v>
+        <v>0.1822397012697827</v>
       </c>
       <c r="F118" t="n">
-        <v>0.5115464987458777</v>
+        <v>0.679083634978436</v>
       </c>
     </row>
     <row r="119">
@@ -2826,13 +2868,13 @@
         <v>0</v>
       </c>
       <c r="D119" t="n">
-        <v>0.0881974109613894</v>
+        <v>0.3534677607919418</v>
       </c>
       <c r="E119" t="n">
-        <v>0.2925310919048348</v>
+        <v>0.06880686480823173</v>
       </c>
       <c r="F119" t="n">
-        <v>0.6192714971337757</v>
+        <v>0.5777253743998265</v>
       </c>
     </row>
     <row r="120">
@@ -2848,13 +2890,13 @@
         <v>0</v>
       </c>
       <c r="D120" t="n">
-        <v>0.01160528692632908</v>
+        <v>0.0261835219605369</v>
       </c>
       <c r="E120" t="n">
-        <v>0.5367557813114037</v>
+        <v>0.5260433143925171</v>
       </c>
       <c r="F120" t="n">
-        <v>0.4516389317622673</v>
+        <v>0.447773163646946</v>
       </c>
     </row>
     <row r="121">
@@ -2886,13 +2928,13 @@
         <v>0</v>
       </c>
       <c r="D122" t="n">
-        <v>0.0304975567763599</v>
+        <v>0.05738052251069409</v>
       </c>
       <c r="E122" t="n">
-        <v>0.5195271598214906</v>
+        <v>0.5068665331696673</v>
       </c>
       <c r="F122" t="n">
-        <v>0.4499752834021495</v>
+        <v>0.4357529443196386</v>
       </c>
     </row>
     <row r="123">
@@ -2924,13 +2966,13 @@
         <v>0</v>
       </c>
       <c r="D124" t="n">
-        <v>0.003924715050677344</v>
+        <v>0.01046932634315787</v>
       </c>
       <c r="E124" t="n">
-        <v>0.6056068551821917</v>
+        <v>0.6118462954753516</v>
       </c>
       <c r="F124" t="n">
-        <v>0.3904684297671309</v>
+        <v>0.3776843781814906</v>
       </c>
     </row>
     <row r="125">
@@ -2946,13 +2988,13 @@
         <v>0</v>
       </c>
       <c r="D125" t="n">
-        <v>0.0257482614030386</v>
+        <v>0.04959069737542635</v>
       </c>
       <c r="E125" t="n">
-        <v>0.5593075778888955</v>
+        <v>0.5360215248114114</v>
       </c>
       <c r="F125" t="n">
-        <v>0.4149441607080658</v>
+        <v>0.4143877778131623</v>
       </c>
     </row>
     <row r="126">
@@ -2962,19 +3004,19 @@
         </is>
       </c>
       <c r="B126" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C126" t="n">
         <v>0</v>
       </c>
       <c r="D126" t="n">
-        <v>0.0409524886818893</v>
+        <v>0.07639526232872892</v>
       </c>
       <c r="E126" t="n">
-        <v>0.5054694335185098</v>
+        <v>0.4056270811631327</v>
       </c>
       <c r="F126" t="n">
-        <v>0.4535780777996009</v>
+        <v>0.5179776565081383</v>
       </c>
     </row>
     <row r="127">
@@ -2990,13 +3032,13 @@
         <v>0</v>
       </c>
       <c r="D127" t="n">
-        <v>0.02716002503975362</v>
+        <v>0.0704686726257223</v>
       </c>
       <c r="E127" t="n">
-        <v>0.642513383425075</v>
+        <v>0.4896830247834821</v>
       </c>
       <c r="F127" t="n">
-        <v>0.3303265915351713</v>
+        <v>0.4398483025907955</v>
       </c>
     </row>
     <row r="128">
@@ -3009,11 +3051,17 @@
         <v>2</v>
       </c>
       <c r="C128" t="n">
-        <v>1</v>
-      </c>
-      <c r="D128" t="inlineStr"/>
-      <c r="E128" t="inlineStr"/>
-      <c r="F128" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.007547569476446359</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.5636541213417336</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.4287983091818199</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129" s="1" t="inlineStr">
@@ -3028,13 +3076,13 @@
         <v>0</v>
       </c>
       <c r="D129" t="n">
-        <v>7.025410242814003e-06</v>
+        <v>2.656451561115725e-05</v>
       </c>
       <c r="E129" t="n">
-        <v>0.6868172751342662</v>
+        <v>0.7461466555043098</v>
       </c>
       <c r="F129" t="n">
-        <v>0.3131756994554911</v>
+        <v>0.2538267799800791</v>
       </c>
     </row>
     <row r="130">
@@ -3044,19 +3092,19 @@
         </is>
       </c>
       <c r="B130" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C130" t="n">
         <v>0</v>
       </c>
       <c r="D130" t="n">
-        <v>0.08603056431303674</v>
+        <v>0.1813217108826911</v>
       </c>
       <c r="E130" t="n">
-        <v>0.5516951252553054</v>
+        <v>0.3587377610328395</v>
       </c>
       <c r="F130" t="n">
-        <v>0.3622743104316579</v>
+        <v>0.4599405280844694</v>
       </c>
     </row>
     <row r="131">
@@ -3072,13 +3120,13 @@
         <v>0</v>
       </c>
       <c r="D131" t="n">
-        <v>0.002697086441900741</v>
+        <v>0.006630949336003108</v>
       </c>
       <c r="E131" t="n">
-        <v>0.5524316455879766</v>
+        <v>0.6295128969842961</v>
       </c>
       <c r="F131" t="n">
-        <v>0.4448712679701225</v>
+        <v>0.3638561536797008</v>
       </c>
     </row>
     <row r="132">
@@ -3110,13 +3158,13 @@
         <v>0</v>
       </c>
       <c r="D133" t="n">
-        <v>0.007409955910746046</v>
+        <v>0.01852633500098738</v>
       </c>
       <c r="E133" t="n">
-        <v>0.5542407506139426</v>
+        <v>0.5370097650144484</v>
       </c>
       <c r="F133" t="n">
-        <v>0.4383492934753112</v>
+        <v>0.4444638999845642</v>
       </c>
     </row>
     <row r="134">
@@ -3132,13 +3180,13 @@
         <v>0</v>
       </c>
       <c r="D134" t="n">
-        <v>0.01890335929480061</v>
+        <v>0.03813584636978355</v>
       </c>
       <c r="E134" t="n">
-        <v>0.466364788776469</v>
+        <v>0.4518692596576767</v>
       </c>
       <c r="F134" t="n">
-        <v>0.5147318519287304</v>
+        <v>0.5099948939725398</v>
       </c>
     </row>
     <row r="135">
@@ -3154,13 +3202,13 @@
         <v>0</v>
       </c>
       <c r="D135" t="n">
-        <v>0.006194035485159703</v>
+        <v>0.01638538164065265</v>
       </c>
       <c r="E135" t="n">
-        <v>0.646842735494808</v>
+        <v>0.6220030667384908</v>
       </c>
       <c r="F135" t="n">
-        <v>0.3469632290200322</v>
+        <v>0.3616115516208565</v>
       </c>
     </row>
     <row r="136">
@@ -3170,19 +3218,19 @@
         </is>
       </c>
       <c r="B136" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C136" t="n">
         <v>0</v>
       </c>
       <c r="D136" t="n">
-        <v>0.02268078354527081</v>
+        <v>0.1073610704986105</v>
       </c>
       <c r="E136" t="n">
-        <v>0.4887718406642503</v>
+        <v>0.2370464961242249</v>
       </c>
       <c r="F136" t="n">
-        <v>0.488547375790479</v>
+        <v>0.6555924333771647</v>
       </c>
     </row>
     <row r="137">
@@ -3198,13 +3246,13 @@
         <v>0</v>
       </c>
       <c r="D137" t="n">
-        <v>0.0005071590040881884</v>
+        <v>0.00168521996727838</v>
       </c>
       <c r="E137" t="n">
-        <v>0.7602848581513473</v>
+        <v>0.7364462247816231</v>
       </c>
       <c r="F137" t="n">
-        <v>0.2392079828445646</v>
+        <v>0.2618685552510984</v>
       </c>
     </row>
     <row r="138">
@@ -3220,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="D138" t="n">
-        <v>0.5093268228682665</v>
+        <v>0.7610126529839162</v>
       </c>
       <c r="E138" t="n">
-        <v>0.3789768279865218</v>
+        <v>0.08667157496596688</v>
       </c>
       <c r="F138" t="n">
-        <v>0.1116963491452118</v>
+        <v>0.1523157720501171</v>
       </c>
     </row>
     <row r="139">
@@ -3242,13 +3290,13 @@
         <v>0</v>
       </c>
       <c r="D139" t="n">
-        <v>0.06070865694729607</v>
+        <v>0.09996008900250677</v>
       </c>
       <c r="E139" t="n">
-        <v>0.3264700564965023</v>
+        <v>0.2843382728449599</v>
       </c>
       <c r="F139" t="n">
-        <v>0.6128212865562016</v>
+        <v>0.6157016381525332</v>
       </c>
     </row>
     <row r="140">
@@ -3264,13 +3312,13 @@
         <v>0</v>
       </c>
       <c r="D140" t="n">
-        <v>0.144969739814341</v>
+        <v>0.1546123413688028</v>
       </c>
       <c r="E140" t="n">
-        <v>0.3182883495174451</v>
+        <v>0.3128320003584282</v>
       </c>
       <c r="F140" t="n">
-        <v>0.5367419106682139</v>
+        <v>0.5325556582727691</v>
       </c>
     </row>
     <row r="141">
@@ -3286,13 +3334,13 @@
         <v>0</v>
       </c>
       <c r="D141" t="n">
-        <v>0.001363463485967113</v>
+        <v>0.003200982757005789</v>
       </c>
       <c r="E141" t="n">
-        <v>0.631167945622331</v>
+        <v>0.6756115390245583</v>
       </c>
       <c r="F141" t="n">
-        <v>0.3674685908917018</v>
+        <v>0.3211874782184361</v>
       </c>
     </row>
     <row r="142">
@@ -3308,13 +3356,13 @@
         <v>0</v>
       </c>
       <c r="D142" t="n">
-        <v>0.05626665645358548</v>
+        <v>0.1453614930812844</v>
       </c>
       <c r="E142" t="n">
-        <v>0.4411855447218143</v>
+        <v>0.2831528022015239</v>
       </c>
       <c r="F142" t="n">
-        <v>0.5025477988246002</v>
+        <v>0.5714857047171917</v>
       </c>
     </row>
     <row r="143">
@@ -3324,19 +3372,19 @@
         </is>
       </c>
       <c r="B143" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C143" t="n">
         <v>0</v>
       </c>
       <c r="D143" t="n">
-        <v>0.01556376777792062</v>
+        <v>0.02014885600539048</v>
       </c>
       <c r="E143" t="n">
-        <v>0.4520931447229827</v>
+        <v>0.5601862155444896</v>
       </c>
       <c r="F143" t="n">
-        <v>0.5323430874990966</v>
+        <v>0.4196649284501199</v>
       </c>
     </row>
     <row r="144">
@@ -3346,19 +3394,19 @@
         </is>
       </c>
       <c r="B144" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C144" t="n">
         <v>0</v>
       </c>
       <c r="D144" t="n">
-        <v>0.0003933886295228681</v>
+        <v>0.002347588501780768</v>
       </c>
       <c r="E144" t="n">
-        <v>0.5574406790892651</v>
+        <v>0.4368507673109371</v>
       </c>
       <c r="F144" t="n">
-        <v>0.4421659322812121</v>
+        <v>0.5608016441872821</v>
       </c>
     </row>
     <row r="145">
@@ -3374,13 +3422,13 @@
         <v>0</v>
       </c>
       <c r="D145" t="n">
-        <v>0.001109466640971457</v>
+        <v>0.001575111753479211</v>
       </c>
       <c r="E145" t="n">
-        <v>0.6197582821759623</v>
+        <v>0.7382233461054418</v>
       </c>
       <c r="F145" t="n">
-        <v>0.3791322511830663</v>
+        <v>0.2602015421410789</v>
       </c>
     </row>
     <row r="146">
@@ -3396,13 +3444,13 @@
         <v>0</v>
       </c>
       <c r="D146" t="n">
-        <v>0.6879737775871354</v>
+        <v>0.6207562063172936</v>
       </c>
       <c r="E146" t="n">
-        <v>0.06536591892261723</v>
+        <v>0.06229197920278094</v>
       </c>
       <c r="F146" t="n">
-        <v>0.2466603034902474</v>
+        <v>0.3169518144799254</v>
       </c>
     </row>
     <row r="147">
@@ -3434,13 +3482,13 @@
         <v>0</v>
       </c>
       <c r="D148" t="n">
-        <v>0.002002316411831962</v>
+        <v>0.003080033290151539</v>
       </c>
       <c r="E148" t="n">
-        <v>0.5866642617624173</v>
+        <v>0.70129150577899</v>
       </c>
       <c r="F148" t="n">
-        <v>0.4113334218257507</v>
+        <v>0.2956284609308585</v>
       </c>
     </row>
     <row r="149">
@@ -3450,19 +3498,19 @@
         </is>
       </c>
       <c r="B149" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C149" t="n">
         <v>0</v>
       </c>
       <c r="D149" t="n">
-        <v>0.3386404316599683</v>
+        <v>0.499697860136535</v>
       </c>
       <c r="E149" t="n">
-        <v>0.2455390217593569</v>
+        <v>0.1142098325609685</v>
       </c>
       <c r="F149" t="n">
-        <v>0.4158205465806747</v>
+        <v>0.3860923073024966</v>
       </c>
     </row>
     <row r="150">
@@ -3478,13 +3526,13 @@
         <v>0</v>
       </c>
       <c r="D150" t="n">
-        <v>0.01938043770836723</v>
+        <v>0.04478443532763883</v>
       </c>
       <c r="E150" t="n">
-        <v>0.5502846425176817</v>
+        <v>0.5329750453967689</v>
       </c>
       <c r="F150" t="n">
-        <v>0.4303349197739511</v>
+        <v>0.4222405192755921</v>
       </c>
     </row>
     <row r="151">
@@ -3500,13 +3548,13 @@
         <v>0</v>
       </c>
       <c r="D151" t="n">
-        <v>0.01770263884344978</v>
+        <v>0.0300945350595845</v>
       </c>
       <c r="E151" t="n">
-        <v>0.5647257525769938</v>
+        <v>0.5887961314081892</v>
       </c>
       <c r="F151" t="n">
-        <v>0.4175716085795566</v>
+        <v>0.3811093335322264</v>
       </c>
     </row>
     <row r="152">
@@ -3522,13 +3570,13 @@
         <v>0</v>
       </c>
       <c r="D152" t="n">
-        <v>0.6069340586035888</v>
+        <v>0.6425400271116903</v>
       </c>
       <c r="E152" t="n">
-        <v>0.1550650465511151</v>
+        <v>0.08536294445932772</v>
       </c>
       <c r="F152" t="n">
-        <v>0.238000894845296</v>
+        <v>0.2720970284289819</v>
       </c>
     </row>
     <row r="153">
@@ -3544,13 +3592,13 @@
         <v>0</v>
       </c>
       <c r="D153" t="n">
-        <v>0.05657830008215472</v>
+        <v>0.2350110423401368</v>
       </c>
       <c r="E153" t="n">
-        <v>0.7972458883606964</v>
+        <v>0.4426177269143933</v>
       </c>
       <c r="F153" t="n">
-        <v>0.146175811557149</v>
+        <v>0.3223712307454699</v>
       </c>
     </row>
     <row r="154">
@@ -3566,13 +3614,13 @@
         <v>0</v>
       </c>
       <c r="D154" t="n">
-        <v>0.006895917252360219</v>
+        <v>0.01140363566858881</v>
       </c>
       <c r="E154" t="n">
-        <v>0.6244283908442609</v>
+        <v>0.7157407347313233</v>
       </c>
       <c r="F154" t="n">
-        <v>0.3686756919033788</v>
+        <v>0.2728556296000879</v>
       </c>
     </row>
     <row r="155">
@@ -3588,13 +3636,13 @@
         <v>0</v>
       </c>
       <c r="D155" t="n">
-        <v>0.6898870671628183</v>
+        <v>0.8440823728914906</v>
       </c>
       <c r="E155" t="n">
-        <v>0.2150353963124542</v>
+        <v>0.04013292641835928</v>
       </c>
       <c r="F155" t="n">
-        <v>0.09507753652472746</v>
+        <v>0.1157847006901501</v>
       </c>
     </row>
     <row r="156">
@@ -3604,19 +3652,19 @@
         </is>
       </c>
       <c r="B156" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C156" t="n">
         <v>0</v>
       </c>
       <c r="D156" t="n">
-        <v>0.04071519002551269</v>
+        <v>0.1996581604329997</v>
       </c>
       <c r="E156" t="n">
-        <v>0.7593455791191204</v>
+        <v>0.397690615554577</v>
       </c>
       <c r="F156" t="n">
-        <v>0.1999392308553669</v>
+        <v>0.4026512240124234</v>
       </c>
     </row>
     <row r="157">
@@ -3632,13 +3680,13 @@
         <v>0</v>
       </c>
       <c r="D157" t="n">
-        <v>0.5580234568061729</v>
+        <v>0.6371673817085419</v>
       </c>
       <c r="E157" t="n">
-        <v>0.1336798463455016</v>
+        <v>0.06307319899373481</v>
       </c>
       <c r="F157" t="n">
-        <v>0.3082966968483254</v>
+        <v>0.2997594192977233</v>
       </c>
     </row>
     <row r="158">
@@ -3654,13 +3702,13 @@
         <v>0</v>
       </c>
       <c r="D158" t="n">
-        <v>0.02916350335363094</v>
+        <v>0.07841034271652349</v>
       </c>
       <c r="E158" t="n">
-        <v>0.4612424965172119</v>
+        <v>0.3225962598511843</v>
       </c>
       <c r="F158" t="n">
-        <v>0.5095940001291572</v>
+        <v>0.5989933974322922</v>
       </c>
     </row>
     <row r="159">
@@ -3676,13 +3724,13 @@
         <v>0</v>
       </c>
       <c r="D159" t="n">
-        <v>0.1974938667291924</v>
+        <v>0.3464273459842592</v>
       </c>
       <c r="E159" t="n">
-        <v>0.3604138831280069</v>
+        <v>0.1870114784333214</v>
       </c>
       <c r="F159" t="n">
-        <v>0.4420922501428007</v>
+        <v>0.4665611755824192</v>
       </c>
     </row>
     <row r="160">
@@ -3692,19 +3740,19 @@
         </is>
       </c>
       <c r="B160" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C160" t="n">
         <v>0</v>
       </c>
       <c r="D160" t="n">
-        <v>0.1703022330270844</v>
+        <v>0.4938530787239948</v>
       </c>
       <c r="E160" t="n">
-        <v>0.6578870968857006</v>
+        <v>0.2015876063664125</v>
       </c>
       <c r="F160" t="n">
-        <v>0.171810670087215</v>
+        <v>0.3045593149095927</v>
       </c>
     </row>
     <row r="161">
@@ -3720,13 +3768,13 @@
         <v>0</v>
       </c>
       <c r="D161" t="n">
-        <v>0.1550361032335481</v>
+        <v>0.273011236418025</v>
       </c>
       <c r="E161" t="n">
-        <v>0.3420742170836181</v>
+        <v>0.2121316282872841</v>
       </c>
       <c r="F161" t="n">
-        <v>0.5028896796828338</v>
+        <v>0.5148571352946908</v>
       </c>
     </row>
     <row r="162">
@@ -3736,19 +3784,19 @@
         </is>
       </c>
       <c r="B162" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C162" t="n">
         <v>0</v>
       </c>
       <c r="D162" t="n">
-        <v>0.1188713386102469</v>
+        <v>0.4461726645881601</v>
       </c>
       <c r="E162" t="n">
-        <v>0.7200412280830999</v>
+        <v>0.2304667860317678</v>
       </c>
       <c r="F162" t="n">
-        <v>0.1610874333066532</v>
+        <v>0.323360549380072</v>
       </c>
     </row>
     <row r="163">
@@ -3764,13 +3812,13 @@
         <v>0</v>
       </c>
       <c r="D163" t="n">
-        <v>0.1094967709264001</v>
+        <v>0.254738747967387</v>
       </c>
       <c r="E163" t="n">
-        <v>0.4129364877107787</v>
+        <v>0.1969444137148463</v>
       </c>
       <c r="F163" t="n">
-        <v>0.477566741362821</v>
+        <v>0.5483168383177667</v>
       </c>
     </row>
     <row r="164">
@@ -3780,14 +3828,20 @@
         </is>
       </c>
       <c r="B164" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C164" t="n">
-        <v>1</v>
-      </c>
-      <c r="D164" t="inlineStr"/>
-      <c r="E164" t="inlineStr"/>
-      <c r="F164" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="D164" t="n">
+        <v>0.5410609885382409</v>
+      </c>
+      <c r="E164" t="n">
+        <v>0.1298831376038907</v>
+      </c>
+      <c r="F164" t="n">
+        <v>0.3290558738578683</v>
+      </c>
     </row>
     <row r="165">
       <c r="A165" s="1" t="inlineStr">
@@ -3802,13 +3856,13 @@
         <v>0</v>
       </c>
       <c r="D165" t="n">
-        <v>0.1100554929980447</v>
+        <v>0.1259914995257977</v>
       </c>
       <c r="E165" t="n">
-        <v>0.386636432842111</v>
+        <v>0.393726598595066</v>
       </c>
       <c r="F165" t="n">
-        <v>0.5033080741598444</v>
+        <v>0.4802819018791362</v>
       </c>
     </row>
     <row r="166">
@@ -3824,13 +3878,13 @@
         <v>0</v>
       </c>
       <c r="D166" t="n">
-        <v>0.02001235924373807</v>
+        <v>0.05622778593435797</v>
       </c>
       <c r="E166" t="n">
-        <v>0.6120648844652327</v>
+        <v>0.5315781428726407</v>
       </c>
       <c r="F166" t="n">
-        <v>0.3679227562910293</v>
+        <v>0.4121940711930013</v>
       </c>
     </row>
     <row r="167">
@@ -3862,13 +3916,13 @@
         <v>0</v>
       </c>
       <c r="D168" t="n">
-        <v>0.002684773687731902</v>
+        <v>0.0008481872676060497</v>
       </c>
       <c r="E168" t="n">
-        <v>0.7893883960346092</v>
+        <v>0.9476146178283404</v>
       </c>
       <c r="F168" t="n">
-        <v>0.207926830277659</v>
+        <v>0.05153719490405353</v>
       </c>
     </row>
     <row r="169">
@@ -3894,19 +3948,19 @@
         </is>
       </c>
       <c r="B170" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C170" t="n">
         <v>0</v>
       </c>
       <c r="D170" t="n">
-        <v>0.0284089931959722</v>
+        <v>0.07055031561261225</v>
       </c>
       <c r="E170" t="n">
-        <v>0.5109241131406571</v>
+        <v>0.3684903578370553</v>
       </c>
       <c r="F170" t="n">
-        <v>0.4606668936633707</v>
+        <v>0.5609593265503324</v>
       </c>
     </row>
     <row r="171">
@@ -3922,13 +3976,13 @@
         <v>0</v>
       </c>
       <c r="D171" t="n">
-        <v>0.001538820202692326</v>
+        <v>0.002487315606783312</v>
       </c>
       <c r="E171" t="n">
-        <v>0.6590985049724474</v>
+        <v>0.7724971629992334</v>
       </c>
       <c r="F171" t="n">
-        <v>0.3393626748248604</v>
+        <v>0.2250155213939832</v>
       </c>
     </row>
     <row r="172">
@@ -3960,13 +4014,13 @@
         <v>0</v>
       </c>
       <c r="D173" t="n">
-        <v>0.0007106522300101765</v>
+        <v>0.000986216333533725</v>
       </c>
       <c r="E173" t="n">
-        <v>0.7081681442864785</v>
+        <v>0.8543321003664373</v>
       </c>
       <c r="F173" t="n">
-        <v>0.2911212034835114</v>
+        <v>0.144681683300029</v>
       </c>
     </row>
     <row r="174">
@@ -3982,13 +4036,13 @@
         <v>0</v>
       </c>
       <c r="D174" t="n">
-        <v>0.1005454679978368</v>
+        <v>0.227443174069187</v>
       </c>
       <c r="E174" t="n">
-        <v>0.4398016919147159</v>
+        <v>0.2587506542650069</v>
       </c>
       <c r="F174" t="n">
-        <v>0.4596528400874472</v>
+        <v>0.5138061716658061</v>
       </c>
     </row>
     <row r="175">
@@ -3998,14 +4052,20 @@
         </is>
       </c>
       <c r="B175" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C175" t="n">
-        <v>1</v>
-      </c>
-      <c r="D175" t="inlineStr"/>
-      <c r="E175" t="inlineStr"/>
-      <c r="F175" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="D175" t="n">
+        <v>0.0247175964771955</v>
+      </c>
+      <c r="E175" t="n">
+        <v>0.5281640425894034</v>
+      </c>
+      <c r="F175" t="n">
+        <v>0.447118360933401</v>
+      </c>
     </row>
     <row r="176">
       <c r="A176" s="1" t="inlineStr">
@@ -4068,13 +4128,13 @@
         <v>0</v>
       </c>
       <c r="D179" t="n">
-        <v>0.2529499234551867</v>
+        <v>0.4045437604360871</v>
       </c>
       <c r="E179" t="n">
-        <v>0.3402868291156004</v>
+        <v>0.1652673077424817</v>
       </c>
       <c r="F179" t="n">
-        <v>0.4067632474292129</v>
+        <v>0.4301889318214313</v>
       </c>
     </row>
     <row r="180">
@@ -4090,13 +4150,13 @@
         <v>0</v>
       </c>
       <c r="D180" t="n">
-        <v>0.701498695115207</v>
+        <v>0.717236701122497</v>
       </c>
       <c r="E180" t="n">
-        <v>0.07203236060164914</v>
+        <v>0.0381375027538521</v>
       </c>
       <c r="F180" t="n">
-        <v>0.2264689442831438</v>
+        <v>0.2446257961236509</v>
       </c>
     </row>
     <row r="181">
@@ -4112,13 +4172,13 @@
         <v>0</v>
       </c>
       <c r="D181" t="n">
-        <v>0.8938693272715503</v>
+        <v>0.8828401690935656</v>
       </c>
       <c r="E181" t="n">
-        <v>0.02055328691947881</v>
+        <v>0.01080327621178092</v>
       </c>
       <c r="F181" t="n">
-        <v>0.08557738580897079</v>
+        <v>0.1063565546946536</v>
       </c>
     </row>
     <row r="182">
@@ -4134,13 +4194,13 @@
         <v>0</v>
       </c>
       <c r="D182" t="n">
-        <v>0.004386135131445846</v>
+        <v>0.01117107576392818</v>
       </c>
       <c r="E182" t="n">
-        <v>0.5080751052917839</v>
+        <v>0.5228414449102613</v>
       </c>
       <c r="F182" t="n">
-        <v>0.4875387595767701</v>
+        <v>0.4659874793258105</v>
       </c>
     </row>
     <row r="183">
@@ -4150,19 +4210,19 @@
         </is>
       </c>
       <c r="B183" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C183" t="n">
         <v>0</v>
       </c>
       <c r="D183" t="n">
-        <v>0.007199009493861391</v>
+        <v>0.01526013037142062</v>
       </c>
       <c r="E183" t="n">
-        <v>0.4947839434843284</v>
+        <v>0.5557983574785378</v>
       </c>
       <c r="F183" t="n">
-        <v>0.49801704702181</v>
+        <v>0.4289415121500414</v>
       </c>
     </row>
     <row r="184">
@@ -4178,13 +4238,13 @@
         <v>0</v>
       </c>
       <c r="D184" t="n">
-        <v>0.9599474720853924</v>
+        <v>0.9535308850957227</v>
       </c>
       <c r="E184" t="n">
-        <v>0.006306274912958413</v>
+        <v>0.001904217939270249</v>
       </c>
       <c r="F184" t="n">
-        <v>0.03374625300164916</v>
+        <v>0.04456489696500706</v>
       </c>
     </row>
     <row r="185">
@@ -4200,13 +4260,13 @@
         <v>0</v>
       </c>
       <c r="D185" t="n">
-        <v>0.03634961112748131</v>
+        <v>0.06452840969827892</v>
       </c>
       <c r="E185" t="n">
-        <v>0.3977679697755155</v>
+        <v>0.3794060730017616</v>
       </c>
       <c r="F185" t="n">
-        <v>0.5658824190970032</v>
+        <v>0.5560655172999595</v>
       </c>
     </row>
     <row r="186">
@@ -4222,13 +4282,13 @@
         <v>0</v>
       </c>
       <c r="D186" t="n">
-        <v>0.002667634854924529</v>
+        <v>0.0087667075182426</v>
       </c>
       <c r="E186" t="n">
-        <v>0.4602550089659995</v>
+        <v>0.4869545454992978</v>
       </c>
       <c r="F186" t="n">
-        <v>0.537077356179076</v>
+        <v>0.5042787469824596</v>
       </c>
     </row>
     <row r="187">
@@ -4244,13 +4304,13 @@
         <v>0</v>
       </c>
       <c r="D187" t="n">
-        <v>0.2230522249196489</v>
+        <v>0.2965182674403469</v>
       </c>
       <c r="E187" t="n">
-        <v>0.2366814210556907</v>
+        <v>0.168528677948115</v>
       </c>
       <c r="F187" t="n">
-        <v>0.5402663540246603</v>
+        <v>0.5349530546115381</v>
       </c>
     </row>
     <row r="188">
@@ -4260,19 +4320,19 @@
         </is>
       </c>
       <c r="B188" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C188" t="n">
         <v>0</v>
       </c>
       <c r="D188" t="n">
-        <v>0.3931320956521069</v>
+        <v>0.5289110654023366</v>
       </c>
       <c r="E188" t="n">
-        <v>0.2074306457475741</v>
+        <v>0.09043758619603506</v>
       </c>
       <c r="F188" t="n">
-        <v>0.399437258600319</v>
+        <v>0.3806513484016285</v>
       </c>
     </row>
     <row r="189">
@@ -4288,13 +4348,13 @@
         <v>0</v>
       </c>
       <c r="D189" t="n">
-        <v>0.3018006680041724</v>
+        <v>0.3521940403974115</v>
       </c>
       <c r="E189" t="n">
-        <v>0.2222355129937036</v>
+        <v>0.1513315400839532</v>
       </c>
       <c r="F189" t="n">
-        <v>0.4759638190021241</v>
+        <v>0.4964744195186354</v>
       </c>
     </row>
     <row r="190">
@@ -4310,13 +4370,13 @@
         <v>0</v>
       </c>
       <c r="D190" t="n">
-        <v>0.002261520723953929</v>
+        <v>0.003517571689134916</v>
       </c>
       <c r="E190" t="n">
-        <v>0.6521979686206233</v>
+        <v>0.7647158899646065</v>
       </c>
       <c r="F190" t="n">
-        <v>0.3455405106554228</v>
+        <v>0.2317665383462585</v>
       </c>
     </row>
     <row r="191">
@@ -4329,11 +4389,17 @@
         <v>3</v>
       </c>
       <c r="C191" t="n">
-        <v>1</v>
-      </c>
-      <c r="D191" t="inlineStr"/>
-      <c r="E191" t="inlineStr"/>
-      <c r="F191" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="D191" t="n">
+        <v>0.05060292212016287</v>
+      </c>
+      <c r="E191" t="n">
+        <v>0.4323818097468305</v>
+      </c>
+      <c r="F191" t="n">
+        <v>0.5170152681330066</v>
+      </c>
     </row>
     <row r="192">
       <c r="A192" s="1" t="inlineStr">
@@ -4412,13 +4478,13 @@
         <v>0</v>
       </c>
       <c r="D196" t="n">
-        <v>0.1049602865541043</v>
+        <v>0.1756041800846792</v>
       </c>
       <c r="E196" t="n">
-        <v>0.3787628165996852</v>
+        <v>0.2860415046108905</v>
       </c>
       <c r="F196" t="n">
-        <v>0.5162768968462105</v>
+        <v>0.5383543153044302</v>
       </c>
     </row>
     <row r="197">
@@ -4428,19 +4494,19 @@
         </is>
       </c>
       <c r="B197" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C197" t="n">
         <v>0</v>
       </c>
       <c r="D197" t="n">
-        <v>0.06192824230393659</v>
+        <v>0.1036694316028374</v>
       </c>
       <c r="E197" t="n">
-        <v>0.5134443954205086</v>
+        <v>0.4277846405382809</v>
       </c>
       <c r="F197" t="n">
-        <v>0.4246273622755549</v>
+        <v>0.4685459278588817</v>
       </c>
     </row>
     <row r="198">
@@ -4456,13 +4522,13 @@
         <v>0</v>
       </c>
       <c r="D198" t="n">
-        <v>0.1323377058611789</v>
+        <v>0.1648682910011866</v>
       </c>
       <c r="E198" t="n">
-        <v>0.2871523173932533</v>
+        <v>0.287612297464109</v>
       </c>
       <c r="F198" t="n">
-        <v>0.5805099767455677</v>
+        <v>0.5475194115347044</v>
       </c>
     </row>
     <row r="199">
@@ -4478,13 +4544,13 @@
         <v>0</v>
       </c>
       <c r="D199" t="n">
-        <v>0.564192749522137</v>
+        <v>0.5941043358519643</v>
       </c>
       <c r="E199" t="n">
-        <v>0.1403881757876969</v>
+        <v>0.08485805592929248</v>
       </c>
       <c r="F199" t="n">
-        <v>0.2954190746901661</v>
+        <v>0.3210376082187432</v>
       </c>
     </row>
     <row r="200">
@@ -4500,13 +4566,13 @@
         <v>0</v>
       </c>
       <c r="D200" t="n">
-        <v>0.5183191697138758</v>
+        <v>0.555146273825237</v>
       </c>
       <c r="E200" t="n">
-        <v>0.09491099687452272</v>
+        <v>0.06398451216588388</v>
       </c>
       <c r="F200" t="n">
-        <v>0.3867698334116014</v>
+        <v>0.3808692140088792</v>
       </c>
     </row>
     <row r="201">
@@ -4522,13 +4588,13 @@
         <v>0</v>
       </c>
       <c r="D201" t="n">
-        <v>0.07631167763938312</v>
+        <v>0.09865385431037843</v>
       </c>
       <c r="E201" t="n">
-        <v>0.3133915858235942</v>
+        <v>0.364015934452712</v>
       </c>
       <c r="F201" t="n">
-        <v>0.6102967365370228</v>
+        <v>0.5373302112369095</v>
       </c>
     </row>
     <row r="202">
@@ -4544,13 +4610,13 @@
         <v>0</v>
       </c>
       <c r="D202" t="n">
-        <v>0.1124964598811428</v>
+        <v>0.1348008567680919</v>
       </c>
       <c r="E202" t="n">
-        <v>0.3002894021281011</v>
+        <v>0.3199834486507654</v>
       </c>
       <c r="F202" t="n">
-        <v>0.5872141379907561</v>
+        <v>0.5452156945811427</v>
       </c>
     </row>
     <row r="203">
@@ -4566,13 +4632,13 @@
         <v>0</v>
       </c>
       <c r="D203" t="n">
-        <v>0.2318342844516869</v>
+        <v>0.2895110058150241</v>
       </c>
       <c r="E203" t="n">
-        <v>0.2940738382289224</v>
+        <v>0.2067485480755649</v>
       </c>
       <c r="F203" t="n">
-        <v>0.4740918773193907</v>
+        <v>0.503740446109411</v>
       </c>
     </row>
     <row r="204">
@@ -4582,19 +4648,19 @@
         </is>
       </c>
       <c r="B204" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C204" t="n">
         <v>0</v>
       </c>
       <c r="D204" t="n">
-        <v>0.3054630040497492</v>
+        <v>0.4464034177005252</v>
       </c>
       <c r="E204" t="n">
-        <v>0.342395458610124</v>
+        <v>0.1541750337116524</v>
       </c>
       <c r="F204" t="n">
-        <v>0.3521415373401268</v>
+        <v>0.3994215485878224</v>
       </c>
     </row>
     <row r="205">
@@ -4604,19 +4670,19 @@
         </is>
       </c>
       <c r="B205" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C205" t="n">
         <v>0</v>
       </c>
       <c r="D205" t="n">
-        <v>0.3781114005739757</v>
+        <v>0.7250264139805445</v>
       </c>
       <c r="E205" t="n">
-        <v>0.4643397078913403</v>
+        <v>0.07522575110987928</v>
       </c>
       <c r="F205" t="n">
-        <v>0.1575488915346841</v>
+        <v>0.1997478349095761</v>
       </c>
     </row>
     <row r="206">
@@ -4648,13 +4714,13 @@
         <v>0</v>
       </c>
       <c r="D207" t="n">
-        <v>0.04902910596230557</v>
+        <v>0.1411805175366424</v>
       </c>
       <c r="E207" t="n">
-        <v>0.3588962099141335</v>
+        <v>0.2059809288619374</v>
       </c>
       <c r="F207" t="n">
-        <v>0.5920746841235609</v>
+        <v>0.6528385536014202</v>
       </c>
     </row>
     <row r="208">
@@ -4670,13 +4736,13 @@
         <v>0</v>
       </c>
       <c r="D208" t="n">
-        <v>0.04279113578695608</v>
+        <v>0.07567596103377174</v>
       </c>
       <c r="E208" t="n">
-        <v>0.3693296647483429</v>
+        <v>0.3724212566043369</v>
       </c>
       <c r="F208" t="n">
-        <v>0.587879199464701</v>
+        <v>0.5519027823618914</v>
       </c>
     </row>
     <row r="209">
@@ -4692,13 +4758,13 @@
         <v>0</v>
       </c>
       <c r="D209" t="n">
-        <v>0.02907747913321642</v>
+        <v>0.05948066933203202</v>
       </c>
       <c r="E209" t="n">
-        <v>0.447831199274171</v>
+        <v>0.4321061113479939</v>
       </c>
       <c r="F209" t="n">
-        <v>0.5230913215926126</v>
+        <v>0.5084132193199742</v>
       </c>
     </row>
     <row r="210">
@@ -4708,14 +4774,20 @@
         </is>
       </c>
       <c r="B210" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C210" t="n">
-        <v>1</v>
-      </c>
-      <c r="D210" t="inlineStr"/>
-      <c r="E210" t="inlineStr"/>
-      <c r="F210" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="D210" t="n">
+        <v>0.04289911648253197</v>
+      </c>
+      <c r="E210" t="n">
+        <v>0.3507570920745396</v>
+      </c>
+      <c r="F210" t="n">
+        <v>0.6063437914429284</v>
+      </c>
     </row>
     <row r="211">
       <c r="A211" s="1" t="inlineStr">
@@ -4762,13 +4834,13 @@
         <v>0</v>
       </c>
       <c r="D213" t="n">
-        <v>0.1500587455526955</v>
+        <v>0.2248049613966576</v>
       </c>
       <c r="E213" t="n">
-        <v>0.3445308192212549</v>
+        <v>0.2614188324547843</v>
       </c>
       <c r="F213" t="n">
-        <v>0.5054104352260497</v>
+        <v>0.5137762061485581</v>
       </c>
     </row>
     <row r="214">
@@ -4784,13 +4856,13 @@
         <v>0</v>
       </c>
       <c r="D214" t="n">
-        <v>0.08045481458824381</v>
+        <v>0.1058656176806251</v>
       </c>
       <c r="E214" t="n">
-        <v>0.3722902419989548</v>
+        <v>0.3715830592948106</v>
       </c>
       <c r="F214" t="n">
-        <v>0.5472549434128013</v>
+        <v>0.5225513230245644</v>
       </c>
     </row>
     <row r="215">
@@ -4800,19 +4872,19 @@
         </is>
       </c>
       <c r="B215" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C215" t="n">
         <v>0</v>
       </c>
       <c r="D215" t="n">
-        <v>0.1147299523354985</v>
+        <v>0.1834728685603598</v>
       </c>
       <c r="E215" t="n">
-        <v>0.4805683719194844</v>
+        <v>0.3779630857132855</v>
       </c>
       <c r="F215" t="n">
-        <v>0.4047016757450172</v>
+        <v>0.4385640457263547</v>
       </c>
     </row>
     <row r="216">
@@ -4822,19 +4894,19 @@
         </is>
       </c>
       <c r="B216" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C216" t="n">
         <v>0</v>
       </c>
       <c r="D216" t="n">
-        <v>0.03536263236836741</v>
+        <v>0.07394659130145134</v>
       </c>
       <c r="E216" t="n">
-        <v>0.4914223917752118</v>
+        <v>0.4560735258577036</v>
       </c>
       <c r="F216" t="n">
-        <v>0.4732149758564207</v>
+        <v>0.4699798828408451</v>
       </c>
     </row>
     <row r="217">
@@ -4850,13 +4922,13 @@
         <v>0</v>
       </c>
       <c r="D217" t="n">
-        <v>0.2878368098982143</v>
+        <v>0.3436766564368302</v>
       </c>
       <c r="E217" t="n">
-        <v>0.3278244542536197</v>
+        <v>0.2275922067897609</v>
       </c>
       <c r="F217" t="n">
-        <v>0.3843387358481659</v>
+        <v>0.428731136773409</v>
       </c>
     </row>
     <row r="218">
@@ -4888,13 +4960,13 @@
         <v>0</v>
       </c>
       <c r="D219" t="n">
-        <v>0.04651375488752937</v>
+        <v>0.08923069849161919</v>
       </c>
       <c r="E219" t="n">
-        <v>0.5630912316140849</v>
+        <v>0.4999152927219606</v>
       </c>
       <c r="F219" t="n">
-        <v>0.3903950134983857</v>
+        <v>0.4108540087864203</v>
       </c>
     </row>
     <row r="220">
@@ -4910,13 +4982,13 @@
         <v>0</v>
       </c>
       <c r="D220" t="n">
-        <v>0.9962683245231044</v>
+        <v>0.9956302148490278</v>
       </c>
       <c r="E220" t="n">
-        <v>0.002030276703567539</v>
+        <v>0.0002990940680518239</v>
       </c>
       <c r="F220" t="n">
-        <v>0.001701398773328011</v>
+        <v>0.004070691082920168</v>
       </c>
     </row>
     <row r="221">
@@ -4932,13 +5004,13 @@
         <v>0</v>
       </c>
       <c r="D221" t="n">
-        <v>0.002959714057749545</v>
+        <v>0.009522812520092355</v>
       </c>
       <c r="E221" t="n">
-        <v>0.7508601883591014</v>
+        <v>0.6302043099276413</v>
       </c>
       <c r="F221" t="n">
-        <v>0.2461800975831491</v>
+        <v>0.3602728775522663</v>
       </c>
     </row>
     <row r="222">
@@ -4954,13 +5026,13 @@
         <v>0</v>
       </c>
       <c r="D222" t="n">
-        <v>0.08666577562375392</v>
+        <v>0.1304542695115113</v>
       </c>
       <c r="E222" t="n">
-        <v>0.450968541588743</v>
+        <v>0.3440801724551458</v>
       </c>
       <c r="F222" t="n">
-        <v>0.462365682787503</v>
+        <v>0.5254655580333427</v>
       </c>
     </row>
     <row r="223">
@@ -4976,13 +5048,13 @@
         <v>0</v>
       </c>
       <c r="D223" t="n">
-        <v>0.9843909436338206</v>
+        <v>0.9840091875713424</v>
       </c>
       <c r="E223" t="n">
-        <v>0.008826341078819707</v>
+        <v>0.001612269344236684</v>
       </c>
       <c r="F223" t="n">
-        <v>0.006782715287359585</v>
+        <v>0.01437854308442102</v>
       </c>
     </row>
     <row r="224">
@@ -4992,19 +5064,19 @@
         </is>
       </c>
       <c r="B224" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C224" t="n">
         <v>0</v>
       </c>
       <c r="D224" t="n">
-        <v>0.4233954275551687</v>
+        <v>0.4372521059302321</v>
       </c>
       <c r="E224" t="n">
-        <v>0.1890224180291591</v>
+        <v>0.116587642227976</v>
       </c>
       <c r="F224" t="n">
-        <v>0.3875821544156721</v>
+        <v>0.4461602518417921</v>
       </c>
     </row>
     <row r="225">
@@ -5014,19 +5086,19 @@
         </is>
       </c>
       <c r="B225" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C225" t="n">
         <v>0</v>
       </c>
       <c r="D225" t="n">
-        <v>0.3863513891498178</v>
+        <v>0.4854797209656839</v>
       </c>
       <c r="E225" t="n">
-        <v>0.2219768976274654</v>
+        <v>0.1320105982795221</v>
       </c>
       <c r="F225" t="n">
-        <v>0.3916717132227169</v>
+        <v>0.382509680754794</v>
       </c>
     </row>
     <row r="226">
@@ -5042,13 +5114,13 @@
         <v>0</v>
       </c>
       <c r="D226" t="n">
-        <v>0.9524083212871668</v>
+        <v>0.965772120594963</v>
       </c>
       <c r="E226" t="n">
-        <v>0.02925126596570984</v>
+        <v>0.005176164652450653</v>
       </c>
       <c r="F226" t="n">
-        <v>0.01834041274712341</v>
+        <v>0.02905171475258631</v>
       </c>
     </row>
     <row r="227">
@@ -5064,13 +5136,13 @@
         <v>0</v>
       </c>
       <c r="D227" t="n">
-        <v>0.009004679590529568</v>
+        <v>0.03136113591462697</v>
       </c>
       <c r="E227" t="n">
-        <v>0.7495538962526601</v>
+        <v>0.5936788660430745</v>
       </c>
       <c r="F227" t="n">
-        <v>0.2414414241568103</v>
+        <v>0.3749599980422985</v>
       </c>
     </row>
     <row r="228">
@@ -5086,13 +5158,13 @@
         <v>0</v>
       </c>
       <c r="D228" t="n">
-        <v>0.002956211458064703</v>
+        <v>0.008306403693971343</v>
       </c>
       <c r="E228" t="n">
-        <v>0.6782527718029024</v>
+        <v>0.6236771600090636</v>
       </c>
       <c r="F228" t="n">
-        <v>0.3187910167390328</v>
+        <v>0.3680164362969651</v>
       </c>
     </row>
     <row r="229">
@@ -5108,13 +5180,13 @@
         <v>0</v>
       </c>
       <c r="D229" t="n">
-        <v>0.5951219715514204</v>
+        <v>0.4350472644245099</v>
       </c>
       <c r="E229" t="n">
-        <v>0.3239879183878909</v>
+        <v>0.3982592637919208</v>
       </c>
       <c r="F229" t="n">
-        <v>0.08089011006068869</v>
+        <v>0.1666934717835693</v>
       </c>
     </row>
     <row r="230">
@@ -5130,13 +5202,13 @@
         <v>0</v>
       </c>
       <c r="D230" t="n">
-        <v>0.0158444570688461</v>
+        <v>0.04590013778616962</v>
       </c>
       <c r="E230" t="n">
-        <v>0.5498063456949621</v>
+        <v>0.5053325588562928</v>
       </c>
       <c r="F230" t="n">
-        <v>0.4343491972361919</v>
+        <v>0.4487673033575376</v>
       </c>
     </row>
     <row r="231">
@@ -5152,13 +5224,13 @@
         <v>0</v>
       </c>
       <c r="D231" t="n">
-        <v>0.01358754606268048</v>
+        <v>0.02577256915155296</v>
       </c>
       <c r="E231" t="n">
-        <v>0.5975081373675202</v>
+        <v>0.6309567324599212</v>
       </c>
       <c r="F231" t="n">
-        <v>0.3889043165697993</v>
+        <v>0.3432706983885258</v>
       </c>
     </row>
     <row r="232">
@@ -5174,13 +5246,13 @@
         <v>0</v>
       </c>
       <c r="D232" t="n">
-        <v>0.0003557406441771726</v>
+        <v>0.001050112384966405</v>
       </c>
       <c r="E232" t="n">
-        <v>0.6304859814642572</v>
+        <v>0.6688563763979569</v>
       </c>
       <c r="F232" t="n">
-        <v>0.3691582778915657</v>
+        <v>0.3300935112170766</v>
       </c>
     </row>
     <row r="233">
@@ -5190,19 +5262,19 @@
         </is>
       </c>
       <c r="B233" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C233" t="n">
         <v>0</v>
       </c>
       <c r="D233" t="n">
-        <v>0.08978764675137547</v>
+        <v>0.4109092643076966</v>
       </c>
       <c r="E233" t="n">
-        <v>0.7208674189238503</v>
+        <v>0.2306484750923641</v>
       </c>
       <c r="F233" t="n">
-        <v>0.1893449343247741</v>
+        <v>0.3584422605999393</v>
       </c>
     </row>
     <row r="234">
@@ -5218,13 +5290,13 @@
         <v>0</v>
       </c>
       <c r="D234" t="n">
-        <v>0.001220700953776836</v>
+        <v>0.003746664117054082</v>
       </c>
       <c r="E234" t="n">
-        <v>0.5471078627150953</v>
+        <v>0.6195954099350666</v>
       </c>
       <c r="F234" t="n">
-        <v>0.4516714363311279</v>
+        <v>0.3766579259478792</v>
       </c>
     </row>
     <row r="235">
@@ -5240,13 +5312,13 @@
         <v>0</v>
       </c>
       <c r="D235" t="n">
-        <v>0.0007069635740411741</v>
+        <v>0.001663788090578917</v>
       </c>
       <c r="E235" t="n">
-        <v>0.6290764373917658</v>
+        <v>0.7361664249162621</v>
       </c>
       <c r="F235" t="n">
-        <v>0.3702165990341932</v>
+        <v>0.262169786993159</v>
       </c>
     </row>
     <row r="236">
@@ -5262,13 +5334,13 @@
         <v>0</v>
       </c>
       <c r="D236" t="n">
-        <v>0.0337435660453354</v>
+        <v>0.05136000199127977</v>
       </c>
       <c r="E236" t="n">
-        <v>0.5406436429735269</v>
+        <v>0.5223840515946563</v>
       </c>
       <c r="F236" t="n">
-        <v>0.4256127909811378</v>
+        <v>0.426255946414064</v>
       </c>
     </row>
     <row r="237">
@@ -5284,13 +5356,13 @@
         <v>0</v>
       </c>
       <c r="D237" t="n">
-        <v>0.0003345504228512149</v>
+        <v>0.0004315603200621002</v>
       </c>
       <c r="E237" t="n">
-        <v>0.6214722348114413</v>
+        <v>0.832235800143206</v>
       </c>
       <c r="F237" t="n">
-        <v>0.3781932147657074</v>
+        <v>0.1673326395367318</v>
       </c>
     </row>
   </sheetData>

--- a/results/02_taxa_assemblage/Wards_LDA/classifier_prediction/artifacts/02_predicted_data.xlsx
+++ b/results/02_taxa_assemblage/Wards_LDA/classifier_prediction/artifacts/02_predicted_data.xlsx
@@ -528,13 +528,13 @@
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>0.5226359306546439</v>
+        <v>0.51760718215146</v>
       </c>
       <c r="E5" t="n">
-        <v>0.2291364728044516</v>
+        <v>0.270569278467964</v>
       </c>
       <c r="F5" t="n">
-        <v>0.2482275965409045</v>
+        <v>0.211823539380576</v>
       </c>
     </row>
     <row r="6">
@@ -566,13 +566,13 @@
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>0.01489446812401716</v>
+        <v>0.01205447541208351</v>
       </c>
       <c r="E7" t="n">
-        <v>0.807751158072272</v>
+        <v>0.7630811594907506</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1773543738037108</v>
+        <v>0.2248643650971658</v>
       </c>
     </row>
     <row r="8">
@@ -588,13 +588,13 @@
         <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>0.2111124066140017</v>
+        <v>0.2957601831399553</v>
       </c>
       <c r="E8" t="n">
-        <v>0.3000021257156584</v>
+        <v>0.2173601465793611</v>
       </c>
       <c r="F8" t="n">
-        <v>0.48888546767034</v>
+        <v>0.4868796702806837</v>
       </c>
     </row>
     <row r="9">
@@ -604,19 +604,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C9" t="n">
         <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>0.5059118442986229</v>
+        <v>0.2745911152028067</v>
       </c>
       <c r="E9" t="n">
-        <v>0.1524629023762065</v>
+        <v>0.3925257286788821</v>
       </c>
       <c r="F9" t="n">
-        <v>0.3416252533251706</v>
+        <v>0.3328831561183114</v>
       </c>
     </row>
     <row r="10">
@@ -632,13 +632,13 @@
         <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>0.1249447267327093</v>
+        <v>0.0990141124486832</v>
       </c>
       <c r="E10" t="n">
-        <v>0.5404418832510692</v>
+        <v>0.5617069783939286</v>
       </c>
       <c r="F10" t="n">
-        <v>0.3346133900162214</v>
+        <v>0.3392789091573882</v>
       </c>
     </row>
     <row r="11">
@@ -686,13 +686,13 @@
         <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>0.0827645530778482</v>
+        <v>0.0319993610748143</v>
       </c>
       <c r="E13" t="n">
-        <v>0.3248219099972258</v>
+        <v>0.4101117860007872</v>
       </c>
       <c r="F13" t="n">
-        <v>0.592413536924926</v>
+        <v>0.5578888529243985</v>
       </c>
     </row>
     <row r="14">
@@ -708,13 +708,13 @@
         <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>0.02021428015156124</v>
+        <v>0.008733585107928842</v>
       </c>
       <c r="E14" t="n">
-        <v>0.5132173807569668</v>
+        <v>0.5180251731637969</v>
       </c>
       <c r="F14" t="n">
-        <v>0.466568339091472</v>
+        <v>0.4732412417282741</v>
       </c>
     </row>
     <row r="15">
@@ -730,13 +730,13 @@
         <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>0.7326345398313907</v>
+        <v>0.7251528545309688</v>
       </c>
       <c r="E15" t="n">
-        <v>0.03909903428440185</v>
+        <v>0.05746029120438521</v>
       </c>
       <c r="F15" t="n">
-        <v>0.2282664258842075</v>
+        <v>0.217386854264646</v>
       </c>
     </row>
     <row r="16">
@@ -752,13 +752,13 @@
         <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>0.5063247691605232</v>
+        <v>0.4413922742866587</v>
       </c>
       <c r="E16" t="n">
-        <v>0.132191629908915</v>
+        <v>0.2016528575176822</v>
       </c>
       <c r="F16" t="n">
-        <v>0.3614836009305619</v>
+        <v>0.356954868195659</v>
       </c>
     </row>
     <row r="17">
@@ -771,17 +771,11 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
-      </c>
-      <c r="D17" t="n">
-        <v>0.005104641533208437</v>
-      </c>
-      <c r="E17" t="n">
-        <v>0.8440637273157225</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0.150831631151069</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
@@ -796,13 +790,13 @@
         <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>0.06501900502098358</v>
+        <v>0.0401239432812983</v>
       </c>
       <c r="E18" t="n">
-        <v>0.421434070455503</v>
+        <v>0.4188914347322743</v>
       </c>
       <c r="F18" t="n">
-        <v>0.5135469245235135</v>
+        <v>0.5409846219864274</v>
       </c>
     </row>
     <row r="19">
@@ -828,20 +822,14 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D20" t="n">
-        <v>0.02271201776655765</v>
-      </c>
-      <c r="E20" t="n">
-        <v>0.6226961647750711</v>
-      </c>
-      <c r="F20" t="n">
-        <v>0.3545918174583714</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
@@ -856,13 +844,13 @@
         <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>0.9770271432156691</v>
+        <v>0.9878496765578777</v>
       </c>
       <c r="E21" t="n">
-        <v>0.003278422550466856</v>
+        <v>0.003249901162520438</v>
       </c>
       <c r="F21" t="n">
-        <v>0.01969443423386409</v>
+        <v>0.008900422279601953</v>
       </c>
     </row>
     <row r="22">
@@ -878,13 +866,13 @@
         <v>0</v>
       </c>
       <c r="D22" t="n">
-        <v>0.839918057419032</v>
+        <v>0.9213121660080671</v>
       </c>
       <c r="E22" t="n">
-        <v>0.03375867393986022</v>
+        <v>0.01429801130649069</v>
       </c>
       <c r="F22" t="n">
-        <v>0.1263232686411078</v>
+        <v>0.06438982268544222</v>
       </c>
     </row>
     <row r="23">
@@ -900,13 +888,13 @@
         <v>0</v>
       </c>
       <c r="D23" t="n">
-        <v>0.00180886925189019</v>
+        <v>0.002743775169934348</v>
       </c>
       <c r="E23" t="n">
-        <v>0.8860539714385011</v>
+        <v>0.7376466831505993</v>
       </c>
       <c r="F23" t="n">
-        <v>0.1121371593096087</v>
+        <v>0.2596095416794664</v>
       </c>
     </row>
     <row r="24">
@@ -922,13 +910,13 @@
         <v>0</v>
       </c>
       <c r="D24" t="n">
-        <v>0.2494046438815222</v>
+        <v>0.2295818063910634</v>
       </c>
       <c r="E24" t="n">
-        <v>0.1372357056035454</v>
+        <v>0.1858265172719191</v>
       </c>
       <c r="F24" t="n">
-        <v>0.6133596505149324</v>
+        <v>0.5845916763370175</v>
       </c>
     </row>
     <row r="25">
@@ -938,20 +926,14 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C25" t="n">
-        <v>0</v>
-      </c>
-      <c r="D25" t="n">
-        <v>0.0002023030387739087</v>
-      </c>
-      <c r="E25" t="n">
-        <v>0.9160878484073041</v>
-      </c>
-      <c r="F25" t="n">
-        <v>0.08370984855392208</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
@@ -982,13 +964,13 @@
         <v>0</v>
       </c>
       <c r="D27" t="n">
-        <v>0.8203715372380513</v>
+        <v>0.9388267025705126</v>
       </c>
       <c r="E27" t="n">
-        <v>0.05724280986039346</v>
+        <v>0.01136631813651446</v>
       </c>
       <c r="F27" t="n">
-        <v>0.1223856529015552</v>
+        <v>0.04980697929297302</v>
       </c>
     </row>
     <row r="28">
@@ -1004,13 +986,13 @@
         <v>0</v>
       </c>
       <c r="D28" t="n">
-        <v>0.9158763859346821</v>
+        <v>0.9410405014249446</v>
       </c>
       <c r="E28" t="n">
-        <v>0.01632040409598928</v>
+        <v>0.01631651261576264</v>
       </c>
       <c r="F28" t="n">
-        <v>0.06780320996932852</v>
+        <v>0.04264298595929285</v>
       </c>
     </row>
     <row r="29">
@@ -1042,13 +1024,13 @@
         <v>0</v>
       </c>
       <c r="D30" t="n">
-        <v>0.8985309978098602</v>
+        <v>0.9417354351954883</v>
       </c>
       <c r="E30" t="n">
-        <v>0.02665473089908258</v>
+        <v>0.03172292099372133</v>
       </c>
       <c r="F30" t="n">
-        <v>0.07481427129105707</v>
+        <v>0.02654164381079019</v>
       </c>
     </row>
     <row r="31">
@@ -1074,19 +1056,19 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C32" t="n">
         <v>0</v>
       </c>
       <c r="D32" t="n">
-        <v>0.01007278726379384</v>
+        <v>0.003861373224362521</v>
       </c>
       <c r="E32" t="n">
-        <v>0.428368076402425</v>
+        <v>0.8785168966340402</v>
       </c>
       <c r="F32" t="n">
-        <v>0.5615591363337812</v>
+        <v>0.1176217301415973</v>
       </c>
     </row>
     <row r="33">
@@ -1134,13 +1116,13 @@
         <v>0</v>
       </c>
       <c r="D35" t="n">
-        <v>0.9537058750726779</v>
+        <v>0.9771977699468267</v>
       </c>
       <c r="E35" t="n">
-        <v>0.002356190242546467</v>
+        <v>0.002168328390848127</v>
       </c>
       <c r="F35" t="n">
-        <v>0.04393793468477569</v>
+        <v>0.02063390166232512</v>
       </c>
     </row>
     <row r="36">
@@ -1156,13 +1138,13 @@
         <v>0</v>
       </c>
       <c r="D36" t="n">
-        <v>2.142789665453652e-05</v>
+        <v>2.018390554521627e-05</v>
       </c>
       <c r="E36" t="n">
-        <v>0.8287253505211895</v>
+        <v>0.8132118164833861</v>
       </c>
       <c r="F36" t="n">
-        <v>0.1712532215821559</v>
+        <v>0.1867679996110687</v>
       </c>
     </row>
     <row r="37">
@@ -1194,13 +1176,13 @@
         <v>0</v>
       </c>
       <c r="D38" t="n">
-        <v>0.005477664647062149</v>
+        <v>0.006736128010350644</v>
       </c>
       <c r="E38" t="n">
-        <v>0.8298238588686576</v>
+        <v>0.7012943514301159</v>
       </c>
       <c r="F38" t="n">
-        <v>0.1646984764842803</v>
+        <v>0.2919695205595335</v>
       </c>
     </row>
     <row r="39">
@@ -1216,13 +1198,13 @@
         <v>0</v>
       </c>
       <c r="D39" t="n">
-        <v>0.0005806711841481914</v>
+        <v>0.0006952220104134867</v>
       </c>
       <c r="E39" t="n">
-        <v>0.8505282872214055</v>
+        <v>0.7263532194860757</v>
       </c>
       <c r="F39" t="n">
-        <v>0.1488910415944464</v>
+        <v>0.2729515585035108</v>
       </c>
     </row>
     <row r="40">
@@ -1238,13 +1220,13 @@
         <v>0</v>
       </c>
       <c r="D40" t="n">
-        <v>0.7945098509383258</v>
+        <v>0.9199809212131519</v>
       </c>
       <c r="E40" t="n">
-        <v>0.09979410300063118</v>
+        <v>0.03463984145188473</v>
       </c>
       <c r="F40" t="n">
-        <v>0.105696046061043</v>
+        <v>0.04537923733496327</v>
       </c>
     </row>
     <row r="41">
@@ -1260,13 +1242,13 @@
         <v>0</v>
       </c>
       <c r="D41" t="n">
-        <v>0.9611066422232786</v>
+        <v>0.9771998057738691</v>
       </c>
       <c r="E41" t="n">
-        <v>0.005145844642839795</v>
+        <v>0.00423688586012302</v>
       </c>
       <c r="F41" t="n">
-        <v>0.03374751313388157</v>
+        <v>0.01856330836600769</v>
       </c>
     </row>
     <row r="42">
@@ -1282,13 +1264,13 @@
         <v>0</v>
       </c>
       <c r="D42" t="n">
-        <v>0.8766703868104359</v>
+        <v>0.9470819149406635</v>
       </c>
       <c r="E42" t="n">
-        <v>0.02658766038610999</v>
+        <v>0.01822606349598558</v>
       </c>
       <c r="F42" t="n">
-        <v>0.09674195280345425</v>
+        <v>0.03469202156335079</v>
       </c>
     </row>
     <row r="43">
@@ -1298,19 +1280,19 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C43" t="n">
         <v>0</v>
       </c>
       <c r="D43" t="n">
-        <v>0.02816565502994422</v>
+        <v>0.01680180313173195</v>
       </c>
       <c r="E43" t="n">
-        <v>0.459029209380788</v>
+        <v>0.6892190166138521</v>
       </c>
       <c r="F43" t="n">
-        <v>0.5128051355892678</v>
+        <v>0.2939791802544161</v>
       </c>
     </row>
     <row r="44">
@@ -1326,13 +1308,13 @@
         <v>0</v>
       </c>
       <c r="D44" t="n">
-        <v>0.02044684171431072</v>
+        <v>0.06856906041966575</v>
       </c>
       <c r="E44" t="n">
-        <v>0.7983207340606485</v>
+        <v>0.5362681667619854</v>
       </c>
       <c r="F44" t="n">
-        <v>0.1812324242250408</v>
+        <v>0.3951627728183489</v>
       </c>
     </row>
     <row r="45">
@@ -1348,13 +1330,13 @@
         <v>0</v>
       </c>
       <c r="D45" t="n">
-        <v>0.9817363061662057</v>
+        <v>0.9870382327589612</v>
       </c>
       <c r="E45" t="n">
-        <v>0.002490860399666152</v>
+        <v>0.004177451504566892</v>
       </c>
       <c r="F45" t="n">
-        <v>0.01577283343412834</v>
+        <v>0.00878431573647191</v>
       </c>
     </row>
     <row r="46">
@@ -1370,13 +1352,13 @@
         <v>0</v>
       </c>
       <c r="D46" t="n">
-        <v>0.896243561138075</v>
+        <v>0.9400714051852146</v>
       </c>
       <c r="E46" t="n">
-        <v>0.02620781381622551</v>
+        <v>0.01973907836299353</v>
       </c>
       <c r="F46" t="n">
-        <v>0.07754862504569944</v>
+        <v>0.04018951645179198</v>
       </c>
     </row>
     <row r="47">
@@ -1408,13 +1390,13 @@
         <v>0</v>
       </c>
       <c r="D48" t="n">
-        <v>0.0007210691321569237</v>
+        <v>0.001277982838205052</v>
       </c>
       <c r="E48" t="n">
-        <v>0.8655117886699846</v>
+        <v>0.6304141844466782</v>
       </c>
       <c r="F48" t="n">
-        <v>0.1337671421978586</v>
+        <v>0.3683078327151166</v>
       </c>
     </row>
     <row r="49">
@@ -1494,13 +1476,13 @@
         <v>0</v>
       </c>
       <c r="D53" t="n">
-        <v>0.0007235402654585954</v>
+        <v>0.0005650555776374082</v>
       </c>
       <c r="E53" t="n">
-        <v>0.7727405686472834</v>
+        <v>0.657205074825814</v>
       </c>
       <c r="F53" t="n">
-        <v>0.2265358910872581</v>
+        <v>0.3422298695965486</v>
       </c>
     </row>
     <row r="54">
@@ -1526,19 +1508,19 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C55" t="n">
         <v>0</v>
       </c>
       <c r="D55" t="n">
-        <v>0.004053038309609303</v>
+        <v>0.001379453550286939</v>
       </c>
       <c r="E55" t="n">
-        <v>0.4564669378998824</v>
+        <v>0.5123257163830953</v>
       </c>
       <c r="F55" t="n">
-        <v>0.5394800237905083</v>
+        <v>0.4862948300666177</v>
       </c>
     </row>
     <row r="56">
@@ -1554,13 +1536,13 @@
         <v>0</v>
       </c>
       <c r="D56" t="n">
-        <v>0.0006180764159351133</v>
+        <v>0.0004303362114403517</v>
       </c>
       <c r="E56" t="n">
-        <v>0.7633332640439305</v>
+        <v>0.6523883766612497</v>
       </c>
       <c r="F56" t="n">
-        <v>0.2360486595401343</v>
+        <v>0.3471812871273099</v>
       </c>
     </row>
     <row r="57">
@@ -1592,13 +1574,13 @@
         <v>0</v>
       </c>
       <c r="D58" t="n">
-        <v>0.07050149504096148</v>
+        <v>0.02277492402061991</v>
       </c>
       <c r="E58" t="n">
-        <v>0.304347398431815</v>
+        <v>0.4569434779542193</v>
       </c>
       <c r="F58" t="n">
-        <v>0.6251511065272235</v>
+        <v>0.5202815980251607</v>
       </c>
     </row>
     <row r="59">
@@ -1624,19 +1606,19 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C60" t="n">
         <v>0</v>
       </c>
       <c r="D60" t="n">
-        <v>0.00819532238724963</v>
+        <v>0.002551967998334427</v>
       </c>
       <c r="E60" t="n">
-        <v>0.4098525099015186</v>
+        <v>0.5622767254260966</v>
       </c>
       <c r="F60" t="n">
-        <v>0.5819521677112318</v>
+        <v>0.435171306575569</v>
       </c>
     </row>
     <row r="61">
@@ -1652,13 +1634,13 @@
         <v>0</v>
       </c>
       <c r="D61" t="n">
-        <v>0.3328784315304523</v>
+        <v>0.2590018031436786</v>
       </c>
       <c r="E61" t="n">
-        <v>0.1688011806896332</v>
+        <v>0.2639232148504566</v>
       </c>
       <c r="F61" t="n">
-        <v>0.4983203877799144</v>
+        <v>0.4770749820058647</v>
       </c>
     </row>
     <row r="62">
@@ -1674,13 +1656,13 @@
         <v>0</v>
       </c>
       <c r="D62" t="n">
-        <v>0.009718299724848197</v>
+        <v>0.003547875739042587</v>
       </c>
       <c r="E62" t="n">
-        <v>0.3129103881415125</v>
+        <v>0.4716707165681738</v>
       </c>
       <c r="F62" t="n">
-        <v>0.6773713121336393</v>
+        <v>0.5247814076927837</v>
       </c>
     </row>
     <row r="63">
@@ -1706,20 +1688,14 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C64" t="n">
-        <v>0</v>
-      </c>
-      <c r="D64" t="n">
-        <v>0.05462561552569862</v>
-      </c>
-      <c r="E64" t="n">
-        <v>0.3418612991495027</v>
-      </c>
-      <c r="F64" t="n">
-        <v>0.6035130853247987</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="D64" t="inlineStr"/>
+      <c r="E64" t="inlineStr"/>
+      <c r="F64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
@@ -1734,13 +1710,13 @@
         <v>0</v>
       </c>
       <c r="D65" t="n">
-        <v>3.083778982781321e-05</v>
+        <v>3.740174611572507e-05</v>
       </c>
       <c r="E65" t="n">
-        <v>0.9115570945033933</v>
+        <v>0.7946256443967609</v>
       </c>
       <c r="F65" t="n">
-        <v>0.08841206770677883</v>
+        <v>0.2053369538571236</v>
       </c>
     </row>
     <row r="66">
@@ -1756,13 +1732,13 @@
         <v>0</v>
       </c>
       <c r="D66" t="n">
-        <v>5.485985531454837e-05</v>
+        <v>0.0001415472376838121</v>
       </c>
       <c r="E66" t="n">
-        <v>0.9596386265763165</v>
+        <v>0.8300981944824123</v>
       </c>
       <c r="F66" t="n">
-        <v>0.04030651356836887</v>
+        <v>0.169760258279904</v>
       </c>
     </row>
     <row r="67">
@@ -1778,13 +1754,13 @@
         <v>0</v>
       </c>
       <c r="D67" t="n">
-        <v>0.05105410043668133</v>
+        <v>0.01832052828428277</v>
       </c>
       <c r="E67" t="n">
-        <v>0.2591283411888629</v>
+        <v>0.4525336264835466</v>
       </c>
       <c r="F67" t="n">
-        <v>0.6898175583744557</v>
+        <v>0.5291458452321707</v>
       </c>
     </row>
     <row r="68">
@@ -1800,13 +1776,13 @@
         <v>0</v>
       </c>
       <c r="D68" t="n">
-        <v>0.0001752578040481906</v>
+        <v>0.0003734287157181768</v>
       </c>
       <c r="E68" t="n">
-        <v>0.9141094283081692</v>
+        <v>0.7619131370860295</v>
       </c>
       <c r="F68" t="n">
-        <v>0.08571531388778268</v>
+        <v>0.2377134341982523</v>
       </c>
     </row>
     <row r="69">
@@ -1822,13 +1798,13 @@
         <v>0</v>
       </c>
       <c r="D69" t="n">
-        <v>0.864503225955499</v>
+        <v>0.9113361485153372</v>
       </c>
       <c r="E69" t="n">
-        <v>0.04347786841769356</v>
+        <v>0.03816412775606925</v>
       </c>
       <c r="F69" t="n">
-        <v>0.09201890562680728</v>
+        <v>0.05049972372859366</v>
       </c>
     </row>
     <row r="70">
@@ -1844,13 +1820,13 @@
         <v>0</v>
       </c>
       <c r="D70" t="n">
-        <v>0.0005290790476988852</v>
+        <v>0.0008678898627406816</v>
       </c>
       <c r="E70" t="n">
-        <v>0.9039921795838798</v>
+        <v>0.77906733942798</v>
       </c>
       <c r="F70" t="n">
-        <v>0.09547874136842131</v>
+        <v>0.2200647707092793</v>
       </c>
     </row>
     <row r="71">
@@ -1866,13 +1842,13 @@
         <v>0</v>
       </c>
       <c r="D71" t="n">
-        <v>0.003125046753655084</v>
+        <v>0.00487850122599108</v>
       </c>
       <c r="E71" t="n">
-        <v>0.8565540705588657</v>
+        <v>0.717810418366899</v>
       </c>
       <c r="F71" t="n">
-        <v>0.1403208826874792</v>
+        <v>0.27731108040711</v>
       </c>
     </row>
     <row r="72">
@@ -1888,13 +1864,13 @@
         <v>0</v>
       </c>
       <c r="D72" t="n">
-        <v>0.003713560465625775</v>
+        <v>0.005439250700404915</v>
       </c>
       <c r="E72" t="n">
-        <v>0.8476333938088463</v>
+        <v>0.7165134726904961</v>
       </c>
       <c r="F72" t="n">
-        <v>0.1486530457255278</v>
+        <v>0.2780472766090989</v>
       </c>
     </row>
     <row r="73">
@@ -1910,13 +1886,13 @@
         <v>0</v>
       </c>
       <c r="D73" t="n">
-        <v>0.9373667605099781</v>
+        <v>0.9457817687375221</v>
       </c>
       <c r="E73" t="n">
-        <v>0.001660263575088163</v>
+        <v>0.007162644503936604</v>
       </c>
       <c r="F73" t="n">
-        <v>0.06097297591493354</v>
+        <v>0.04705558675854146</v>
       </c>
     </row>
     <row r="74">
@@ -1932,13 +1908,13 @@
         <v>0</v>
       </c>
       <c r="D74" t="n">
-        <v>0.0001937317755229256</v>
+        <v>0.0002876055405284884</v>
       </c>
       <c r="E74" t="n">
-        <v>0.9132952285982988</v>
+        <v>0.8130466924084268</v>
       </c>
       <c r="F74" t="n">
-        <v>0.0865110396261783</v>
+        <v>0.1866657020510448</v>
       </c>
     </row>
     <row r="75">
@@ -1954,13 +1930,13 @@
         <v>0</v>
       </c>
       <c r="D75" t="n">
-        <v>0.9979422524357064</v>
+        <v>0.9984865808016532</v>
       </c>
       <c r="E75" t="n">
-        <v>2.953299747249403e-05</v>
+        <v>0.0001619984195814975</v>
       </c>
       <c r="F75" t="n">
-        <v>0.002028214566821061</v>
+        <v>0.001351420778765154</v>
       </c>
     </row>
     <row r="76">
@@ -1976,13 +1952,13 @@
         <v>0</v>
       </c>
       <c r="D76" t="n">
-        <v>0.0006456952010762668</v>
+        <v>0.0003054653713125799</v>
       </c>
       <c r="E76" t="n">
-        <v>0.7505381108874264</v>
+        <v>0.7838879045408672</v>
       </c>
       <c r="F76" t="n">
-        <v>0.2488161939114974</v>
+        <v>0.2158066300878203</v>
       </c>
     </row>
     <row r="77">
@@ -1998,13 +1974,13 @@
         <v>0</v>
       </c>
       <c r="D77" t="n">
-        <v>0.004426741616751683</v>
+        <v>0.005242822307192374</v>
       </c>
       <c r="E77" t="n">
-        <v>0.8193104789957325</v>
+        <v>0.6997029799393949</v>
       </c>
       <c r="F77" t="n">
-        <v>0.1762627793875157</v>
+        <v>0.2950541977534127</v>
       </c>
     </row>
     <row r="78">
@@ -2020,13 +1996,13 @@
         <v>0</v>
       </c>
       <c r="D78" t="n">
-        <v>0.7772444951454648</v>
+        <v>0.6010616279629724</v>
       </c>
       <c r="E78" t="n">
-        <v>0.01139369204458552</v>
+        <v>0.08549260105655891</v>
       </c>
       <c r="F78" t="n">
-        <v>0.2113618128099498</v>
+        <v>0.3134457709804687</v>
       </c>
     </row>
     <row r="79">
@@ -2058,13 +2034,13 @@
         <v>0</v>
       </c>
       <c r="D80" t="n">
-        <v>0.003517930746702923</v>
+        <v>0.004456917574095678</v>
       </c>
       <c r="E80" t="n">
-        <v>0.8522036843746639</v>
+        <v>0.7080235852858264</v>
       </c>
       <c r="F80" t="n">
-        <v>0.1442783848786331</v>
+        <v>0.2875194971400778</v>
       </c>
     </row>
     <row r="81">
@@ -2080,13 +2056,13 @@
         <v>0</v>
       </c>
       <c r="D81" t="n">
-        <v>0.0009337733786778985</v>
+        <v>0.001561938397351656</v>
       </c>
       <c r="E81" t="n">
-        <v>0.8766811712241706</v>
+        <v>0.7117291693348339</v>
       </c>
       <c r="F81" t="n">
-        <v>0.1223850553971517</v>
+        <v>0.2867088922678145</v>
       </c>
     </row>
     <row r="82">
@@ -2134,13 +2110,13 @@
         <v>0</v>
       </c>
       <c r="D84" t="n">
-        <v>0.001472929436446006</v>
+        <v>0.0012175708255841</v>
       </c>
       <c r="E84" t="n">
-        <v>0.8152451008245123</v>
+        <v>0.7548664984488747</v>
       </c>
       <c r="F84" t="n">
-        <v>0.1832819697390417</v>
+        <v>0.2439159307255413</v>
       </c>
     </row>
     <row r="85">
@@ -2156,13 +2132,13 @@
         <v>0</v>
       </c>
       <c r="D85" t="n">
-        <v>0.003060821216489918</v>
+        <v>0.004479624506333896</v>
       </c>
       <c r="E85" t="n">
-        <v>0.853871540695966</v>
+        <v>0.7149602907218178</v>
       </c>
       <c r="F85" t="n">
-        <v>0.143067638087544</v>
+        <v>0.2805600847718482</v>
       </c>
     </row>
     <row r="86">
@@ -2178,13 +2154,13 @@
         <v>0</v>
       </c>
       <c r="D86" t="n">
-        <v>0.000421307979369978</v>
+        <v>0.0002564594631069681</v>
       </c>
       <c r="E86" t="n">
-        <v>0.7715673493321499</v>
+        <v>0.7232681052812836</v>
       </c>
       <c r="F86" t="n">
-        <v>0.2280113426884801</v>
+        <v>0.2764754352556095</v>
       </c>
     </row>
     <row r="87">
@@ -2200,13 +2176,13 @@
         <v>0</v>
       </c>
       <c r="D87" t="n">
-        <v>0.05515574370145446</v>
+        <v>0.02563866988899983</v>
       </c>
       <c r="E87" t="n">
-        <v>0.617987572448749</v>
+        <v>0.6991915295648777</v>
       </c>
       <c r="F87" t="n">
-        <v>0.3268566838497964</v>
+        <v>0.2751698005461224</v>
       </c>
     </row>
     <row r="88">
@@ -2222,13 +2198,13 @@
         <v>0</v>
       </c>
       <c r="D88" t="n">
-        <v>0.004945117846483969</v>
+        <v>0.005742487844379996</v>
       </c>
       <c r="E88" t="n">
-        <v>0.8381302530711638</v>
+        <v>0.7172031081031892</v>
       </c>
       <c r="F88" t="n">
-        <v>0.1569246290823523</v>
+        <v>0.2770544040524309</v>
       </c>
     </row>
     <row r="89">
@@ -2244,13 +2220,13 @@
         <v>0</v>
       </c>
       <c r="D89" t="n">
-        <v>0.2331855651124553</v>
+        <v>0.2222106657781951</v>
       </c>
       <c r="E89" t="n">
-        <v>0.3519909906348873</v>
+        <v>0.3781507847196793</v>
       </c>
       <c r="F89" t="n">
-        <v>0.4148234442526574</v>
+        <v>0.3996385495021256</v>
       </c>
     </row>
     <row r="90">
@@ -2266,13 +2242,13 @@
         <v>0</v>
       </c>
       <c r="D90" t="n">
-        <v>0.0004750690565556648</v>
+        <v>0.0007066046473367104</v>
       </c>
       <c r="E90" t="n">
-        <v>0.8557782652030248</v>
+        <v>0.6790269300336879</v>
       </c>
       <c r="F90" t="n">
-        <v>0.1437466657404196</v>
+        <v>0.3202664653189753</v>
       </c>
     </row>
     <row r="91">
@@ -2282,19 +2258,19 @@
         </is>
       </c>
       <c r="B91" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C91" t="n">
         <v>0</v>
       </c>
       <c r="D91" t="n">
-        <v>0.01349642535602927</v>
+        <v>0.01210386891107713</v>
       </c>
       <c r="E91" t="n">
-        <v>0.5981582549964327</v>
+        <v>0.4393425371199008</v>
       </c>
       <c r="F91" t="n">
-        <v>0.3883453196475382</v>
+        <v>0.548553593969022</v>
       </c>
     </row>
     <row r="92">
@@ -2310,13 +2286,13 @@
         <v>0</v>
       </c>
       <c r="D92" t="n">
-        <v>0.0006727949649865781</v>
+        <v>0.0007292112691210329</v>
       </c>
       <c r="E92" t="n">
-        <v>0.8061233697291238</v>
+        <v>0.6455321469010049</v>
       </c>
       <c r="F92" t="n">
-        <v>0.1932038353058896</v>
+        <v>0.3537386418298741</v>
       </c>
     </row>
     <row r="93">
@@ -2332,13 +2308,13 @@
         <v>0</v>
       </c>
       <c r="D93" t="n">
-        <v>0.00101403861383066</v>
+        <v>0.0006238185439785032</v>
       </c>
       <c r="E93" t="n">
-        <v>0.6979009430942837</v>
+        <v>0.6412528853359752</v>
       </c>
       <c r="F93" t="n">
-        <v>0.3010850182918857</v>
+        <v>0.3581232961200462</v>
       </c>
     </row>
     <row r="94">
@@ -2386,13 +2362,13 @@
         <v>0</v>
       </c>
       <c r="D96" t="n">
-        <v>0.04413911539510598</v>
+        <v>0.0541327110882038</v>
       </c>
       <c r="E96" t="n">
-        <v>0.7120541700111769</v>
+        <v>0.641889427924991</v>
       </c>
       <c r="F96" t="n">
-        <v>0.2438067145937171</v>
+        <v>0.3039778609868051</v>
       </c>
     </row>
     <row r="97">
@@ -2408,13 +2384,13 @@
         <v>0</v>
       </c>
       <c r="D97" t="n">
-        <v>0.037179693335226</v>
+        <v>0.04920453936175027</v>
       </c>
       <c r="E97" t="n">
-        <v>0.678839677769554</v>
+        <v>0.5826193937725729</v>
       </c>
       <c r="F97" t="n">
-        <v>0.28398062889522</v>
+        <v>0.3681760668656768</v>
       </c>
     </row>
     <row r="98">
@@ -2430,13 +2406,13 @@
         <v>0</v>
       </c>
       <c r="D98" t="n">
-        <v>0.007793192301721256</v>
+        <v>0.0035981751801462</v>
       </c>
       <c r="E98" t="n">
-        <v>0.6182927995401172</v>
+        <v>0.6030068300259129</v>
       </c>
       <c r="F98" t="n">
-        <v>0.3739140081581617</v>
+        <v>0.393394994793941</v>
       </c>
     </row>
     <row r="99">
@@ -2452,13 +2428,13 @@
         <v>0</v>
       </c>
       <c r="D99" t="n">
-        <v>0.02514751171959442</v>
+        <v>0.02109210953442122</v>
       </c>
       <c r="E99" t="n">
-        <v>0.7483022208776379</v>
+        <v>0.720978615623573</v>
       </c>
       <c r="F99" t="n">
-        <v>0.2265502674027678</v>
+        <v>0.2579292748420057</v>
       </c>
     </row>
     <row r="100">
@@ -2471,17 +2447,11 @@
         <v>2</v>
       </c>
       <c r="C100" t="n">
-        <v>0</v>
-      </c>
-      <c r="D100" t="n">
-        <v>0.08544147363357721</v>
-      </c>
-      <c r="E100" t="n">
-        <v>0.5868283460139794</v>
-      </c>
-      <c r="F100" t="n">
-        <v>0.3277301803524433</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="D100" t="inlineStr"/>
+      <c r="E100" t="inlineStr"/>
+      <c r="F100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" s="1" t="inlineStr">
@@ -2496,13 +2466,13 @@
         <v>0</v>
       </c>
       <c r="D101" t="n">
-        <v>0.07468099432222131</v>
+        <v>0.06420066065082394</v>
       </c>
       <c r="E101" t="n">
-        <v>0.5565653316180164</v>
+        <v>0.616061800252762</v>
       </c>
       <c r="F101" t="n">
-        <v>0.3687536740597622</v>
+        <v>0.319737539096414</v>
       </c>
     </row>
     <row r="102">
@@ -2518,13 +2488,13 @@
         <v>0</v>
       </c>
       <c r="D102" t="n">
-        <v>0.001954041972127674</v>
+        <v>0.003070489889771696</v>
       </c>
       <c r="E102" t="n">
-        <v>0.8468037140799585</v>
+        <v>0.6620162081674001</v>
       </c>
       <c r="F102" t="n">
-        <v>0.151242243947914</v>
+        <v>0.3349133019428282</v>
       </c>
     </row>
     <row r="103">
@@ -2572,13 +2542,13 @@
         <v>0</v>
       </c>
       <c r="D105" t="n">
-        <v>0.004461907287384504</v>
+        <v>0.006513029511756216</v>
       </c>
       <c r="E105" t="n">
-        <v>0.7079364522288883</v>
+        <v>0.5936771424720676</v>
       </c>
       <c r="F105" t="n">
-        <v>0.2876016404837271</v>
+        <v>0.3998098280161762</v>
       </c>
     </row>
     <row r="106">
@@ -2594,13 +2564,13 @@
         <v>0</v>
       </c>
       <c r="D106" t="n">
-        <v>0.01119031268289366</v>
+        <v>0.01225102141739912</v>
       </c>
       <c r="E106" t="n">
-        <v>0.5998677708815472</v>
+        <v>0.5208367057431222</v>
       </c>
       <c r="F106" t="n">
-        <v>0.3889419164355592</v>
+        <v>0.4669122728394788</v>
       </c>
     </row>
     <row r="107">
@@ -2626,19 +2596,19 @@
         </is>
       </c>
       <c r="B108" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C108" t="n">
         <v>0</v>
       </c>
       <c r="D108" t="n">
-        <v>0.017109858366055</v>
+        <v>0.0118133116382031</v>
       </c>
       <c r="E108" t="n">
-        <v>0.5550572851856269</v>
+        <v>0.4755697492674225</v>
       </c>
       <c r="F108" t="n">
-        <v>0.4278328564483181</v>
+        <v>0.5126169390943744</v>
       </c>
     </row>
     <row r="109">
@@ -2654,13 +2624,13 @@
         <v>0</v>
       </c>
       <c r="D109" t="n">
-        <v>0.007329412109380988</v>
+        <v>0.01023253759466686</v>
       </c>
       <c r="E109" t="n">
-        <v>0.7723039889432153</v>
+        <v>0.6245673809128108</v>
       </c>
       <c r="F109" t="n">
-        <v>0.2203665989474038</v>
+        <v>0.3652000814925224</v>
       </c>
     </row>
     <row r="110">
@@ -2676,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="D110" t="n">
-        <v>0.01009970330900376</v>
+        <v>0.006063725469751265</v>
       </c>
       <c r="E110" t="n">
-        <v>0.6857423323208712</v>
+        <v>0.6237289470124288</v>
       </c>
       <c r="F110" t="n">
-        <v>0.304157964370125</v>
+        <v>0.37020732751782</v>
       </c>
     </row>
     <row r="111">
@@ -2692,19 +2662,19 @@
         </is>
       </c>
       <c r="B111" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C111" t="n">
         <v>0</v>
       </c>
       <c r="D111" t="n">
-        <v>0.2009366662283203</v>
+        <v>0.101747981755627</v>
       </c>
       <c r="E111" t="n">
-        <v>0.3685997683148823</v>
+        <v>0.5343690061694557</v>
       </c>
       <c r="F111" t="n">
-        <v>0.4304635654567974</v>
+        <v>0.3638830120749172</v>
       </c>
     </row>
     <row r="112">
@@ -2714,19 +2684,19 @@
         </is>
       </c>
       <c r="B112" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C112" t="n">
         <v>0</v>
       </c>
       <c r="D112" t="n">
-        <v>0.01232784534982507</v>
+        <v>0.005701805664541797</v>
       </c>
       <c r="E112" t="n">
-        <v>0.4859373573029658</v>
+        <v>0.5228739879686952</v>
       </c>
       <c r="F112" t="n">
-        <v>0.5017347973472092</v>
+        <v>0.471424206366763</v>
       </c>
     </row>
     <row r="113">
@@ -2742,13 +2712,13 @@
         <v>0</v>
       </c>
       <c r="D113" t="n">
-        <v>0.02132888138551817</v>
+        <v>0.01130203422796566</v>
       </c>
       <c r="E113" t="n">
-        <v>0.4006855635816408</v>
+        <v>0.4598698568707273</v>
       </c>
       <c r="F113" t="n">
-        <v>0.5779855550328411</v>
+        <v>0.528828108901307</v>
       </c>
     </row>
     <row r="114">
@@ -2764,13 +2734,13 @@
         <v>0</v>
       </c>
       <c r="D114" t="n">
-        <v>0.03635960641284908</v>
+        <v>0.02057852473530415</v>
       </c>
       <c r="E114" t="n">
-        <v>0.7138793483344235</v>
+        <v>0.7367741128251278</v>
       </c>
       <c r="F114" t="n">
-        <v>0.2497610452527275</v>
+        <v>0.2426473624395681</v>
       </c>
     </row>
     <row r="115">
@@ -2780,7 +2750,7 @@
         </is>
       </c>
       <c r="B115" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C115" t="n">
         <v>1</v>
@@ -2802,13 +2772,13 @@
         <v>0</v>
       </c>
       <c r="D116" t="n">
-        <v>0.03426322300592603</v>
+        <v>0.0163680081329358</v>
       </c>
       <c r="E116" t="n">
-        <v>0.6582207055116334</v>
+        <v>0.6962155233462303</v>
       </c>
       <c r="F116" t="n">
-        <v>0.3075160714824406</v>
+        <v>0.287416468520834</v>
       </c>
     </row>
     <row r="117">
@@ -2824,13 +2794,13 @@
         <v>0</v>
       </c>
       <c r="D117" t="n">
-        <v>0.009054925023791183</v>
+        <v>0.004095055011798962</v>
       </c>
       <c r="E117" t="n">
-        <v>0.6164126126747811</v>
+        <v>0.6356449222191967</v>
       </c>
       <c r="F117" t="n">
-        <v>0.3745324623014277</v>
+        <v>0.3602600227690043</v>
       </c>
     </row>
     <row r="118">
@@ -2846,13 +2816,13 @@
         <v>0</v>
       </c>
       <c r="D118" t="n">
-        <v>0.1386766637517812</v>
+        <v>0.03683985583460932</v>
       </c>
       <c r="E118" t="n">
-        <v>0.1822397012697827</v>
+        <v>0.4346460524293754</v>
       </c>
       <c r="F118" t="n">
-        <v>0.679083634978436</v>
+        <v>0.5285140917360153</v>
       </c>
     </row>
     <row r="119">
@@ -2868,13 +2838,13 @@
         <v>0</v>
       </c>
       <c r="D119" t="n">
-        <v>0.3534677607919418</v>
+        <v>0.1128523448790581</v>
       </c>
       <c r="E119" t="n">
-        <v>0.06880686480823173</v>
+        <v>0.2471448726854077</v>
       </c>
       <c r="F119" t="n">
-        <v>0.5777253743998265</v>
+        <v>0.6400027824355342</v>
       </c>
     </row>
     <row r="120">
@@ -2890,13 +2860,13 @@
         <v>0</v>
       </c>
       <c r="D120" t="n">
-        <v>0.0261835219605369</v>
+        <v>0.01487391903700042</v>
       </c>
       <c r="E120" t="n">
-        <v>0.5260433143925171</v>
+        <v>0.5135216159757228</v>
       </c>
       <c r="F120" t="n">
-        <v>0.447773163646946</v>
+        <v>0.4716044649872768</v>
       </c>
     </row>
     <row r="121">
@@ -2928,13 +2898,13 @@
         <v>0</v>
       </c>
       <c r="D122" t="n">
-        <v>0.05738052251069409</v>
+        <v>0.03780408442060543</v>
       </c>
       <c r="E122" t="n">
-        <v>0.5068665331696673</v>
+        <v>0.4847931146867933</v>
       </c>
       <c r="F122" t="n">
-        <v>0.4357529443196386</v>
+        <v>0.4774028008926013</v>
       </c>
     </row>
     <row r="123">
@@ -2966,13 +2936,13 @@
         <v>0</v>
       </c>
       <c r="D124" t="n">
-        <v>0.01046932634315787</v>
+        <v>0.005133123005743236</v>
       </c>
       <c r="E124" t="n">
-        <v>0.6118462954753516</v>
+        <v>0.6018588421409363</v>
       </c>
       <c r="F124" t="n">
-        <v>0.3776843781814906</v>
+        <v>0.3930080348533204</v>
       </c>
     </row>
     <row r="125">
@@ -2988,13 +2958,13 @@
         <v>0</v>
       </c>
       <c r="D125" t="n">
-        <v>0.04959069737542635</v>
+        <v>0.03169922928396272</v>
       </c>
       <c r="E125" t="n">
-        <v>0.5360215248114114</v>
+        <v>0.5312950839908714</v>
       </c>
       <c r="F125" t="n">
-        <v>0.4143877778131623</v>
+        <v>0.4370056867251658</v>
       </c>
     </row>
     <row r="126">
@@ -3004,19 +2974,19 @@
         </is>
       </c>
       <c r="B126" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C126" t="n">
         <v>0</v>
       </c>
       <c r="D126" t="n">
-        <v>0.07639526232872892</v>
+        <v>0.04883687407677096</v>
       </c>
       <c r="E126" t="n">
-        <v>0.4056270811631327</v>
+        <v>0.4770702623419099</v>
       </c>
       <c r="F126" t="n">
-        <v>0.5179776565081383</v>
+        <v>0.4740928635813192</v>
       </c>
     </row>
     <row r="127">
@@ -3032,13 +3002,13 @@
         <v>0</v>
       </c>
       <c r="D127" t="n">
-        <v>0.0704686726257223</v>
+        <v>0.03206416697654246</v>
       </c>
       <c r="E127" t="n">
-        <v>0.4896830247834821</v>
+        <v>0.6249397965861281</v>
       </c>
       <c r="F127" t="n">
-        <v>0.4398483025907955</v>
+        <v>0.3429960364373294</v>
       </c>
     </row>
     <row r="128">
@@ -3051,17 +3021,11 @@
         <v>2</v>
       </c>
       <c r="C128" t="n">
-        <v>0</v>
-      </c>
-      <c r="D128" t="n">
-        <v>0.007547569476446359</v>
-      </c>
-      <c r="E128" t="n">
-        <v>0.5636541213417336</v>
-      </c>
-      <c r="F128" t="n">
-        <v>0.4287983091818199</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="D128" t="inlineStr"/>
+      <c r="E128" t="inlineStr"/>
+      <c r="F128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" s="1" t="inlineStr">
@@ -3076,13 +3040,13 @@
         <v>0</v>
       </c>
       <c r="D129" t="n">
-        <v>2.656451561115725e-05</v>
+        <v>9.767107353208476e-06</v>
       </c>
       <c r="E129" t="n">
-        <v>0.7461466555043098</v>
+        <v>0.7474917826721202</v>
       </c>
       <c r="F129" t="n">
-        <v>0.2538267799800791</v>
+        <v>0.2524984502205264</v>
       </c>
     </row>
     <row r="130">
@@ -3092,19 +3056,19 @@
         </is>
       </c>
       <c r="B130" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C130" t="n">
         <v>0</v>
       </c>
       <c r="D130" t="n">
-        <v>0.1813217108826911</v>
+        <v>0.09877620206353643</v>
       </c>
       <c r="E130" t="n">
-        <v>0.3587377610328395</v>
+        <v>0.5139005807941567</v>
       </c>
       <c r="F130" t="n">
-        <v>0.4599405280844694</v>
+        <v>0.3873232171423069</v>
       </c>
     </row>
     <row r="131">
@@ -3120,13 +3084,13 @@
         <v>0</v>
       </c>
       <c r="D131" t="n">
-        <v>0.006630949336003108</v>
+        <v>0.003684699074020826</v>
       </c>
       <c r="E131" t="n">
-        <v>0.6295128969842961</v>
+        <v>0.5433186407907059</v>
       </c>
       <c r="F131" t="n">
-        <v>0.3638561536797008</v>
+        <v>0.4529966601352734</v>
       </c>
     </row>
     <row r="132">
@@ -3158,13 +3122,13 @@
         <v>0</v>
       </c>
       <c r="D133" t="n">
-        <v>0.01852633500098738</v>
+        <v>0.00958816741907819</v>
       </c>
       <c r="E133" t="n">
-        <v>0.5370097650144484</v>
+        <v>0.5444961258686151</v>
       </c>
       <c r="F133" t="n">
-        <v>0.4444638999845642</v>
+        <v>0.4459157067123067</v>
       </c>
     </row>
     <row r="134">
@@ -3180,13 +3144,13 @@
         <v>0</v>
       </c>
       <c r="D134" t="n">
-        <v>0.03813584636978355</v>
+        <v>0.02401468659799207</v>
       </c>
       <c r="E134" t="n">
-        <v>0.4518692596576767</v>
+        <v>0.4421555968914535</v>
       </c>
       <c r="F134" t="n">
-        <v>0.5099948939725398</v>
+        <v>0.5338297165105544</v>
       </c>
     </row>
     <row r="135">
@@ -3202,13 +3166,13 @@
         <v>0</v>
       </c>
       <c r="D135" t="n">
-        <v>0.01638538164065265</v>
+        <v>0.007825050498714486</v>
       </c>
       <c r="E135" t="n">
-        <v>0.6220030667384908</v>
+        <v>0.6434371175334682</v>
       </c>
       <c r="F135" t="n">
-        <v>0.3616115516208565</v>
+        <v>0.3487378319678172</v>
       </c>
     </row>
     <row r="136">
@@ -3224,13 +3188,13 @@
         <v>0</v>
       </c>
       <c r="D136" t="n">
-        <v>0.1073610704986105</v>
+        <v>0.02942152001896371</v>
       </c>
       <c r="E136" t="n">
-        <v>0.2370464961242249</v>
+        <v>0.4744526280555509</v>
       </c>
       <c r="F136" t="n">
-        <v>0.6555924333771647</v>
+        <v>0.4961258519254854</v>
       </c>
     </row>
     <row r="137">
@@ -3246,13 +3210,13 @@
         <v>0</v>
       </c>
       <c r="D137" t="n">
-        <v>0.00168521996727838</v>
+        <v>0.0006251374989475184</v>
       </c>
       <c r="E137" t="n">
-        <v>0.7364462247816231</v>
+        <v>0.7832883708472738</v>
       </c>
       <c r="F137" t="n">
-        <v>0.2618685552510984</v>
+        <v>0.2160864916537787</v>
       </c>
     </row>
     <row r="138">
@@ -3268,13 +3232,13 @@
         <v>0</v>
       </c>
       <c r="D138" t="n">
-        <v>0.7610126529839162</v>
+        <v>0.509115528178437</v>
       </c>
       <c r="E138" t="n">
-        <v>0.08667157496596688</v>
+        <v>0.363961121361396</v>
       </c>
       <c r="F138" t="n">
-        <v>0.1523157720501171</v>
+        <v>0.126923350460167</v>
       </c>
     </row>
     <row r="139">
@@ -3290,13 +3254,13 @@
         <v>0</v>
       </c>
       <c r="D139" t="n">
-        <v>0.09996008900250677</v>
+        <v>0.07355975122037242</v>
       </c>
       <c r="E139" t="n">
-        <v>0.2843382728449599</v>
+        <v>0.282574000700665</v>
       </c>
       <c r="F139" t="n">
-        <v>0.6157016381525332</v>
+        <v>0.6438662480789625</v>
       </c>
     </row>
     <row r="140">
@@ -3312,13 +3276,13 @@
         <v>0</v>
       </c>
       <c r="D140" t="n">
-        <v>0.1546123413688028</v>
+        <v>0.1640917491585634</v>
       </c>
       <c r="E140" t="n">
-        <v>0.3128320003584282</v>
+        <v>0.27765992831846</v>
       </c>
       <c r="F140" t="n">
-        <v>0.5325556582727691</v>
+        <v>0.5582483225229766</v>
       </c>
     </row>
     <row r="141">
@@ -3334,13 +3298,13 @@
         <v>0</v>
       </c>
       <c r="D141" t="n">
-        <v>0.003200982757005789</v>
+        <v>0.00178794002651481</v>
       </c>
       <c r="E141" t="n">
-        <v>0.6756115390245583</v>
+        <v>0.6396899698412746</v>
       </c>
       <c r="F141" t="n">
-        <v>0.3211874782184361</v>
+        <v>0.3585220901322105</v>
       </c>
     </row>
     <row r="142">
@@ -3356,13 +3320,13 @@
         <v>0</v>
       </c>
       <c r="D142" t="n">
-        <v>0.1453614930812844</v>
+        <v>0.06924378676850632</v>
       </c>
       <c r="E142" t="n">
-        <v>0.2831528022015239</v>
+        <v>0.402459235865563</v>
       </c>
       <c r="F142" t="n">
-        <v>0.5714857047171917</v>
+        <v>0.5282969773659307</v>
       </c>
     </row>
     <row r="143">
@@ -3372,19 +3336,19 @@
         </is>
       </c>
       <c r="B143" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C143" t="n">
         <v>0</v>
       </c>
       <c r="D143" t="n">
-        <v>0.02014885600539048</v>
+        <v>0.01967261730959972</v>
       </c>
       <c r="E143" t="n">
-        <v>0.5601862155444896</v>
+        <v>0.4144740002755156</v>
       </c>
       <c r="F143" t="n">
-        <v>0.4196649284501199</v>
+        <v>0.5658533824148847</v>
       </c>
     </row>
     <row r="144">
@@ -3394,19 +3358,19 @@
         </is>
       </c>
       <c r="B144" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C144" t="n">
         <v>0</v>
       </c>
       <c r="D144" t="n">
-        <v>0.002347588501780768</v>
+        <v>0.0005602416049171976</v>
       </c>
       <c r="E144" t="n">
-        <v>0.4368507673109371</v>
+        <v>0.5726306920679233</v>
       </c>
       <c r="F144" t="n">
-        <v>0.5608016441872821</v>
+        <v>0.4268090663271594</v>
       </c>
     </row>
     <row r="145">
@@ -3422,13 +3386,13 @@
         <v>0</v>
       </c>
       <c r="D145" t="n">
-        <v>0.001575111753479211</v>
+        <v>0.001443875555768597</v>
       </c>
       <c r="E145" t="n">
-        <v>0.7382233461054418</v>
+        <v>0.6207520476799472</v>
       </c>
       <c r="F145" t="n">
-        <v>0.2602015421410789</v>
+        <v>0.3778040767642843</v>
       </c>
     </row>
     <row r="146">
@@ -3444,13 +3408,13 @@
         <v>0</v>
       </c>
       <c r="D146" t="n">
-        <v>0.6207562063172936</v>
+        <v>0.6902705972099411</v>
       </c>
       <c r="E146" t="n">
-        <v>0.06229197920278094</v>
+        <v>0.04732322087535153</v>
       </c>
       <c r="F146" t="n">
-        <v>0.3169518144799254</v>
+        <v>0.2624061819147074</v>
       </c>
     </row>
     <row r="147">
@@ -3482,13 +3446,13 @@
         <v>0</v>
       </c>
       <c r="D148" t="n">
-        <v>0.003080033290151539</v>
+        <v>0.002626942250964396</v>
       </c>
       <c r="E148" t="n">
-        <v>0.70129150577899</v>
+        <v>0.5794849088860996</v>
       </c>
       <c r="F148" t="n">
-        <v>0.2956284609308585</v>
+        <v>0.4178881488629361</v>
       </c>
     </row>
     <row r="149">
@@ -3498,19 +3462,19 @@
         </is>
       </c>
       <c r="B149" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C149" t="n">
         <v>0</v>
       </c>
       <c r="D149" t="n">
-        <v>0.499697860136535</v>
+        <v>0.3708597040818889</v>
       </c>
       <c r="E149" t="n">
-        <v>0.1142098325609685</v>
+        <v>0.1971183133696527</v>
       </c>
       <c r="F149" t="n">
-        <v>0.3860923073024966</v>
+        <v>0.4320219825484583</v>
       </c>
     </row>
     <row r="150">
@@ -3526,13 +3490,13 @@
         <v>0</v>
       </c>
       <c r="D150" t="n">
-        <v>0.04478443532763883</v>
+        <v>0.02464552215254325</v>
       </c>
       <c r="E150" t="n">
-        <v>0.5329750453967689</v>
+        <v>0.5240951259622555</v>
       </c>
       <c r="F150" t="n">
-        <v>0.4222405192755921</v>
+        <v>0.4512593518852012</v>
       </c>
     </row>
     <row r="151">
@@ -3548,13 +3512,13 @@
         <v>0</v>
       </c>
       <c r="D151" t="n">
-        <v>0.0300945350595845</v>
+        <v>0.02197460151673028</v>
       </c>
       <c r="E151" t="n">
-        <v>0.5887961314081892</v>
+        <v>0.5400711879232767</v>
       </c>
       <c r="F151" t="n">
-        <v>0.3811093335322264</v>
+        <v>0.4379542105599931</v>
       </c>
     </row>
     <row r="152">
@@ -3570,13 +3534,13 @@
         <v>0</v>
       </c>
       <c r="D152" t="n">
-        <v>0.6425400271116903</v>
+        <v>0.6201985330379503</v>
       </c>
       <c r="E152" t="n">
-        <v>0.08536294445932772</v>
+        <v>0.1264297659182416</v>
       </c>
       <c r="F152" t="n">
-        <v>0.2720970284289819</v>
+        <v>0.2533717010438081</v>
       </c>
     </row>
     <row r="153">
@@ -3592,13 +3556,13 @@
         <v>0</v>
       </c>
       <c r="D153" t="n">
-        <v>0.2350110423401368</v>
+        <v>0.05927752566573501</v>
       </c>
       <c r="E153" t="n">
-        <v>0.4426177269143933</v>
+        <v>0.7906092535616842</v>
       </c>
       <c r="F153" t="n">
-        <v>0.3223712307454699</v>
+        <v>0.1501132207725807</v>
       </c>
     </row>
     <row r="154">
@@ -3614,13 +3578,13 @@
         <v>0</v>
       </c>
       <c r="D154" t="n">
-        <v>0.01140363566858881</v>
+        <v>0.008865439765162755</v>
       </c>
       <c r="E154" t="n">
-        <v>0.7157407347313233</v>
+        <v>0.6059929422467317</v>
       </c>
       <c r="F154" t="n">
-        <v>0.2728556296000879</v>
+        <v>0.3851416179881055</v>
       </c>
     </row>
     <row r="155">
@@ -3636,13 +3600,13 @@
         <v>0</v>
       </c>
       <c r="D155" t="n">
-        <v>0.8440823728914906</v>
+        <v>0.6895003305546978</v>
       </c>
       <c r="E155" t="n">
-        <v>0.04013292641835928</v>
+        <v>0.2011002120708265</v>
       </c>
       <c r="F155" t="n">
-        <v>0.1157847006901501</v>
+        <v>0.1093994573744756</v>
       </c>
     </row>
     <row r="156">
@@ -3652,19 +3616,19 @@
         </is>
       </c>
       <c r="B156" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C156" t="n">
         <v>0</v>
       </c>
       <c r="D156" t="n">
-        <v>0.1996581604329997</v>
+        <v>0.0455918682427106</v>
       </c>
       <c r="E156" t="n">
-        <v>0.397690615554577</v>
+        <v>0.7467821125219257</v>
       </c>
       <c r="F156" t="n">
-        <v>0.4026512240124234</v>
+        <v>0.2076260192353636</v>
       </c>
     </row>
     <row r="157">
@@ -3680,13 +3644,13 @@
         <v>0</v>
       </c>
       <c r="D157" t="n">
-        <v>0.6371673817085419</v>
+        <v>0.5788993729160854</v>
       </c>
       <c r="E157" t="n">
-        <v>0.06307319899373481</v>
+        <v>0.1023803033762263</v>
       </c>
       <c r="F157" t="n">
-        <v>0.2997594192977233</v>
+        <v>0.3187203237076884</v>
       </c>
     </row>
     <row r="158">
@@ -3702,13 +3666,13 @@
         <v>0</v>
       </c>
       <c r="D158" t="n">
-        <v>0.07841034271652349</v>
+        <v>0.03656027573275506</v>
       </c>
       <c r="E158" t="n">
-        <v>0.3225962598511843</v>
+        <v>0.4333479860766822</v>
       </c>
       <c r="F158" t="n">
-        <v>0.5989933974322922</v>
+        <v>0.5300917381905628</v>
       </c>
     </row>
     <row r="159">
@@ -3724,13 +3688,13 @@
         <v>0</v>
       </c>
       <c r="D159" t="n">
-        <v>0.3464273459842592</v>
+        <v>0.2237958242243156</v>
       </c>
       <c r="E159" t="n">
-        <v>0.1870114784333214</v>
+        <v>0.3130062343080082</v>
       </c>
       <c r="F159" t="n">
-        <v>0.4665611755824192</v>
+        <v>0.4631979414676762</v>
       </c>
     </row>
     <row r="160">
@@ -3740,19 +3704,19 @@
         </is>
       </c>
       <c r="B160" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C160" t="n">
         <v>0</v>
       </c>
       <c r="D160" t="n">
-        <v>0.4938530787239948</v>
+        <v>0.1762253330389614</v>
       </c>
       <c r="E160" t="n">
-        <v>0.2015876063664125</v>
+        <v>0.6415246782233009</v>
       </c>
       <c r="F160" t="n">
-        <v>0.3045593149095927</v>
+        <v>0.1822499887377377</v>
       </c>
     </row>
     <row r="161">
@@ -3768,13 +3732,13 @@
         <v>0</v>
       </c>
       <c r="D161" t="n">
-        <v>0.273011236418025</v>
+        <v>0.1798250666980026</v>
       </c>
       <c r="E161" t="n">
-        <v>0.2121316282872841</v>
+        <v>0.294323391126369</v>
       </c>
       <c r="F161" t="n">
-        <v>0.5148571352946908</v>
+        <v>0.5258515421756285</v>
       </c>
     </row>
     <row r="162">
@@ -3784,19 +3748,19 @@
         </is>
       </c>
       <c r="B162" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C162" t="n">
         <v>0</v>
       </c>
       <c r="D162" t="n">
-        <v>0.4461726645881601</v>
+        <v>0.1239159097427915</v>
       </c>
       <c r="E162" t="n">
-        <v>0.2304667860317678</v>
+        <v>0.7059853806373754</v>
       </c>
       <c r="F162" t="n">
-        <v>0.323360549380072</v>
+        <v>0.1700987096198331</v>
       </c>
     </row>
     <row r="163">
@@ -3812,13 +3776,13 @@
         <v>0</v>
       </c>
       <c r="D163" t="n">
-        <v>0.254738747967387</v>
+        <v>0.128947949894246</v>
       </c>
       <c r="E163" t="n">
-        <v>0.1969444137148463</v>
+        <v>0.3695396513349855</v>
       </c>
       <c r="F163" t="n">
-        <v>0.5483168383177667</v>
+        <v>0.5015123987707685</v>
       </c>
     </row>
     <row r="164">
@@ -3834,13 +3798,13 @@
         <v>0</v>
       </c>
       <c r="D164" t="n">
-        <v>0.5410609885382409</v>
+        <v>0.4847853320798295</v>
       </c>
       <c r="E164" t="n">
-        <v>0.1298831376038907</v>
+        <v>0.1980538790093002</v>
       </c>
       <c r="F164" t="n">
-        <v>0.3290558738578683</v>
+        <v>0.3171607889108704</v>
       </c>
     </row>
     <row r="165">
@@ -3856,13 +3820,13 @@
         <v>0</v>
       </c>
       <c r="D165" t="n">
-        <v>0.1259914995257977</v>
+        <v>0.1260650450469211</v>
       </c>
       <c r="E165" t="n">
-        <v>0.393726598595066</v>
+        <v>0.3316989560981368</v>
       </c>
       <c r="F165" t="n">
-        <v>0.4802819018791362</v>
+        <v>0.5422359988549422</v>
       </c>
     </row>
     <row r="166">
@@ -3878,13 +3842,13 @@
         <v>0</v>
       </c>
       <c r="D166" t="n">
-        <v>0.05622778593435797</v>
+        <v>0.02503696559645176</v>
       </c>
       <c r="E166" t="n">
-        <v>0.5315781428726407</v>
+        <v>0.5897858226885438</v>
       </c>
       <c r="F166" t="n">
-        <v>0.4121940711930013</v>
+        <v>0.3851772117150044</v>
       </c>
     </row>
     <row r="167">
@@ -3916,13 +3880,13 @@
         <v>0</v>
       </c>
       <c r="D168" t="n">
-        <v>0.0008481872676060497</v>
+        <v>0.003139944909731976</v>
       </c>
       <c r="E168" t="n">
-        <v>0.9476146178283404</v>
+        <v>0.79592530327851</v>
       </c>
       <c r="F168" t="n">
-        <v>0.05153719490405353</v>
+        <v>0.200934751811758</v>
       </c>
     </row>
     <row r="169">
@@ -3948,19 +3912,19 @@
         </is>
       </c>
       <c r="B170" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C170" t="n">
         <v>0</v>
       </c>
       <c r="D170" t="n">
-        <v>0.07055031561261225</v>
+        <v>0.03480532150946573</v>
       </c>
       <c r="E170" t="n">
-        <v>0.3684903578370553</v>
+        <v>0.4918437340742409</v>
       </c>
       <c r="F170" t="n">
-        <v>0.5609593265503324</v>
+        <v>0.4733509444162934</v>
       </c>
     </row>
     <row r="171">
@@ -3976,13 +3940,13 @@
         <v>0</v>
       </c>
       <c r="D171" t="n">
-        <v>0.002487315606783312</v>
+        <v>0.002018742498085715</v>
       </c>
       <c r="E171" t="n">
-        <v>0.7724971629992334</v>
+        <v>0.654273850372295</v>
       </c>
       <c r="F171" t="n">
-        <v>0.2250155213939832</v>
+        <v>0.3437074071296192</v>
       </c>
     </row>
     <row r="172">
@@ -4014,13 +3978,13 @@
         <v>0</v>
       </c>
       <c r="D173" t="n">
-        <v>0.000986216333533725</v>
+        <v>0.0009516612540138629</v>
       </c>
       <c r="E173" t="n">
-        <v>0.8543321003664373</v>
+        <v>0.706519633621997</v>
       </c>
       <c r="F173" t="n">
-        <v>0.144681683300029</v>
+        <v>0.292528705123989</v>
       </c>
     </row>
     <row r="174">
@@ -4036,13 +4000,13 @@
         <v>0</v>
       </c>
       <c r="D174" t="n">
-        <v>0.227443174069187</v>
+        <v>0.1193259956066753</v>
       </c>
       <c r="E174" t="n">
-        <v>0.2587506542650069</v>
+        <v>0.3945569809761895</v>
       </c>
       <c r="F174" t="n">
-        <v>0.5138061716658061</v>
+        <v>0.4861170234171352</v>
       </c>
     </row>
     <row r="175">
@@ -4052,20 +4016,14 @@
         </is>
       </c>
       <c r="B175" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C175" t="n">
-        <v>0</v>
-      </c>
-      <c r="D175" t="n">
-        <v>0.0247175964771955</v>
-      </c>
-      <c r="E175" t="n">
-        <v>0.5281640425894034</v>
-      </c>
-      <c r="F175" t="n">
-        <v>0.447118360933401</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="D175" t="inlineStr"/>
+      <c r="E175" t="inlineStr"/>
+      <c r="F175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" s="1" t="inlineStr">
@@ -4128,13 +4086,13 @@
         <v>0</v>
       </c>
       <c r="D179" t="n">
-        <v>0.4045437604360871</v>
+        <v>0.279853177604698</v>
       </c>
       <c r="E179" t="n">
-        <v>0.1652673077424817</v>
+        <v>0.2916165746323326</v>
       </c>
       <c r="F179" t="n">
-        <v>0.4301889318214313</v>
+        <v>0.4285302477629694</v>
       </c>
     </row>
     <row r="180">
@@ -4150,13 +4108,13 @@
         <v>0</v>
       </c>
       <c r="D180" t="n">
-        <v>0.717236701122497</v>
+        <v>0.7105372425055266</v>
       </c>
       <c r="E180" t="n">
-        <v>0.0381375027538521</v>
+        <v>0.05348750231082362</v>
       </c>
       <c r="F180" t="n">
-        <v>0.2446257961236509</v>
+        <v>0.2359752551836497</v>
       </c>
     </row>
     <row r="181">
@@ -4172,13 +4130,13 @@
         <v>0</v>
       </c>
       <c r="D181" t="n">
-        <v>0.8828401690935656</v>
+        <v>0.8920912981271465</v>
       </c>
       <c r="E181" t="n">
-        <v>0.01080327621178092</v>
+        <v>0.01489384997319195</v>
       </c>
       <c r="F181" t="n">
-        <v>0.1063565546946536</v>
+        <v>0.09301485189966149</v>
       </c>
     </row>
     <row r="182">
@@ -4194,13 +4152,13 @@
         <v>0</v>
       </c>
       <c r="D182" t="n">
-        <v>0.01117107576392818</v>
+        <v>0.005871503195385705</v>
       </c>
       <c r="E182" t="n">
-        <v>0.5228414449102613</v>
+        <v>0.4980622291385985</v>
       </c>
       <c r="F182" t="n">
-        <v>0.4659874793258105</v>
+        <v>0.4960662676660159</v>
       </c>
     </row>
     <row r="183">
@@ -4210,19 +4168,19 @@
         </is>
       </c>
       <c r="B183" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C183" t="n">
         <v>0</v>
       </c>
       <c r="D183" t="n">
-        <v>0.01526013037142062</v>
+        <v>0.009570610155345946</v>
       </c>
       <c r="E183" t="n">
-        <v>0.5557983574785378</v>
+        <v>0.4748241597499574</v>
       </c>
       <c r="F183" t="n">
-        <v>0.4289415121500414</v>
+        <v>0.5156052300946966</v>
       </c>
     </row>
     <row r="184">
@@ -4238,13 +4196,13 @@
         <v>0</v>
       </c>
       <c r="D184" t="n">
-        <v>0.9535308850957227</v>
+        <v>0.9572419375400542</v>
       </c>
       <c r="E184" t="n">
-        <v>0.001904217939270249</v>
+        <v>0.004628005795674433</v>
       </c>
       <c r="F184" t="n">
-        <v>0.04456489696500706</v>
+        <v>0.03813005666427149</v>
       </c>
     </row>
     <row r="185">
@@ -4260,13 +4218,13 @@
         <v>0</v>
       </c>
       <c r="D185" t="n">
-        <v>0.06452840969827892</v>
+        <v>0.04522009915667066</v>
       </c>
       <c r="E185" t="n">
-        <v>0.3794060730017616</v>
+        <v>0.3610605316636669</v>
       </c>
       <c r="F185" t="n">
-        <v>0.5560655172999595</v>
+        <v>0.5937193691796624</v>
       </c>
     </row>
     <row r="186">
@@ -4282,13 +4240,13 @@
         <v>0</v>
       </c>
       <c r="D186" t="n">
-        <v>0.0087667075182426</v>
+        <v>0.003771018911563155</v>
       </c>
       <c r="E186" t="n">
-        <v>0.4869545454992978</v>
+        <v>0.4509210662125389</v>
       </c>
       <c r="F186" t="n">
-        <v>0.5042787469824596</v>
+        <v>0.5453079148758979</v>
       </c>
     </row>
     <row r="187">
@@ -4304,13 +4262,13 @@
         <v>0</v>
       </c>
       <c r="D187" t="n">
-        <v>0.2965182674403469</v>
+        <v>0.2496142270949258</v>
       </c>
       <c r="E187" t="n">
-        <v>0.168528677948115</v>
+        <v>0.1906958198232022</v>
       </c>
       <c r="F187" t="n">
-        <v>0.5349530546115381</v>
+        <v>0.559689953081872</v>
       </c>
     </row>
     <row r="188">
@@ -4326,13 +4284,13 @@
         <v>0</v>
       </c>
       <c r="D188" t="n">
-        <v>0.5289110654023366</v>
+        <v>0.4224018155313388</v>
       </c>
       <c r="E188" t="n">
-        <v>0.09043758619603506</v>
+        <v>0.1652960733629105</v>
       </c>
       <c r="F188" t="n">
-        <v>0.3806513484016285</v>
+        <v>0.4123021111057508</v>
       </c>
     </row>
     <row r="189">
@@ -4348,13 +4306,13 @@
         <v>0</v>
       </c>
       <c r="D189" t="n">
-        <v>0.3521940403974115</v>
+        <v>0.3260461638385658</v>
       </c>
       <c r="E189" t="n">
-        <v>0.1513315400839532</v>
+        <v>0.17835728519124</v>
       </c>
       <c r="F189" t="n">
-        <v>0.4964744195186354</v>
+        <v>0.4955965509701942</v>
       </c>
     </row>
     <row r="190">
@@ -4370,13 +4328,13 @@
         <v>0</v>
       </c>
       <c r="D190" t="n">
-        <v>0.003517571689134916</v>
+        <v>0.00293421979415622</v>
       </c>
       <c r="E190" t="n">
-        <v>0.7647158899646065</v>
+        <v>0.649101293562858</v>
       </c>
       <c r="F190" t="n">
-        <v>0.2317665383462585</v>
+        <v>0.3479644866429858</v>
       </c>
     </row>
     <row r="191">
@@ -4392,13 +4350,13 @@
         <v>0</v>
       </c>
       <c r="D191" t="n">
-        <v>0.05060292212016287</v>
+        <v>0.02483337602375767</v>
       </c>
       <c r="E191" t="n">
-        <v>0.4323818097468305</v>
+        <v>0.4742409277942788</v>
       </c>
       <c r="F191" t="n">
-        <v>0.5170152681330066</v>
+        <v>0.5009256961819635</v>
       </c>
     </row>
     <row r="192">
@@ -4478,13 +4436,13 @@
         <v>0</v>
       </c>
       <c r="D196" t="n">
-        <v>0.1756041800846792</v>
+        <v>0.123113868758581</v>
       </c>
       <c r="E196" t="n">
-        <v>0.2860415046108905</v>
+        <v>0.3296858566761404</v>
       </c>
       <c r="F196" t="n">
-        <v>0.5383543153044302</v>
+        <v>0.5472002745652785</v>
       </c>
     </row>
     <row r="197">
@@ -4494,19 +4452,19 @@
         </is>
       </c>
       <c r="B197" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C197" t="n">
         <v>0</v>
       </c>
       <c r="D197" t="n">
-        <v>0.1036694316028374</v>
+        <v>0.07255065133789687</v>
       </c>
       <c r="E197" t="n">
-        <v>0.4277846405382809</v>
+        <v>0.4742483426525034</v>
       </c>
       <c r="F197" t="n">
-        <v>0.4685459278588817</v>
+        <v>0.4532010060095998</v>
       </c>
     </row>
     <row r="198">
@@ -4522,13 +4480,13 @@
         <v>0</v>
       </c>
       <c r="D198" t="n">
-        <v>0.1648682910011866</v>
+        <v>0.1534898680847904</v>
       </c>
       <c r="E198" t="n">
-        <v>0.287612297464109</v>
+        <v>0.2407065275021459</v>
       </c>
       <c r="F198" t="n">
-        <v>0.5475194115347044</v>
+        <v>0.6058036044130637</v>
       </c>
     </row>
     <row r="199">
@@ -4544,13 +4502,13 @@
         <v>0</v>
       </c>
       <c r="D199" t="n">
-        <v>0.5941043358519643</v>
+        <v>0.5806276195846464</v>
       </c>
       <c r="E199" t="n">
-        <v>0.08485805592929248</v>
+        <v>0.109791871275276</v>
       </c>
       <c r="F199" t="n">
-        <v>0.3210376082187432</v>
+        <v>0.3095805091400777</v>
       </c>
     </row>
     <row r="200">
@@ -4566,13 +4524,13 @@
         <v>0</v>
       </c>
       <c r="D200" t="n">
-        <v>0.555146273825237</v>
+        <v>0.5399254708913455</v>
       </c>
       <c r="E200" t="n">
-        <v>0.06398451216588388</v>
+        <v>0.0683120003780279</v>
       </c>
       <c r="F200" t="n">
-        <v>0.3808692140088792</v>
+        <v>0.3917625287306267</v>
       </c>
     </row>
     <row r="201">
@@ -4588,13 +4546,13 @@
         <v>0</v>
       </c>
       <c r="D201" t="n">
-        <v>0.09865385431037843</v>
+        <v>0.09180628850395912</v>
       </c>
       <c r="E201" t="n">
-        <v>0.364015934452712</v>
+        <v>0.2656104288581034</v>
       </c>
       <c r="F201" t="n">
-        <v>0.5373302112369095</v>
+        <v>0.6425832826379375</v>
       </c>
     </row>
     <row r="202">
@@ -4610,13 +4568,13 @@
         <v>0</v>
       </c>
       <c r="D202" t="n">
-        <v>0.1348008567680919</v>
+        <v>0.1309556879091091</v>
       </c>
       <c r="E202" t="n">
-        <v>0.3199834486507654</v>
+        <v>0.2514995290904372</v>
       </c>
       <c r="F202" t="n">
-        <v>0.5452156945811427</v>
+        <v>0.6175447830004538</v>
       </c>
     </row>
     <row r="203">
@@ -4632,13 +4590,13 @@
         <v>0</v>
       </c>
       <c r="D203" t="n">
-        <v>0.2895110058150241</v>
+        <v>0.254754980198042</v>
       </c>
       <c r="E203" t="n">
-        <v>0.2067485480755649</v>
+        <v>0.2456454710494092</v>
       </c>
       <c r="F203" t="n">
-        <v>0.503740446109411</v>
+        <v>0.4995995487525487</v>
       </c>
     </row>
     <row r="204">
@@ -4648,19 +4606,19 @@
         </is>
       </c>
       <c r="B204" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C204" t="n">
         <v>0</v>
       </c>
       <c r="D204" t="n">
-        <v>0.4464034177005252</v>
+        <v>0.3283012810952446</v>
       </c>
       <c r="E204" t="n">
-        <v>0.1541750337116524</v>
+        <v>0.295438737005695</v>
       </c>
       <c r="F204" t="n">
-        <v>0.3994215485878224</v>
+        <v>0.3762599818990604</v>
       </c>
     </row>
     <row r="205">
@@ -4670,19 +4628,19 @@
         </is>
       </c>
       <c r="B205" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C205" t="n">
         <v>0</v>
       </c>
       <c r="D205" t="n">
-        <v>0.7250264139805445</v>
+        <v>0.3864794264793991</v>
       </c>
       <c r="E205" t="n">
-        <v>0.07522575110987928</v>
+        <v>0.4410692092408022</v>
       </c>
       <c r="F205" t="n">
-        <v>0.1997478349095761</v>
+        <v>0.1724513642797987</v>
       </c>
     </row>
     <row r="206">
@@ -4714,13 +4672,13 @@
         <v>0</v>
       </c>
       <c r="D207" t="n">
-        <v>0.1411805175366424</v>
+        <v>0.06207717865421838</v>
       </c>
       <c r="E207" t="n">
-        <v>0.2059809288619374</v>
+        <v>0.3215279553442579</v>
       </c>
       <c r="F207" t="n">
-        <v>0.6528385536014202</v>
+        <v>0.6163948660015236</v>
       </c>
     </row>
     <row r="208">
@@ -4736,13 +4694,13 @@
         <v>0</v>
       </c>
       <c r="D208" t="n">
-        <v>0.07567596103377174</v>
+        <v>0.05352667283457474</v>
       </c>
       <c r="E208" t="n">
-        <v>0.3724212566043369</v>
+        <v>0.3279483437958965</v>
       </c>
       <c r="F208" t="n">
-        <v>0.5519027823618914</v>
+        <v>0.6185249833695287</v>
       </c>
     </row>
     <row r="209">
@@ -4758,13 +4716,13 @@
         <v>0</v>
       </c>
       <c r="D209" t="n">
-        <v>0.05948066933203202</v>
+        <v>0.03677345296803439</v>
       </c>
       <c r="E209" t="n">
-        <v>0.4321061113479939</v>
+        <v>0.4083225644743333</v>
       </c>
       <c r="F209" t="n">
-        <v>0.5084132193199742</v>
+        <v>0.5549039825576322</v>
       </c>
     </row>
     <row r="210">
@@ -4780,13 +4738,13 @@
         <v>0</v>
       </c>
       <c r="D210" t="n">
-        <v>0.04289911648253197</v>
+        <v>0.01559487605615839</v>
       </c>
       <c r="E210" t="n">
-        <v>0.3507570920745396</v>
+        <v>0.4086212037119415</v>
       </c>
       <c r="F210" t="n">
-        <v>0.6063437914429284</v>
+        <v>0.5757839202319002</v>
       </c>
     </row>
     <row r="211">
@@ -4834,13 +4792,13 @@
         <v>0</v>
       </c>
       <c r="D213" t="n">
-        <v>0.2248049613966576</v>
+        <v>0.172319158820116</v>
       </c>
       <c r="E213" t="n">
-        <v>0.2614188324547843</v>
+        <v>0.2936779368337709</v>
       </c>
       <c r="F213" t="n">
-        <v>0.5137762061485581</v>
+        <v>0.5340029043461131</v>
       </c>
     </row>
     <row r="214">
@@ -4856,13 +4814,13 @@
         <v>0</v>
       </c>
       <c r="D214" t="n">
-        <v>0.1058656176806251</v>
+        <v>0.09516382340193062</v>
       </c>
       <c r="E214" t="n">
-        <v>0.3715830592948106</v>
+        <v>0.3293585924733091</v>
       </c>
       <c r="F214" t="n">
-        <v>0.5225513230245644</v>
+        <v>0.5754775841247604</v>
       </c>
     </row>
     <row r="215">
@@ -4872,19 +4830,19 @@
         </is>
       </c>
       <c r="B215" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C215" t="n">
         <v>0</v>
       </c>
       <c r="D215" t="n">
-        <v>0.1834728685603598</v>
+        <v>0.1316815272174085</v>
       </c>
       <c r="E215" t="n">
-        <v>0.3779630857132855</v>
+        <v>0.4350689827766037</v>
       </c>
       <c r="F215" t="n">
-        <v>0.4385640457263547</v>
+        <v>0.4332494900059877</v>
       </c>
     </row>
     <row r="216">
@@ -4900,13 +4858,13 @@
         <v>0</v>
       </c>
       <c r="D216" t="n">
-        <v>0.07394659130145134</v>
+        <v>0.04417047380578389</v>
       </c>
       <c r="E216" t="n">
-        <v>0.4560735258577036</v>
+        <v>0.4544321248001296</v>
       </c>
       <c r="F216" t="n">
-        <v>0.4699798828408451</v>
+        <v>0.5013974013940865</v>
       </c>
     </row>
     <row r="217">
@@ -4922,13 +4880,13 @@
         <v>0</v>
       </c>
       <c r="D217" t="n">
-        <v>0.3436766564368302</v>
+        <v>0.3097169289180479</v>
       </c>
       <c r="E217" t="n">
-        <v>0.2275922067897609</v>
+        <v>0.2835265379368562</v>
       </c>
       <c r="F217" t="n">
-        <v>0.428731136773409</v>
+        <v>0.4067565331450959</v>
       </c>
     </row>
     <row r="218">
@@ -4960,13 +4918,13 @@
         <v>0</v>
       </c>
       <c r="D219" t="n">
-        <v>0.08923069849161919</v>
+        <v>0.05580392040463149</v>
       </c>
       <c r="E219" t="n">
-        <v>0.4999152927219606</v>
+        <v>0.5312923306076103</v>
       </c>
       <c r="F219" t="n">
-        <v>0.4108540087864203</v>
+        <v>0.4129037489877583</v>
       </c>
     </row>
     <row r="220">
@@ -4982,13 +4940,13 @@
         <v>0</v>
       </c>
       <c r="D220" t="n">
-        <v>0.9956302148490278</v>
+        <v>0.9954723721375416</v>
       </c>
       <c r="E220" t="n">
-        <v>0.0002990940680518239</v>
+        <v>0.002042051227056875</v>
       </c>
       <c r="F220" t="n">
-        <v>0.004070691082920168</v>
+        <v>0.002485576635401477</v>
       </c>
     </row>
     <row r="221">
@@ -5004,13 +4962,13 @@
         <v>0</v>
       </c>
       <c r="D221" t="n">
-        <v>0.009522812520092355</v>
+        <v>0.00343008240876631</v>
       </c>
       <c r="E221" t="n">
-        <v>0.6302043099276413</v>
+        <v>0.7655356573029193</v>
       </c>
       <c r="F221" t="n">
-        <v>0.3602728775522663</v>
+        <v>0.2310342602883145</v>
       </c>
     </row>
     <row r="222">
@@ -5026,13 +4984,13 @@
         <v>0</v>
       </c>
       <c r="D222" t="n">
-        <v>0.1304542695115113</v>
+        <v>0.09946998478892784</v>
       </c>
       <c r="E222" t="n">
-        <v>0.3440801724551458</v>
+        <v>0.4149510132024654</v>
       </c>
       <c r="F222" t="n">
-        <v>0.5254655580333427</v>
+        <v>0.4855790020086068</v>
       </c>
     </row>
     <row r="223">
@@ -5048,13 +5006,13 @@
         <v>0</v>
       </c>
       <c r="D223" t="n">
-        <v>0.9840091875713424</v>
+        <v>0.9819913837691001</v>
       </c>
       <c r="E223" t="n">
-        <v>0.001612269344236684</v>
+        <v>0.008782867979931204</v>
       </c>
       <c r="F223" t="n">
-        <v>0.01437854308442102</v>
+        <v>0.0092257482509687</v>
       </c>
     </row>
     <row r="224">
@@ -5064,19 +5022,19 @@
         </is>
       </c>
       <c r="B224" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C224" t="n">
         <v>0</v>
       </c>
       <c r="D224" t="n">
-        <v>0.4372521059302321</v>
+        <v>0.4416936287134857</v>
       </c>
       <c r="E224" t="n">
-        <v>0.116587642227976</v>
+        <v>0.1547448631958188</v>
       </c>
       <c r="F224" t="n">
-        <v>0.4461602518417921</v>
+        <v>0.4035615080906955</v>
       </c>
     </row>
     <row r="225">
@@ -5092,13 +5050,13 @@
         <v>0</v>
       </c>
       <c r="D225" t="n">
-        <v>0.4854797209656839</v>
+        <v>0.414853408047691</v>
       </c>
       <c r="E225" t="n">
-        <v>0.1320105982795221</v>
+        <v>0.1772738153453089</v>
       </c>
       <c r="F225" t="n">
-        <v>0.382509680754794</v>
+        <v>0.4078727766069999</v>
       </c>
     </row>
     <row r="226">
@@ -5114,13 +5072,13 @@
         <v>0</v>
       </c>
       <c r="D226" t="n">
-        <v>0.965772120594963</v>
+        <v>0.9484666617649317</v>
       </c>
       <c r="E226" t="n">
-        <v>0.005176164652450653</v>
+        <v>0.0281205161394814</v>
       </c>
       <c r="F226" t="n">
-        <v>0.02905171475258631</v>
+        <v>0.02341282209558683</v>
       </c>
     </row>
     <row r="227">
@@ -5136,13 +5094,13 @@
         <v>0</v>
       </c>
       <c r="D227" t="n">
-        <v>0.03136113591462697</v>
+        <v>0.01044217263402622</v>
       </c>
       <c r="E227" t="n">
-        <v>0.5936788660430745</v>
+        <v>0.7506160995853948</v>
       </c>
       <c r="F227" t="n">
-        <v>0.3749599980422985</v>
+        <v>0.238941727780579</v>
       </c>
     </row>
     <row r="228">
@@ -5158,13 +5116,13 @@
         <v>0</v>
       </c>
       <c r="D228" t="n">
-        <v>0.008306403693971343</v>
+        <v>0.003662964625538209</v>
       </c>
       <c r="E228" t="n">
-        <v>0.6236771600090636</v>
+        <v>0.6860584903595133</v>
       </c>
       <c r="F228" t="n">
-        <v>0.3680164362969651</v>
+        <v>0.3102785450149484</v>
       </c>
     </row>
     <row r="229">
@@ -5180,13 +5138,13 @@
         <v>0</v>
       </c>
       <c r="D229" t="n">
-        <v>0.4350472644245099</v>
+        <v>0.5742012291793078</v>
       </c>
       <c r="E229" t="n">
-        <v>0.3982592637919208</v>
+        <v>0.3239448931577482</v>
       </c>
       <c r="F229" t="n">
-        <v>0.1666934717835693</v>
+        <v>0.101853877662944</v>
       </c>
     </row>
     <row r="230">
@@ -5202,13 +5160,13 @@
         <v>0</v>
       </c>
       <c r="D230" t="n">
-        <v>0.04590013778616962</v>
+        <v>0.02058740129726125</v>
       </c>
       <c r="E230" t="n">
-        <v>0.5053325588562928</v>
+        <v>0.5219976911744317</v>
       </c>
       <c r="F230" t="n">
-        <v>0.4487673033575376</v>
+        <v>0.457414907528307</v>
       </c>
     </row>
     <row r="231">
@@ -5224,13 +5182,13 @@
         <v>0</v>
       </c>
       <c r="D231" t="n">
-        <v>0.02577256915155296</v>
+        <v>0.01713956608524491</v>
       </c>
       <c r="E231" t="n">
-        <v>0.6309567324599212</v>
+        <v>0.5762813616300242</v>
       </c>
       <c r="F231" t="n">
-        <v>0.3432706983885258</v>
+        <v>0.4065790722847308</v>
       </c>
     </row>
     <row r="232">
@@ -5246,13 +5204,13 @@
         <v>0</v>
       </c>
       <c r="D232" t="n">
-        <v>0.001050112384966405</v>
+        <v>0.0004803012858747151</v>
       </c>
       <c r="E232" t="n">
-        <v>0.6688563763979569</v>
+        <v>0.6578613847542459</v>
       </c>
       <c r="F232" t="n">
-        <v>0.3300935112170766</v>
+        <v>0.3416583139598794</v>
       </c>
     </row>
     <row r="233">
@@ -5262,19 +5220,19 @@
         </is>
       </c>
       <c r="B233" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C233" t="n">
         <v>0</v>
       </c>
       <c r="D233" t="n">
-        <v>0.4109092643076966</v>
+        <v>0.09796870015785934</v>
       </c>
       <c r="E233" t="n">
-        <v>0.2306484750923641</v>
+        <v>0.7027683460094356</v>
       </c>
       <c r="F233" t="n">
-        <v>0.3584422605999393</v>
+        <v>0.199262953832705</v>
       </c>
     </row>
     <row r="234">
@@ -5290,13 +5248,13 @@
         <v>0</v>
       </c>
       <c r="D234" t="n">
-        <v>0.003746664117054082</v>
+        <v>0.001728152126272874</v>
       </c>
       <c r="E234" t="n">
-        <v>0.6195954099350666</v>
+        <v>0.5412364765813809</v>
       </c>
       <c r="F234" t="n">
-        <v>0.3766579259478792</v>
+        <v>0.4570353712923463</v>
       </c>
     </row>
     <row r="235">
@@ -5312,13 +5270,13 @@
         <v>0</v>
       </c>
       <c r="D235" t="n">
-        <v>0.001663788090578917</v>
+        <v>0.0009763702093701143</v>
       </c>
       <c r="E235" t="n">
-        <v>0.7361664249162621</v>
+        <v>0.6304542705380582</v>
       </c>
       <c r="F235" t="n">
-        <v>0.262169786993159</v>
+        <v>0.3685693592525715</v>
       </c>
     </row>
     <row r="236">
@@ -5334,13 +5292,13 @@
         <v>0</v>
       </c>
       <c r="D236" t="n">
-        <v>0.05136000199127977</v>
+        <v>0.04035020288634447</v>
       </c>
       <c r="E236" t="n">
-        <v>0.5223840515946563</v>
+        <v>0.5024775873355821</v>
       </c>
       <c r="F236" t="n">
-        <v>0.426255946414064</v>
+        <v>0.4571722097780735</v>
       </c>
     </row>
     <row r="237">
@@ -5356,13 +5314,13 @@
         <v>0</v>
       </c>
       <c r="D237" t="n">
-        <v>0.0004315603200621002</v>
+        <v>0.0004702247280142451</v>
       </c>
       <c r="E237" t="n">
-        <v>0.832235800143206</v>
+        <v>0.6260409157102886</v>
       </c>
       <c r="F237" t="n">
-        <v>0.1673326395367318</v>
+        <v>0.3734888595616971</v>
       </c>
     </row>
   </sheetData>

--- a/results/02_taxa_assemblage/Wards_LDA/classifier_prediction/artifacts/02_predicted_data.xlsx
+++ b/results/02_taxa_assemblage/Wards_LDA/classifier_prediction/artifacts/02_predicted_data.xlsx
@@ -453,7 +453,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F237"/>
+  <dimension ref="A1:E237"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,7 +466,6 @@
       <c r="C1" s="1" t="n"/>
       <c r="D1" s="1" t="n"/>
       <c r="E1" s="1" t="n"/>
-      <c r="F1" s="1" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr"/>
@@ -478,7 +477,6 @@
       <c r="C2" s="1" t="n"/>
       <c r="D2" s="1" t="n"/>
       <c r="E2" s="1" t="n"/>
-      <c r="F2" s="1" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr"/>
@@ -502,11 +500,6 @@
           <t>Prob_Cluster 2</t>
         </is>
       </c>
-      <c r="F3" s="1" t="inlineStr">
-        <is>
-          <t>Prob_Cluster 3</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -528,13 +521,10 @@
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>0.51760718215146</v>
+        <v>0.5291468892144217</v>
       </c>
       <c r="E5" t="n">
-        <v>0.270569278467964</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0.211823539380576</v>
+        <v>0.4708531107855783</v>
       </c>
     </row>
     <row r="6">
@@ -544,14 +534,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C6" t="n">
         <v>1</v>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
@@ -566,13 +555,10 @@
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>0.01205447541208351</v>
+        <v>0.04348490384636483</v>
       </c>
       <c r="E7" t="n">
-        <v>0.7630811594907506</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0.2248643650971658</v>
+        <v>0.9565150961536352</v>
       </c>
     </row>
     <row r="8">
@@ -582,19 +568,16 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>0.2957601831399553</v>
+        <v>0.2353438514779373</v>
       </c>
       <c r="E8" t="n">
-        <v>0.2173601465793611</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0.4868796702806837</v>
+        <v>0.7646561485220627</v>
       </c>
     </row>
     <row r="9">
@@ -604,19 +587,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C9" t="n">
         <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>0.2745911152028067</v>
+        <v>0.5417270132381565</v>
       </c>
       <c r="E9" t="n">
-        <v>0.3925257286788821</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0.3328831561183114</v>
+        <v>0.4582729867618435</v>
       </c>
     </row>
     <row r="10">
@@ -632,13 +612,10 @@
         <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>0.0990141124486832</v>
+        <v>0.1827556355542379</v>
       </c>
       <c r="E10" t="n">
-        <v>0.5617069783939286</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0.3392789091573882</v>
+        <v>0.8172443644457621</v>
       </c>
     </row>
     <row r="11">
@@ -655,7 +632,6 @@
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
@@ -664,14 +640,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C12" t="n">
         <v>1</v>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
@@ -680,19 +655,16 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
         <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>0.0319993610748143</v>
+        <v>0.1071116155030736</v>
       </c>
       <c r="E13" t="n">
-        <v>0.4101117860007872</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0.5578888529243985</v>
+        <v>0.8928883844969264</v>
       </c>
     </row>
     <row r="14">
@@ -708,13 +680,10 @@
         <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>0.008733585107928842</v>
+        <v>0.03477477060407608</v>
       </c>
       <c r="E14" t="n">
-        <v>0.5180251731637969</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0.4732412417282741</v>
+        <v>0.9652252293959239</v>
       </c>
     </row>
     <row r="15">
@@ -730,13 +699,10 @@
         <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>0.7251528545309688</v>
+        <v>0.6768785921372942</v>
       </c>
       <c r="E15" t="n">
-        <v>0.05746029120438521</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0.217386854264646</v>
+        <v>0.3231214078627058</v>
       </c>
     </row>
     <row r="16">
@@ -746,19 +712,16 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C16" t="n">
         <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>0.4413922742866587</v>
+        <v>0.4597407274628499</v>
       </c>
       <c r="E16" t="n">
-        <v>0.2016528575176822</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0.356954868195659</v>
+        <v>0.5402592725371501</v>
       </c>
     </row>
     <row r="17">
@@ -771,11 +734,14 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>1</v>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0.01745685426471877</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.9825431457352812</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
@@ -784,19 +750,16 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C18" t="n">
         <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0401239432812983</v>
+        <v>0.08458138701714968</v>
       </c>
       <c r="E18" t="n">
-        <v>0.4188914347322743</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0.5409846219864274</v>
+        <v>0.9154186129828503</v>
       </c>
     </row>
     <row r="19">
@@ -809,11 +772,14 @@
         <v>1</v>
       </c>
       <c r="C19" t="n">
-        <v>1</v>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0.8597346692236427</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.1402653307763573</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
@@ -822,14 +788,17 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C20" t="n">
-        <v>1</v>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0.040106701362985</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.959893298637015</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
@@ -844,13 +813,10 @@
         <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>0.9878496765578777</v>
+        <v>0.9535884131702312</v>
       </c>
       <c r="E21" t="n">
-        <v>0.003249901162520438</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0.008900422279601953</v>
+        <v>0.04641158682976875</v>
       </c>
     </row>
     <row r="22">
@@ -866,13 +832,10 @@
         <v>0</v>
       </c>
       <c r="D22" t="n">
-        <v>0.9213121660080671</v>
+        <v>0.7598055663438654</v>
       </c>
       <c r="E22" t="n">
-        <v>0.01429801130649069</v>
-      </c>
-      <c r="F22" t="n">
-        <v>0.06438982268544222</v>
+        <v>0.2401944336561346</v>
       </c>
     </row>
     <row r="23">
@@ -888,13 +851,10 @@
         <v>0</v>
       </c>
       <c r="D23" t="n">
-        <v>0.002743775169934348</v>
+        <v>0.00825952044767253</v>
       </c>
       <c r="E23" t="n">
-        <v>0.7376466831505993</v>
-      </c>
-      <c r="F23" t="n">
-        <v>0.2596095416794664</v>
+        <v>0.9917404795523275</v>
       </c>
     </row>
     <row r="24">
@@ -904,19 +864,16 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C24" t="n">
         <v>0</v>
       </c>
       <c r="D24" t="n">
-        <v>0.2295818063910634</v>
+        <v>0.2619877295358899</v>
       </c>
       <c r="E24" t="n">
-        <v>0.1858265172719191</v>
-      </c>
-      <c r="F24" t="n">
-        <v>0.5845916763370175</v>
+        <v>0.7380122704641101</v>
       </c>
     </row>
     <row r="25">
@@ -926,14 +883,17 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C25" t="n">
-        <v>1</v>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr"/>
-      <c r="F25" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="D25" t="n">
+        <v>0.001473222077032044</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.998526777922968</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
@@ -949,7 +909,6 @@
       </c>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr"/>
-      <c r="F26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
@@ -964,13 +923,10 @@
         <v>0</v>
       </c>
       <c r="D27" t="n">
-        <v>0.9388267025705126</v>
+        <v>0.7646046287397673</v>
       </c>
       <c r="E27" t="n">
-        <v>0.01136631813651446</v>
-      </c>
-      <c r="F27" t="n">
-        <v>0.04980697929297302</v>
+        <v>0.2353953712602327</v>
       </c>
     </row>
     <row r="28">
@@ -986,13 +942,10 @@
         <v>0</v>
       </c>
       <c r="D28" t="n">
-        <v>0.9410405014249446</v>
+        <v>0.8864274640186438</v>
       </c>
       <c r="E28" t="n">
-        <v>0.01631651261576264</v>
-      </c>
-      <c r="F28" t="n">
-        <v>0.04264298595929285</v>
+        <v>0.1135725359813562</v>
       </c>
     </row>
     <row r="29">
@@ -1009,7 +962,6 @@
       </c>
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr"/>
-      <c r="F29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
@@ -1024,13 +976,10 @@
         <v>0</v>
       </c>
       <c r="D30" t="n">
-        <v>0.9417354351954883</v>
+        <v>0.8747323121534849</v>
       </c>
       <c r="E30" t="n">
-        <v>0.03172292099372133</v>
-      </c>
-      <c r="F30" t="n">
-        <v>0.02654164381079019</v>
+        <v>0.1252676878465151</v>
       </c>
     </row>
     <row r="31">
@@ -1040,14 +989,13 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C31" t="n">
         <v>1</v>
       </c>
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr"/>
-      <c r="F31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
@@ -1062,13 +1010,10 @@
         <v>0</v>
       </c>
       <c r="D32" t="n">
-        <v>0.003861373224362521</v>
+        <v>0.02372979571816303</v>
       </c>
       <c r="E32" t="n">
-        <v>0.8785168966340402</v>
-      </c>
-      <c r="F32" t="n">
-        <v>0.1176217301415973</v>
+        <v>0.976270204281837</v>
       </c>
     </row>
     <row r="33">
@@ -1085,7 +1030,6 @@
       </c>
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr"/>
-      <c r="F33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
@@ -1094,14 +1038,13 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C34" t="n">
         <v>1</v>
       </c>
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr"/>
-      <c r="F34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
@@ -1116,13 +1059,10 @@
         <v>0</v>
       </c>
       <c r="D35" t="n">
-        <v>0.9771977699468267</v>
+        <v>0.9358345701505542</v>
       </c>
       <c r="E35" t="n">
-        <v>0.002168328390848127</v>
-      </c>
-      <c r="F35" t="n">
-        <v>0.02063390166232512</v>
+        <v>0.06416542984944586</v>
       </c>
     </row>
     <row r="36">
@@ -1138,13 +1078,10 @@
         <v>0</v>
       </c>
       <c r="D36" t="n">
-        <v>2.018390554521627e-05</v>
+        <v>0.0001978980120255214</v>
       </c>
       <c r="E36" t="n">
-        <v>0.8132118164833861</v>
-      </c>
-      <c r="F36" t="n">
-        <v>0.1867679996110687</v>
+        <v>0.9998021019879745</v>
       </c>
     </row>
     <row r="37">
@@ -1161,7 +1098,6 @@
       </c>
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr"/>
-      <c r="F37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
@@ -1176,13 +1112,10 @@
         <v>0</v>
       </c>
       <c r="D38" t="n">
-        <v>0.006736128010350644</v>
+        <v>0.01992074491959084</v>
       </c>
       <c r="E38" t="n">
-        <v>0.7012943514301159</v>
-      </c>
-      <c r="F38" t="n">
-        <v>0.2919695205595335</v>
+        <v>0.9800792550804092</v>
       </c>
     </row>
     <row r="39">
@@ -1198,13 +1131,10 @@
         <v>0</v>
       </c>
       <c r="D39" t="n">
-        <v>0.0006952220104134867</v>
+        <v>0.003399813435439047</v>
       </c>
       <c r="E39" t="n">
-        <v>0.7263532194860757</v>
-      </c>
-      <c r="F39" t="n">
-        <v>0.2729515585035108</v>
+        <v>0.996600186564561</v>
       </c>
     </row>
     <row r="40">
@@ -1220,13 +1150,10 @@
         <v>0</v>
       </c>
       <c r="D40" t="n">
-        <v>0.9199809212131519</v>
+        <v>0.7290790368985778</v>
       </c>
       <c r="E40" t="n">
-        <v>0.03463984145188473</v>
-      </c>
-      <c r="F40" t="n">
-        <v>0.04537923733496327</v>
+        <v>0.2709209631014222</v>
       </c>
     </row>
     <row r="41">
@@ -1242,13 +1169,10 @@
         <v>0</v>
       </c>
       <c r="D41" t="n">
-        <v>0.9771998057738691</v>
+        <v>0.9374718426438814</v>
       </c>
       <c r="E41" t="n">
-        <v>0.00423688586012302</v>
-      </c>
-      <c r="F41" t="n">
-        <v>0.01856330836600769</v>
+        <v>0.06252815735611861</v>
       </c>
     </row>
     <row r="42">
@@ -1264,13 +1188,10 @@
         <v>0</v>
       </c>
       <c r="D42" t="n">
-        <v>0.9470819149406635</v>
+        <v>0.8453457007907309</v>
       </c>
       <c r="E42" t="n">
-        <v>0.01822606349598558</v>
-      </c>
-      <c r="F42" t="n">
-        <v>0.03469202156335079</v>
+        <v>0.1546542992092691</v>
       </c>
     </row>
     <row r="43">
@@ -1286,13 +1207,10 @@
         <v>0</v>
       </c>
       <c r="D43" t="n">
-        <v>0.01680180313173195</v>
+        <v>0.05524534806865977</v>
       </c>
       <c r="E43" t="n">
-        <v>0.6892190166138521</v>
-      </c>
-      <c r="F43" t="n">
-        <v>0.2939791802544161</v>
+        <v>0.9447546519313402</v>
       </c>
     </row>
     <row r="44">
@@ -1308,13 +1226,10 @@
         <v>0</v>
       </c>
       <c r="D44" t="n">
-        <v>0.06856906041966575</v>
+        <v>0.04566337570724799</v>
       </c>
       <c r="E44" t="n">
-        <v>0.5362681667619854</v>
-      </c>
-      <c r="F44" t="n">
-        <v>0.3951627728183489</v>
+        <v>0.954336624292752</v>
       </c>
     </row>
     <row r="45">
@@ -1330,13 +1245,10 @@
         <v>0</v>
       </c>
       <c r="D45" t="n">
-        <v>0.9870382327589612</v>
+        <v>0.9686579233521502</v>
       </c>
       <c r="E45" t="n">
-        <v>0.004177451504566892</v>
-      </c>
-      <c r="F45" t="n">
-        <v>0.00878431573647191</v>
+        <v>0.03134207664784988</v>
       </c>
     </row>
     <row r="46">
@@ -1352,13 +1264,10 @@
         <v>0</v>
       </c>
       <c r="D46" t="n">
-        <v>0.9400714051852146</v>
+        <v>0.8466055093634658</v>
       </c>
       <c r="E46" t="n">
-        <v>0.01973907836299353</v>
-      </c>
-      <c r="F46" t="n">
-        <v>0.04018951645179198</v>
+        <v>0.1533944906365342</v>
       </c>
     </row>
     <row r="47">
@@ -1375,7 +1284,6 @@
       </c>
       <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr"/>
-      <c r="F47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
@@ -1390,13 +1298,10 @@
         <v>0</v>
       </c>
       <c r="D48" t="n">
-        <v>0.001277982838205052</v>
+        <v>0.003949493952930316</v>
       </c>
       <c r="E48" t="n">
-        <v>0.6304141844466782</v>
-      </c>
-      <c r="F48" t="n">
-        <v>0.3683078327151166</v>
+        <v>0.9960505060470697</v>
       </c>
     </row>
     <row r="49">
@@ -1413,7 +1318,6 @@
       </c>
       <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr"/>
-      <c r="F49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
@@ -1422,14 +1326,13 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C50" t="n">
         <v>1</v>
       </c>
       <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr"/>
-      <c r="F50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
@@ -1445,7 +1348,6 @@
       </c>
       <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr"/>
-      <c r="F51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
@@ -1454,14 +1356,13 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C52" t="n">
         <v>1</v>
       </c>
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr"/>
-      <c r="F52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
@@ -1476,13 +1377,10 @@
         <v>0</v>
       </c>
       <c r="D53" t="n">
-        <v>0.0005650555776374082</v>
+        <v>0.002934651000632948</v>
       </c>
       <c r="E53" t="n">
-        <v>0.657205074825814</v>
-      </c>
-      <c r="F53" t="n">
-        <v>0.3422298695965486</v>
+        <v>0.9970653489993671</v>
       </c>
     </row>
     <row r="54">
@@ -1492,14 +1390,13 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C54" t="n">
         <v>1</v>
       </c>
       <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr"/>
-      <c r="F54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
@@ -1514,13 +1411,10 @@
         <v>0</v>
       </c>
       <c r="D55" t="n">
-        <v>0.001379453550286939</v>
+        <v>0.009860570034319505</v>
       </c>
       <c r="E55" t="n">
-        <v>0.5123257163830953</v>
-      </c>
-      <c r="F55" t="n">
-        <v>0.4862948300666177</v>
+        <v>0.9901394299656805</v>
       </c>
     </row>
     <row r="56">
@@ -1536,13 +1430,10 @@
         <v>0</v>
       </c>
       <c r="D56" t="n">
-        <v>0.0004303362114403517</v>
+        <v>0.002554532359199446</v>
       </c>
       <c r="E56" t="n">
-        <v>0.6523883766612497</v>
-      </c>
-      <c r="F56" t="n">
-        <v>0.3471812871273099</v>
+        <v>0.9974454676408006</v>
       </c>
     </row>
     <row r="57">
@@ -1559,7 +1450,6 @@
       </c>
       <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr"/>
-      <c r="F57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
@@ -1568,19 +1458,16 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C58" t="n">
         <v>0</v>
       </c>
       <c r="D58" t="n">
-        <v>0.02277492402061991</v>
+        <v>0.1008328831025137</v>
       </c>
       <c r="E58" t="n">
-        <v>0.4569434779542193</v>
-      </c>
-      <c r="F58" t="n">
-        <v>0.5202815980251607</v>
+        <v>0.8991671168974863</v>
       </c>
     </row>
     <row r="59">
@@ -1597,7 +1484,6 @@
       </c>
       <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr"/>
-      <c r="F59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
@@ -1612,13 +1498,10 @@
         <v>0</v>
       </c>
       <c r="D60" t="n">
-        <v>0.002551967998334427</v>
+        <v>0.01824827992643874</v>
       </c>
       <c r="E60" t="n">
-        <v>0.5622767254260966</v>
-      </c>
-      <c r="F60" t="n">
-        <v>0.435171306575569</v>
+        <v>0.9817517200735613</v>
       </c>
     </row>
     <row r="61">
@@ -1628,19 +1511,16 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C61" t="n">
         <v>0</v>
       </c>
       <c r="D61" t="n">
-        <v>0.2590018031436786</v>
+        <v>0.3326153087013833</v>
       </c>
       <c r="E61" t="n">
-        <v>0.2639232148504566</v>
-      </c>
-      <c r="F61" t="n">
-        <v>0.4770749820058647</v>
+        <v>0.6673846912986167</v>
       </c>
     </row>
     <row r="62">
@@ -1650,19 +1530,16 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C62" t="n">
         <v>0</v>
       </c>
       <c r="D62" t="n">
-        <v>0.003547875739042587</v>
+        <v>0.02057009168174728</v>
       </c>
       <c r="E62" t="n">
-        <v>0.4716707165681738</v>
-      </c>
-      <c r="F62" t="n">
-        <v>0.5247814076927837</v>
+        <v>0.9794299083182527</v>
       </c>
     </row>
     <row r="63">
@@ -1679,7 +1556,6 @@
       </c>
       <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr"/>
-      <c r="F63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
@@ -1691,11 +1567,14 @@
         <v>2</v>
       </c>
       <c r="C64" t="n">
-        <v>1</v>
-      </c>
-      <c r="D64" t="inlineStr"/>
-      <c r="E64" t="inlineStr"/>
-      <c r="F64" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="D64" t="n">
+        <v>0.08087662139040463</v>
+      </c>
+      <c r="E64" t="n">
+        <v>0.9191233786095954</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
@@ -1710,13 +1589,10 @@
         <v>0</v>
       </c>
       <c r="D65" t="n">
-        <v>3.740174611572507e-05</v>
+        <v>0.0003135736281658641</v>
       </c>
       <c r="E65" t="n">
-        <v>0.7946256443967609</v>
-      </c>
-      <c r="F65" t="n">
-        <v>0.2053369538571236</v>
+        <v>0.9996864263718341</v>
       </c>
     </row>
     <row r="66">
@@ -1732,13 +1608,10 @@
         <v>0</v>
       </c>
       <c r="D66" t="n">
-        <v>0.0001415472376838121</v>
+        <v>0.0006864518936575692</v>
       </c>
       <c r="E66" t="n">
-        <v>0.8300981944824123</v>
-      </c>
-      <c r="F66" t="n">
-        <v>0.169760258279904</v>
+        <v>0.9993135481063424</v>
       </c>
     </row>
     <row r="67">
@@ -1748,19 +1621,16 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C67" t="n">
         <v>0</v>
       </c>
       <c r="D67" t="n">
-        <v>0.01832052828428277</v>
+        <v>0.1021551555032782</v>
       </c>
       <c r="E67" t="n">
-        <v>0.4525336264835466</v>
-      </c>
-      <c r="F67" t="n">
-        <v>0.5291458452321707</v>
+        <v>0.8978448444967218</v>
       </c>
     </row>
     <row r="68">
@@ -1776,13 +1646,10 @@
         <v>0</v>
       </c>
       <c r="D68" t="n">
-        <v>0.0003734287157181768</v>
+        <v>0.001613030044245289</v>
       </c>
       <c r="E68" t="n">
-        <v>0.7619131370860295</v>
-      </c>
-      <c r="F68" t="n">
-        <v>0.2377134341982523</v>
+        <v>0.9983869699557547</v>
       </c>
     </row>
     <row r="69">
@@ -1798,13 +1665,10 @@
         <v>0</v>
       </c>
       <c r="D69" t="n">
-        <v>0.9113361485153372</v>
+        <v>0.8185485479711493</v>
       </c>
       <c r="E69" t="n">
-        <v>0.03816412775606925</v>
-      </c>
-      <c r="F69" t="n">
-        <v>0.05049972372859366</v>
+        <v>0.1814514520288507</v>
       </c>
     </row>
     <row r="70">
@@ -1820,13 +1684,10 @@
         <v>0</v>
       </c>
       <c r="D70" t="n">
-        <v>0.0008678898627406816</v>
+        <v>0.003770381795894506</v>
       </c>
       <c r="E70" t="n">
-        <v>0.77906733942798</v>
-      </c>
-      <c r="F70" t="n">
-        <v>0.2200647707092793</v>
+        <v>0.9962296182041055</v>
       </c>
     </row>
     <row r="71">
@@ -1842,13 +1703,10 @@
         <v>0</v>
       </c>
       <c r="D71" t="n">
-        <v>0.00487850122599108</v>
+        <v>0.01378123968892264</v>
       </c>
       <c r="E71" t="n">
-        <v>0.717810418366899</v>
-      </c>
-      <c r="F71" t="n">
-        <v>0.27731108040711</v>
+        <v>0.9862187603110774</v>
       </c>
     </row>
     <row r="72">
@@ -1864,13 +1722,10 @@
         <v>0</v>
       </c>
       <c r="D72" t="n">
-        <v>0.005439250700404915</v>
+        <v>0.01555407007949616</v>
       </c>
       <c r="E72" t="n">
-        <v>0.7165134726904961</v>
-      </c>
-      <c r="F72" t="n">
-        <v>0.2780472766090989</v>
+        <v>0.9844459299205038</v>
       </c>
     </row>
     <row r="73">
@@ -1886,13 +1741,10 @@
         <v>0</v>
       </c>
       <c r="D73" t="n">
-        <v>0.9457817687375221</v>
+        <v>0.9532846967357801</v>
       </c>
       <c r="E73" t="n">
-        <v>0.007162644503936604</v>
-      </c>
-      <c r="F73" t="n">
-        <v>0.04705558675854146</v>
+        <v>0.04671530326421988</v>
       </c>
     </row>
     <row r="74">
@@ -1908,13 +1760,10 @@
         <v>0</v>
       </c>
       <c r="D74" t="n">
-        <v>0.0002876055405284884</v>
+        <v>0.001824529495160765</v>
       </c>
       <c r="E74" t="n">
-        <v>0.8130466924084268</v>
-      </c>
-      <c r="F74" t="n">
-        <v>0.1866657020510448</v>
+        <v>0.9981754705048392</v>
       </c>
     </row>
     <row r="75">
@@ -1930,13 +1779,10 @@
         <v>0</v>
       </c>
       <c r="D75" t="n">
-        <v>0.9984865808016532</v>
+        <v>0.997677533585198</v>
       </c>
       <c r="E75" t="n">
-        <v>0.0001619984195814975</v>
-      </c>
-      <c r="F75" t="n">
-        <v>0.001351420778765154</v>
+        <v>0.002322466414802042</v>
       </c>
     </row>
     <row r="76">
@@ -1952,13 +1798,10 @@
         <v>0</v>
       </c>
       <c r="D76" t="n">
-        <v>0.0003054653713125799</v>
+        <v>0.003294265723723822</v>
       </c>
       <c r="E76" t="n">
-        <v>0.7838879045408672</v>
-      </c>
-      <c r="F76" t="n">
-        <v>0.2158066300878203</v>
+        <v>0.9967057342762762</v>
       </c>
     </row>
     <row r="77">
@@ -1974,13 +1817,10 @@
         <v>0</v>
       </c>
       <c r="D77" t="n">
-        <v>0.005242822307192374</v>
+        <v>0.01606825201869411</v>
       </c>
       <c r="E77" t="n">
-        <v>0.6997029799393949</v>
-      </c>
-      <c r="F77" t="n">
-        <v>0.2950541977534127</v>
+        <v>0.9839317479813059</v>
       </c>
     </row>
     <row r="78">
@@ -1996,13 +1836,10 @@
         <v>0</v>
       </c>
       <c r="D78" t="n">
-        <v>0.6010616279629724</v>
+        <v>0.8257656601241825</v>
       </c>
       <c r="E78" t="n">
-        <v>0.08549260105655891</v>
-      </c>
-      <c r="F78" t="n">
-        <v>0.3134457709804687</v>
+        <v>0.1742343398758174</v>
       </c>
     </row>
     <row r="79">
@@ -2015,11 +1852,14 @@
         <v>1</v>
       </c>
       <c r="C79" t="n">
-        <v>1</v>
-      </c>
-      <c r="D79" t="inlineStr"/>
-      <c r="E79" t="inlineStr"/>
-      <c r="F79" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="D79" t="n">
+        <v>0.9554298002281537</v>
+      </c>
+      <c r="E79" t="n">
+        <v>0.04457019977184624</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
@@ -2034,13 +1874,10 @@
         <v>0</v>
       </c>
       <c r="D80" t="n">
-        <v>0.004456917574095678</v>
+        <v>0.01415919378288011</v>
       </c>
       <c r="E80" t="n">
-        <v>0.7080235852858264</v>
-      </c>
-      <c r="F80" t="n">
-        <v>0.2875194971400778</v>
+        <v>0.9858408062171199</v>
       </c>
     </row>
     <row r="81">
@@ -2056,13 +1893,10 @@
         <v>0</v>
       </c>
       <c r="D81" t="n">
-        <v>0.001561938397351656</v>
+        <v>0.005246676303495512</v>
       </c>
       <c r="E81" t="n">
-        <v>0.7117291693348339</v>
-      </c>
-      <c r="F81" t="n">
-        <v>0.2867088922678145</v>
+        <v>0.9947533236965045</v>
       </c>
     </row>
     <row r="82">
@@ -2072,14 +1906,17 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C82" t="n">
-        <v>1</v>
-      </c>
-      <c r="D82" t="inlineStr"/>
-      <c r="E82" t="inlineStr"/>
-      <c r="F82" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="D82" t="n">
+        <v>0.08290823501792666</v>
+      </c>
+      <c r="E82" t="n">
+        <v>0.9170917649820733</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
@@ -2088,14 +1925,13 @@
         </is>
       </c>
       <c r="B83" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C83" t="n">
         <v>1</v>
       </c>
       <c r="D83" t="inlineStr"/>
       <c r="E83" t="inlineStr"/>
-      <c r="F83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
@@ -2110,13 +1946,10 @@
         <v>0</v>
       </c>
       <c r="D84" t="n">
-        <v>0.0012175708255841</v>
+        <v>0.006937054649514551</v>
       </c>
       <c r="E84" t="n">
-        <v>0.7548664984488747</v>
-      </c>
-      <c r="F84" t="n">
-        <v>0.2439159307255413</v>
+        <v>0.9930629453504854</v>
       </c>
     </row>
     <row r="85">
@@ -2132,13 +1965,10 @@
         <v>0</v>
       </c>
       <c r="D85" t="n">
-        <v>0.004479624506333896</v>
+        <v>0.01301157212554682</v>
       </c>
       <c r="E85" t="n">
-        <v>0.7149602907218178</v>
-      </c>
-      <c r="F85" t="n">
-        <v>0.2805600847718482</v>
+        <v>0.9869884278744532</v>
       </c>
     </row>
     <row r="86">
@@ -2154,13 +1984,10 @@
         <v>0</v>
       </c>
       <c r="D86" t="n">
-        <v>0.0002564594631069681</v>
+        <v>0.002275570250511616</v>
       </c>
       <c r="E86" t="n">
-        <v>0.7232681052812836</v>
-      </c>
-      <c r="F86" t="n">
-        <v>0.2764754352556095</v>
+        <v>0.9977244297494884</v>
       </c>
     </row>
     <row r="87">
@@ -2176,13 +2003,10 @@
         <v>0</v>
       </c>
       <c r="D87" t="n">
-        <v>0.02563866988899983</v>
+        <v>0.1008914828552911</v>
       </c>
       <c r="E87" t="n">
-        <v>0.6991915295648777</v>
-      </c>
-      <c r="F87" t="n">
-        <v>0.2751698005461224</v>
+        <v>0.8991085171447089</v>
       </c>
     </row>
     <row r="88">
@@ -2198,13 +2022,10 @@
         <v>0</v>
       </c>
       <c r="D88" t="n">
-        <v>0.005742487844379996</v>
+        <v>0.01873661816682148</v>
       </c>
       <c r="E88" t="n">
-        <v>0.7172031081031892</v>
-      </c>
-      <c r="F88" t="n">
-        <v>0.2770544040524309</v>
+        <v>0.9812633818331785</v>
       </c>
     </row>
     <row r="89">
@@ -2214,19 +2035,16 @@
         </is>
       </c>
       <c r="B89" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C89" t="n">
         <v>0</v>
       </c>
       <c r="D89" t="n">
-        <v>0.2222106657781951</v>
+        <v>0.2461221647758375</v>
       </c>
       <c r="E89" t="n">
-        <v>0.3781507847196793</v>
-      </c>
-      <c r="F89" t="n">
-        <v>0.3996385495021256</v>
+        <v>0.7538778352241625</v>
       </c>
     </row>
     <row r="90">
@@ -2242,13 +2060,10 @@
         <v>0</v>
       </c>
       <c r="D90" t="n">
-        <v>0.0007066046473367104</v>
+        <v>0.002486056229118794</v>
       </c>
       <c r="E90" t="n">
-        <v>0.6790269300336879</v>
-      </c>
-      <c r="F90" t="n">
-        <v>0.3202664653189753</v>
+        <v>0.9975139437708812</v>
       </c>
     </row>
     <row r="91">
@@ -2258,19 +2073,16 @@
         </is>
       </c>
       <c r="B91" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C91" t="n">
         <v>0</v>
       </c>
       <c r="D91" t="n">
-        <v>0.01210386891107713</v>
+        <v>0.02568475510121226</v>
       </c>
       <c r="E91" t="n">
-        <v>0.4393425371199008</v>
-      </c>
-      <c r="F91" t="n">
-        <v>0.548553593969022</v>
+        <v>0.9743152448987877</v>
       </c>
     </row>
     <row r="92">
@@ -2286,13 +2098,10 @@
         <v>0</v>
       </c>
       <c r="D92" t="n">
-        <v>0.0007292112691210329</v>
+        <v>0.00293726212330836</v>
       </c>
       <c r="E92" t="n">
-        <v>0.6455321469010049</v>
-      </c>
-      <c r="F92" t="n">
-        <v>0.3537386418298741</v>
+        <v>0.9970627378766916</v>
       </c>
     </row>
     <row r="93">
@@ -2308,13 +2117,10 @@
         <v>0</v>
       </c>
       <c r="D93" t="n">
-        <v>0.0006238185439785032</v>
+        <v>0.003578051442975405</v>
       </c>
       <c r="E93" t="n">
-        <v>0.6412528853359752</v>
-      </c>
-      <c r="F93" t="n">
-        <v>0.3581232961200462</v>
+        <v>0.9964219485570246</v>
       </c>
     </row>
     <row r="94">
@@ -2331,7 +2137,6 @@
       </c>
       <c r="D94" t="inlineStr"/>
       <c r="E94" t="inlineStr"/>
-      <c r="F94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" s="1" t="inlineStr">
@@ -2347,7 +2152,6 @@
       </c>
       <c r="D95" t="inlineStr"/>
       <c r="E95" t="inlineStr"/>
-      <c r="F95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" s="1" t="inlineStr">
@@ -2362,13 +2166,10 @@
         <v>0</v>
       </c>
       <c r="D96" t="n">
-        <v>0.0541327110882038</v>
+        <v>0.07670366579812915</v>
       </c>
       <c r="E96" t="n">
-        <v>0.641889427924991</v>
-      </c>
-      <c r="F96" t="n">
-        <v>0.3039778609868051</v>
+        <v>0.9232963342018708</v>
       </c>
     </row>
     <row r="97">
@@ -2384,13 +2185,10 @@
         <v>0</v>
       </c>
       <c r="D97" t="n">
-        <v>0.04920453936175027</v>
+        <v>0.06304655650179036</v>
       </c>
       <c r="E97" t="n">
-        <v>0.5826193937725729</v>
-      </c>
-      <c r="F97" t="n">
-        <v>0.3681760668656768</v>
+        <v>0.9369534434982096</v>
       </c>
     </row>
     <row r="98">
@@ -2406,13 +2204,10 @@
         <v>0</v>
       </c>
       <c r="D98" t="n">
-        <v>0.0035981751801462</v>
+        <v>0.01831410249616494</v>
       </c>
       <c r="E98" t="n">
-        <v>0.6030068300259129</v>
-      </c>
-      <c r="F98" t="n">
-        <v>0.393394994793941</v>
+        <v>0.9816858975038351</v>
       </c>
     </row>
     <row r="99">
@@ -2428,13 +2223,10 @@
         <v>0</v>
       </c>
       <c r="D99" t="n">
-        <v>0.02109210953442122</v>
+        <v>0.05338274848233426</v>
       </c>
       <c r="E99" t="n">
-        <v>0.720978615623573</v>
-      </c>
-      <c r="F99" t="n">
-        <v>0.2579292748420057</v>
+        <v>0.9466172515176657</v>
       </c>
     </row>
     <row r="100">
@@ -2447,11 +2239,14 @@
         <v>2</v>
       </c>
       <c r="C100" t="n">
-        <v>1</v>
-      </c>
-      <c r="D100" t="inlineStr"/>
-      <c r="E100" t="inlineStr"/>
-      <c r="F100" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="D100" t="n">
+        <v>0.1225608813146007</v>
+      </c>
+      <c r="E100" t="n">
+        <v>0.8774391186853993</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="1" t="inlineStr">
@@ -2466,13 +2261,10 @@
         <v>0</v>
       </c>
       <c r="D101" t="n">
-        <v>0.06420066065082394</v>
+        <v>0.1071091691640724</v>
       </c>
       <c r="E101" t="n">
-        <v>0.616061800252762</v>
-      </c>
-      <c r="F101" t="n">
-        <v>0.319737539096414</v>
+        <v>0.8928908308359276</v>
       </c>
     </row>
     <row r="102">
@@ -2488,13 +2280,10 @@
         <v>0</v>
       </c>
       <c r="D102" t="n">
-        <v>0.003070489889771696</v>
+        <v>0.007638243562572589</v>
       </c>
       <c r="E102" t="n">
-        <v>0.6620162081674001</v>
-      </c>
-      <c r="F102" t="n">
-        <v>0.3349133019428282</v>
+        <v>0.9923617564374274</v>
       </c>
     </row>
     <row r="103">
@@ -2511,7 +2300,6 @@
       </c>
       <c r="D103" t="inlineStr"/>
       <c r="E103" t="inlineStr"/>
-      <c r="F103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" s="1" t="inlineStr">
@@ -2527,7 +2315,6 @@
       </c>
       <c r="D104" t="inlineStr"/>
       <c r="E104" t="inlineStr"/>
-      <c r="F104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" s="1" t="inlineStr">
@@ -2542,13 +2329,10 @@
         <v>0</v>
       </c>
       <c r="D105" t="n">
-        <v>0.006513029511756216</v>
+        <v>0.01287939055314336</v>
       </c>
       <c r="E105" t="n">
-        <v>0.5936771424720676</v>
-      </c>
-      <c r="F105" t="n">
-        <v>0.3998098280161762</v>
+        <v>0.9871206094468566</v>
       </c>
     </row>
     <row r="106">
@@ -2564,13 +2348,10 @@
         <v>0</v>
       </c>
       <c r="D106" t="n">
-        <v>0.01225102141739912</v>
+        <v>0.02541185824521397</v>
       </c>
       <c r="E106" t="n">
-        <v>0.5208367057431222</v>
-      </c>
-      <c r="F106" t="n">
-        <v>0.4669122728394788</v>
+        <v>0.974588141754786</v>
       </c>
     </row>
     <row r="107">
@@ -2587,7 +2368,6 @@
       </c>
       <c r="D107" t="inlineStr"/>
       <c r="E107" t="inlineStr"/>
-      <c r="F107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" s="1" t="inlineStr">
@@ -2596,19 +2376,16 @@
         </is>
       </c>
       <c r="B108" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C108" t="n">
         <v>0</v>
       </c>
       <c r="D108" t="n">
-        <v>0.0118133116382031</v>
+        <v>0.03459609166201405</v>
       </c>
       <c r="E108" t="n">
-        <v>0.4755697492674225</v>
-      </c>
-      <c r="F108" t="n">
-        <v>0.5126169390943744</v>
+        <v>0.9654039083379859</v>
       </c>
     </row>
     <row r="109">
@@ -2624,13 +2401,10 @@
         <v>0</v>
       </c>
       <c r="D109" t="n">
-        <v>0.01023253759466686</v>
+        <v>0.02032461960574949</v>
       </c>
       <c r="E109" t="n">
-        <v>0.6245673809128108</v>
-      </c>
-      <c r="F109" t="n">
-        <v>0.3652000814925224</v>
+        <v>0.9796753803942505</v>
       </c>
     </row>
     <row r="110">
@@ -2646,13 +2420,10 @@
         <v>0</v>
       </c>
       <c r="D110" t="n">
-        <v>0.006063725469751265</v>
+        <v>0.02369829975793303</v>
       </c>
       <c r="E110" t="n">
-        <v>0.6237289470124288</v>
-      </c>
-      <c r="F110" t="n">
-        <v>0.37020732751782</v>
+        <v>0.976301700242067</v>
       </c>
     </row>
     <row r="111">
@@ -2668,13 +2439,10 @@
         <v>0</v>
       </c>
       <c r="D111" t="n">
-        <v>0.101747981755627</v>
+        <v>0.2391949643933278</v>
       </c>
       <c r="E111" t="n">
-        <v>0.5343690061694557</v>
-      </c>
-      <c r="F111" t="n">
-        <v>0.3638830120749172</v>
+        <v>0.7608050356066722</v>
       </c>
     </row>
     <row r="112">
@@ -2690,13 +2458,10 @@
         <v>0</v>
       </c>
       <c r="D112" t="n">
-        <v>0.005701805664541797</v>
+        <v>0.02588158688855668</v>
       </c>
       <c r="E112" t="n">
-        <v>0.5228739879686952</v>
-      </c>
-      <c r="F112" t="n">
-        <v>0.471424206366763</v>
+        <v>0.9741184131114433</v>
       </c>
     </row>
     <row r="113">
@@ -2706,19 +2471,16 @@
         </is>
       </c>
       <c r="B113" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C113" t="n">
         <v>0</v>
       </c>
       <c r="D113" t="n">
-        <v>0.01130203422796566</v>
+        <v>0.03968254913441116</v>
       </c>
       <c r="E113" t="n">
-        <v>0.4598698568707273</v>
-      </c>
-      <c r="F113" t="n">
-        <v>0.528828108901307</v>
+        <v>0.9603174508655888</v>
       </c>
     </row>
     <row r="114">
@@ -2734,13 +2496,10 @@
         <v>0</v>
       </c>
       <c r="D114" t="n">
-        <v>0.02057852473530415</v>
+        <v>0.08023268023365138</v>
       </c>
       <c r="E114" t="n">
-        <v>0.7367741128251278</v>
-      </c>
-      <c r="F114" t="n">
-        <v>0.2426473624395681</v>
+        <v>0.9197673197663486</v>
       </c>
     </row>
     <row r="115">
@@ -2750,14 +2509,13 @@
         </is>
       </c>
       <c r="B115" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C115" t="n">
         <v>1</v>
       </c>
       <c r="D115" t="inlineStr"/>
       <c r="E115" t="inlineStr"/>
-      <c r="F115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" s="1" t="inlineStr">
@@ -2772,13 +2530,10 @@
         <v>0</v>
       </c>
       <c r="D116" t="n">
-        <v>0.0163680081329358</v>
+        <v>0.06336615976226745</v>
       </c>
       <c r="E116" t="n">
-        <v>0.6962155233462303</v>
-      </c>
-      <c r="F116" t="n">
-        <v>0.287416468520834</v>
+        <v>0.9366338402377326</v>
       </c>
     </row>
     <row r="117">
@@ -2794,13 +2549,10 @@
         <v>0</v>
       </c>
       <c r="D117" t="n">
-        <v>0.004095055011798962</v>
+        <v>0.02214239474877489</v>
       </c>
       <c r="E117" t="n">
-        <v>0.6356449222191967</v>
-      </c>
-      <c r="F117" t="n">
-        <v>0.3602600227690043</v>
+        <v>0.9778576052512251</v>
       </c>
     </row>
     <row r="118">
@@ -2810,19 +2562,16 @@
         </is>
       </c>
       <c r="B118" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C118" t="n">
         <v>0</v>
       </c>
       <c r="D118" t="n">
-        <v>0.03683985583460932</v>
+        <v>0.1869735010288469</v>
       </c>
       <c r="E118" t="n">
-        <v>0.4346460524293754</v>
-      </c>
-      <c r="F118" t="n">
-        <v>0.5285140917360153</v>
+        <v>0.8130264989711531</v>
       </c>
     </row>
     <row r="119">
@@ -2832,19 +2581,16 @@
         </is>
       </c>
       <c r="B119" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C119" t="n">
         <v>0</v>
       </c>
       <c r="D119" t="n">
-        <v>0.1128523448790581</v>
+        <v>0.4035563062621289</v>
       </c>
       <c r="E119" t="n">
-        <v>0.2471448726854077</v>
-      </c>
-      <c r="F119" t="n">
-        <v>0.6400027824355342</v>
+        <v>0.5964436937378711</v>
       </c>
     </row>
     <row r="120">
@@ -2860,13 +2606,10 @@
         <v>0</v>
       </c>
       <c r="D120" t="n">
-        <v>0.01487391903700042</v>
+        <v>0.04365860043434178</v>
       </c>
       <c r="E120" t="n">
-        <v>0.5135216159757228</v>
-      </c>
-      <c r="F120" t="n">
-        <v>0.4716044649872768</v>
+        <v>0.9563413995656582</v>
       </c>
     </row>
     <row r="121">
@@ -2883,7 +2626,6 @@
       </c>
       <c r="D121" t="inlineStr"/>
       <c r="E121" t="inlineStr"/>
-      <c r="F121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" s="1" t="inlineStr">
@@ -2898,13 +2640,10 @@
         <v>0</v>
       </c>
       <c r="D122" t="n">
-        <v>0.03780408442060543</v>
+        <v>0.08391461871784067</v>
       </c>
       <c r="E122" t="n">
-        <v>0.4847931146867933</v>
-      </c>
-      <c r="F122" t="n">
-        <v>0.4774028008926013</v>
+        <v>0.9160853812821593</v>
       </c>
     </row>
     <row r="123">
@@ -2917,11 +2656,14 @@
         <v>2</v>
       </c>
       <c r="C123" t="n">
-        <v>1</v>
-      </c>
-      <c r="D123" t="inlineStr"/>
-      <c r="E123" t="inlineStr"/>
-      <c r="F123" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.02844334758235967</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.9715566524176403</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" s="1" t="inlineStr">
@@ -2936,13 +2678,10 @@
         <v>0</v>
       </c>
       <c r="D124" t="n">
-        <v>0.005133123005743236</v>
+        <v>0.02363971262412679</v>
       </c>
       <c r="E124" t="n">
-        <v>0.6018588421409363</v>
-      </c>
-      <c r="F124" t="n">
-        <v>0.3930080348533204</v>
+        <v>0.9763602873758732</v>
       </c>
     </row>
     <row r="125">
@@ -2958,13 +2697,10 @@
         <v>0</v>
       </c>
       <c r="D125" t="n">
-        <v>0.03169922928396272</v>
+        <v>0.07815429963863252</v>
       </c>
       <c r="E125" t="n">
-        <v>0.5312950839908714</v>
-      </c>
-      <c r="F125" t="n">
-        <v>0.4370056867251658</v>
+        <v>0.9218457003613675</v>
       </c>
     </row>
     <row r="126">
@@ -2980,13 +2716,10 @@
         <v>0</v>
       </c>
       <c r="D126" t="n">
-        <v>0.04883687407677096</v>
+        <v>0.1065752686546224</v>
       </c>
       <c r="E126" t="n">
-        <v>0.4770702623419099</v>
-      </c>
-      <c r="F126" t="n">
-        <v>0.4740928635813192</v>
+        <v>0.8934247313453776</v>
       </c>
     </row>
     <row r="127">
@@ -3002,13 +2735,10 @@
         <v>0</v>
       </c>
       <c r="D127" t="n">
-        <v>0.03206416697654246</v>
+        <v>0.1064759613498109</v>
       </c>
       <c r="E127" t="n">
-        <v>0.6249397965861281</v>
-      </c>
-      <c r="F127" t="n">
-        <v>0.3429960364373294</v>
+        <v>0.8935240386501891</v>
       </c>
     </row>
     <row r="128">
@@ -3021,11 +2751,14 @@
         <v>2</v>
       </c>
       <c r="C128" t="n">
-        <v>1</v>
-      </c>
-      <c r="D128" t="inlineStr"/>
-      <c r="E128" t="inlineStr"/>
-      <c r="F128" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.0179522519147689</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.9820477480852311</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129" s="1" t="inlineStr">
@@ -3040,13 +2773,10 @@
         <v>0</v>
       </c>
       <c r="D129" t="n">
-        <v>9.767107353208476e-06</v>
+        <v>0.0001908669832950682</v>
       </c>
       <c r="E129" t="n">
-        <v>0.7474917826721202</v>
-      </c>
-      <c r="F129" t="n">
-        <v>0.2524984502205264</v>
+        <v>0.9998091330167049</v>
       </c>
     </row>
     <row r="130">
@@ -3062,13 +2792,10 @@
         <v>0</v>
       </c>
       <c r="D130" t="n">
-        <v>0.09877620206353643</v>
+        <v>0.2097152343445231</v>
       </c>
       <c r="E130" t="n">
-        <v>0.5139005807941567</v>
-      </c>
-      <c r="F130" t="n">
-        <v>0.3873232171423069</v>
+        <v>0.7902847656554769</v>
       </c>
     </row>
     <row r="131">
@@ -3084,13 +2811,10 @@
         <v>0</v>
       </c>
       <c r="D131" t="n">
-        <v>0.003684699074020826</v>
+        <v>0.01532741472088173</v>
       </c>
       <c r="E131" t="n">
-        <v>0.5433186407907059</v>
-      </c>
-      <c r="F131" t="n">
-        <v>0.4529966601352734</v>
+        <v>0.9846725852791183</v>
       </c>
     </row>
     <row r="132">
@@ -3107,7 +2831,6 @@
       </c>
       <c r="D132" t="inlineStr"/>
       <c r="E132" t="inlineStr"/>
-      <c r="F132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" s="1" t="inlineStr">
@@ -3122,13 +2845,10 @@
         <v>0</v>
       </c>
       <c r="D133" t="n">
-        <v>0.00958816741907819</v>
+        <v>0.03634038120005734</v>
       </c>
       <c r="E133" t="n">
-        <v>0.5444961258686151</v>
-      </c>
-      <c r="F133" t="n">
-        <v>0.4459157067123067</v>
+        <v>0.9636596187999427</v>
       </c>
     </row>
     <row r="134">
@@ -3138,19 +2858,16 @@
         </is>
       </c>
       <c r="B134" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C134" t="n">
         <v>0</v>
       </c>
       <c r="D134" t="n">
-        <v>0.02401468659799207</v>
+        <v>0.06143540172929263</v>
       </c>
       <c r="E134" t="n">
-        <v>0.4421555968914535</v>
-      </c>
-      <c r="F134" t="n">
-        <v>0.5338297165105544</v>
+        <v>0.9385645982707074</v>
       </c>
     </row>
     <row r="135">
@@ -3166,13 +2883,10 @@
         <v>0</v>
       </c>
       <c r="D135" t="n">
-        <v>0.007825050498714486</v>
+        <v>0.03630893457626339</v>
       </c>
       <c r="E135" t="n">
-        <v>0.6434371175334682</v>
-      </c>
-      <c r="F135" t="n">
-        <v>0.3487378319678172</v>
+        <v>0.9636910654237366</v>
       </c>
     </row>
     <row r="136">
@@ -3182,19 +2896,16 @@
         </is>
       </c>
       <c r="B136" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C136" t="n">
         <v>0</v>
       </c>
       <c r="D136" t="n">
-        <v>0.02942152001896371</v>
+        <v>0.163642665138092</v>
       </c>
       <c r="E136" t="n">
-        <v>0.4744526280555509</v>
-      </c>
-      <c r="F136" t="n">
-        <v>0.4961258519254854</v>
+        <v>0.836357334861908</v>
       </c>
     </row>
     <row r="137">
@@ -3210,13 +2921,10 @@
         <v>0</v>
       </c>
       <c r="D137" t="n">
-        <v>0.0006251374989475184</v>
+        <v>0.006489984455751219</v>
       </c>
       <c r="E137" t="n">
-        <v>0.7832883708472738</v>
-      </c>
-      <c r="F137" t="n">
-        <v>0.2160864916537787</v>
+        <v>0.9935100155442488</v>
       </c>
     </row>
     <row r="138">
@@ -3232,13 +2940,10 @@
         <v>0</v>
       </c>
       <c r="D138" t="n">
-        <v>0.509115528178437</v>
+        <v>0.7237016055645402</v>
       </c>
       <c r="E138" t="n">
-        <v>0.363961121361396</v>
-      </c>
-      <c r="F138" t="n">
-        <v>0.126923350460167</v>
+        <v>0.2762983944354598</v>
       </c>
     </row>
     <row r="139">
@@ -3248,19 +2953,16 @@
         </is>
       </c>
       <c r="B139" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C139" t="n">
         <v>0</v>
       </c>
       <c r="D139" t="n">
-        <v>0.07355975122037242</v>
+        <v>0.1159636562920494</v>
       </c>
       <c r="E139" t="n">
-        <v>0.282574000700665</v>
-      </c>
-      <c r="F139" t="n">
-        <v>0.6438662480789625</v>
+        <v>0.8840363437079506</v>
       </c>
     </row>
     <row r="140">
@@ -3270,19 +2972,16 @@
         </is>
       </c>
       <c r="B140" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C140" t="n">
         <v>0</v>
       </c>
       <c r="D140" t="n">
-        <v>0.1640917491585634</v>
+        <v>0.1864275719268247</v>
       </c>
       <c r="E140" t="n">
-        <v>0.27765992831846</v>
-      </c>
-      <c r="F140" t="n">
-        <v>0.5582483225229766</v>
+        <v>0.8135724280731753</v>
       </c>
     </row>
     <row r="141">
@@ -3298,13 +2997,10 @@
         <v>0</v>
       </c>
       <c r="D141" t="n">
-        <v>0.00178794002651481</v>
+        <v>0.009255549370284943</v>
       </c>
       <c r="E141" t="n">
-        <v>0.6396899698412746</v>
-      </c>
-      <c r="F141" t="n">
-        <v>0.3585220901322105</v>
+        <v>0.9907444506297151</v>
       </c>
     </row>
     <row r="142">
@@ -3314,19 +3010,16 @@
         </is>
       </c>
       <c r="B142" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C142" t="n">
         <v>0</v>
       </c>
       <c r="D142" t="n">
-        <v>0.06924378676850632</v>
+        <v>0.1769396407827839</v>
       </c>
       <c r="E142" t="n">
-        <v>0.402459235865563</v>
-      </c>
-      <c r="F142" t="n">
-        <v>0.5282969773659307</v>
+        <v>0.8230603592172161</v>
       </c>
     </row>
     <row r="143">
@@ -3336,19 +3029,16 @@
         </is>
       </c>
       <c r="B143" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C143" t="n">
         <v>0</v>
       </c>
       <c r="D143" t="n">
-        <v>0.01967261730959972</v>
+        <v>0.03138777486928612</v>
       </c>
       <c r="E143" t="n">
-        <v>0.4144740002755156</v>
-      </c>
-      <c r="F143" t="n">
-        <v>0.5658533824148847</v>
+        <v>0.9686122251307139</v>
       </c>
     </row>
     <row r="144">
@@ -3364,13 +3054,10 @@
         <v>0</v>
       </c>
       <c r="D144" t="n">
-        <v>0.0005602416049171976</v>
+        <v>0.00548903670855605</v>
       </c>
       <c r="E144" t="n">
-        <v>0.5726306920679233</v>
-      </c>
-      <c r="F144" t="n">
-        <v>0.4268090663271594</v>
+        <v>0.994510963291444</v>
       </c>
     </row>
     <row r="145">
@@ -3386,13 +3073,10 @@
         <v>0</v>
       </c>
       <c r="D145" t="n">
-        <v>0.001443875555768597</v>
+        <v>0.004772048395536799</v>
       </c>
       <c r="E145" t="n">
-        <v>0.6207520476799472</v>
-      </c>
-      <c r="F145" t="n">
-        <v>0.3778040767642843</v>
+        <v>0.9952279516044632</v>
       </c>
     </row>
     <row r="146">
@@ -3408,13 +3092,10 @@
         <v>0</v>
       </c>
       <c r="D146" t="n">
-        <v>0.6902705972099411</v>
+        <v>0.5433593484251042</v>
       </c>
       <c r="E146" t="n">
-        <v>0.04732322087535153</v>
-      </c>
-      <c r="F146" t="n">
-        <v>0.2624061819147074</v>
+        <v>0.4566406515748957</v>
       </c>
     </row>
     <row r="147">
@@ -3424,14 +3105,13 @@
         </is>
       </c>
       <c r="B147" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C147" t="n">
         <v>1</v>
       </c>
       <c r="D147" t="inlineStr"/>
       <c r="E147" t="inlineStr"/>
-      <c r="F147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" s="1" t="inlineStr">
@@ -3446,13 +3126,10 @@
         <v>0</v>
       </c>
       <c r="D148" t="n">
-        <v>0.002626942250964396</v>
+        <v>0.007971174580242102</v>
       </c>
       <c r="E148" t="n">
-        <v>0.5794849088860996</v>
-      </c>
-      <c r="F148" t="n">
-        <v>0.4178881488629361</v>
+        <v>0.9920288254197579</v>
       </c>
     </row>
     <row r="149">
@@ -3462,19 +3139,16 @@
         </is>
       </c>
       <c r="B149" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C149" t="n">
         <v>0</v>
       </c>
       <c r="D149" t="n">
-        <v>0.3708597040818889</v>
+        <v>0.480144535220108</v>
       </c>
       <c r="E149" t="n">
-        <v>0.1971183133696527</v>
-      </c>
-      <c r="F149" t="n">
-        <v>0.4320219825484583</v>
+        <v>0.519855464779892</v>
       </c>
     </row>
     <row r="150">
@@ -3490,13 +3164,10 @@
         <v>0</v>
       </c>
       <c r="D150" t="n">
-        <v>0.02464552215254325</v>
+        <v>0.07331503619613555</v>
       </c>
       <c r="E150" t="n">
-        <v>0.5240951259622555</v>
-      </c>
-      <c r="F150" t="n">
-        <v>0.4512593518852012</v>
+        <v>0.9266849638038644</v>
       </c>
     </row>
     <row r="151">
@@ -3512,13 +3183,10 @@
         <v>0</v>
       </c>
       <c r="D151" t="n">
-        <v>0.02197460151673028</v>
+        <v>0.05273022604647504</v>
       </c>
       <c r="E151" t="n">
-        <v>0.5400711879232767</v>
-      </c>
-      <c r="F151" t="n">
-        <v>0.4379542105599931</v>
+        <v>0.947269773953525</v>
       </c>
     </row>
     <row r="152">
@@ -3534,13 +3202,10 @@
         <v>0</v>
       </c>
       <c r="D152" t="n">
-        <v>0.6201985330379503</v>
+        <v>0.6070728132634405</v>
       </c>
       <c r="E152" t="n">
-        <v>0.1264297659182416</v>
-      </c>
-      <c r="F152" t="n">
-        <v>0.2533717010438081</v>
+        <v>0.3929271867365595</v>
       </c>
     </row>
     <row r="153">
@@ -3556,13 +3221,10 @@
         <v>0</v>
       </c>
       <c r="D153" t="n">
-        <v>0.05927752566573501</v>
+        <v>0.3075119776824822</v>
       </c>
       <c r="E153" t="n">
-        <v>0.7906092535616842</v>
-      </c>
-      <c r="F153" t="n">
-        <v>0.1501132207725807</v>
+        <v>0.6924880223175178</v>
       </c>
     </row>
     <row r="154">
@@ -3578,13 +3240,10 @@
         <v>0</v>
       </c>
       <c r="D154" t="n">
-        <v>0.008865439765162755</v>
+        <v>0.02619831716964816</v>
       </c>
       <c r="E154" t="n">
-        <v>0.6059929422467317</v>
-      </c>
-      <c r="F154" t="n">
-        <v>0.3851416179881055</v>
+        <v>0.9738016828303518</v>
       </c>
     </row>
     <row r="155">
@@ -3600,13 +3259,10 @@
         <v>0</v>
       </c>
       <c r="D155" t="n">
-        <v>0.6895003305546978</v>
+        <v>0.804019743444695</v>
       </c>
       <c r="E155" t="n">
-        <v>0.2011002120708265</v>
-      </c>
-      <c r="F155" t="n">
-        <v>0.1093994573744756</v>
+        <v>0.1959802565553051</v>
       </c>
     </row>
     <row r="156">
@@ -3622,13 +3278,10 @@
         <v>0</v>
       </c>
       <c r="D156" t="n">
-        <v>0.0455918682427106</v>
+        <v>0.2503369582298005</v>
       </c>
       <c r="E156" t="n">
-        <v>0.7467821125219257</v>
-      </c>
-      <c r="F156" t="n">
-        <v>0.2076260192353636</v>
+        <v>0.7496630417701995</v>
       </c>
     </row>
     <row r="157">
@@ -3644,13 +3297,10 @@
         <v>0</v>
       </c>
       <c r="D157" t="n">
-        <v>0.5788993729160854</v>
+        <v>0.6021154591016104</v>
       </c>
       <c r="E157" t="n">
-        <v>0.1023803033762263</v>
-      </c>
-      <c r="F157" t="n">
-        <v>0.3187203237076884</v>
+        <v>0.3978845408983896</v>
       </c>
     </row>
     <row r="158">
@@ -3660,19 +3310,16 @@
         </is>
       </c>
       <c r="B158" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C158" t="n">
         <v>0</v>
       </c>
       <c r="D158" t="n">
-        <v>0.03656027573275506</v>
+        <v>0.1084147722368612</v>
       </c>
       <c r="E158" t="n">
-        <v>0.4333479860766822</v>
-      </c>
-      <c r="F158" t="n">
-        <v>0.5300917381905628</v>
+        <v>0.8915852277631388</v>
       </c>
     </row>
     <row r="159">
@@ -3682,19 +3329,16 @@
         </is>
       </c>
       <c r="B159" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C159" t="n">
         <v>0</v>
       </c>
       <c r="D159" t="n">
-        <v>0.2237958242243156</v>
+        <v>0.3643993356741022</v>
       </c>
       <c r="E159" t="n">
-        <v>0.3130062343080082</v>
-      </c>
-      <c r="F159" t="n">
-        <v>0.4631979414676762</v>
+        <v>0.6356006643258978</v>
       </c>
     </row>
     <row r="160">
@@ -3704,19 +3348,16 @@
         </is>
       </c>
       <c r="B160" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C160" t="n">
         <v>0</v>
       </c>
       <c r="D160" t="n">
-        <v>0.1762253330389614</v>
+        <v>0.5133654942310559</v>
       </c>
       <c r="E160" t="n">
-        <v>0.6415246782233009</v>
-      </c>
-      <c r="F160" t="n">
-        <v>0.1822499887377377</v>
+        <v>0.4866345057689441</v>
       </c>
     </row>
     <row r="161">
@@ -3726,19 +3367,16 @@
         </is>
       </c>
       <c r="B161" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C161" t="n">
         <v>0</v>
       </c>
       <c r="D161" t="n">
-        <v>0.1798250666980026</v>
+        <v>0.2943344482401121</v>
       </c>
       <c r="E161" t="n">
-        <v>0.294323391126369</v>
-      </c>
-      <c r="F161" t="n">
-        <v>0.5258515421756285</v>
+        <v>0.7056655517598879</v>
       </c>
     </row>
     <row r="162">
@@ -3754,13 +3392,10 @@
         <v>0</v>
       </c>
       <c r="D162" t="n">
-        <v>0.1239159097427915</v>
+        <v>0.4683165521018722</v>
       </c>
       <c r="E162" t="n">
-        <v>0.7059853806373754</v>
-      </c>
-      <c r="F162" t="n">
-        <v>0.1700987096198331</v>
+        <v>0.5316834478981278</v>
       </c>
     </row>
     <row r="163">
@@ -3770,19 +3405,16 @@
         </is>
       </c>
       <c r="B163" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C163" t="n">
         <v>0</v>
       </c>
       <c r="D163" t="n">
-        <v>0.128947949894246</v>
+        <v>0.2824381763076395</v>
       </c>
       <c r="E163" t="n">
-        <v>0.3695396513349855</v>
-      </c>
-      <c r="F163" t="n">
-        <v>0.5015123987707685</v>
+        <v>0.7175618236923605</v>
       </c>
     </row>
     <row r="164">
@@ -3798,13 +3430,10 @@
         <v>0</v>
       </c>
       <c r="D164" t="n">
-        <v>0.4847853320798295</v>
+        <v>0.5249364398718945</v>
       </c>
       <c r="E164" t="n">
-        <v>0.1980538790093002</v>
-      </c>
-      <c r="F164" t="n">
-        <v>0.3171607889108704</v>
+        <v>0.4750635601281054</v>
       </c>
     </row>
     <row r="165">
@@ -3814,19 +3443,16 @@
         </is>
       </c>
       <c r="B165" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C165" t="n">
         <v>0</v>
       </c>
       <c r="D165" t="n">
-        <v>0.1260650450469211</v>
+        <v>0.1337972555980114</v>
       </c>
       <c r="E165" t="n">
-        <v>0.3316989560981368</v>
-      </c>
-      <c r="F165" t="n">
-        <v>0.5422359988549422</v>
+        <v>0.8662027444019886</v>
       </c>
     </row>
     <row r="166">
@@ -3842,13 +3468,10 @@
         <v>0</v>
       </c>
       <c r="D166" t="n">
-        <v>0.02503696559645176</v>
+        <v>0.0901774484525355</v>
       </c>
       <c r="E166" t="n">
-        <v>0.5897858226885438</v>
-      </c>
-      <c r="F166" t="n">
-        <v>0.3851772117150044</v>
+        <v>0.9098225515474645</v>
       </c>
     </row>
     <row r="167">
@@ -3865,7 +3488,6 @@
       </c>
       <c r="D167" t="inlineStr"/>
       <c r="E167" t="inlineStr"/>
-      <c r="F167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" s="1" t="inlineStr">
@@ -3880,13 +3502,10 @@
         <v>0</v>
       </c>
       <c r="D168" t="n">
-        <v>0.003139944909731976</v>
+        <v>0.008452415478026443</v>
       </c>
       <c r="E168" t="n">
-        <v>0.79592530327851</v>
-      </c>
-      <c r="F168" t="n">
-        <v>0.200934751811758</v>
+        <v>0.9915475845219736</v>
       </c>
     </row>
     <row r="169">
@@ -3903,7 +3522,6 @@
       </c>
       <c r="D169" t="inlineStr"/>
       <c r="E169" t="inlineStr"/>
-      <c r="F169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" s="1" t="inlineStr">
@@ -3918,13 +3536,10 @@
         <v>0</v>
       </c>
       <c r="D170" t="n">
-        <v>0.03480532150946573</v>
+        <v>0.1066434032628168</v>
       </c>
       <c r="E170" t="n">
-        <v>0.4918437340742409</v>
-      </c>
-      <c r="F170" t="n">
-        <v>0.4733509444162934</v>
+        <v>0.8933565967371832</v>
       </c>
     </row>
     <row r="171">
@@ -3940,13 +3555,10 @@
         <v>0</v>
       </c>
       <c r="D171" t="n">
-        <v>0.002018742498085715</v>
+        <v>0.007564418947960672</v>
       </c>
       <c r="E171" t="n">
-        <v>0.654273850372295</v>
-      </c>
-      <c r="F171" t="n">
-        <v>0.3437074071296192</v>
+        <v>0.9924355810520393</v>
       </c>
     </row>
     <row r="172">
@@ -3963,7 +3575,6 @@
       </c>
       <c r="D172" t="inlineStr"/>
       <c r="E172" t="inlineStr"/>
-      <c r="F172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" s="1" t="inlineStr">
@@ -3978,13 +3589,10 @@
         <v>0</v>
       </c>
       <c r="D173" t="n">
-        <v>0.0009516612540138629</v>
+        <v>0.004188371145998238</v>
       </c>
       <c r="E173" t="n">
-        <v>0.706519633621997</v>
-      </c>
-      <c r="F173" t="n">
-        <v>0.292528705123989</v>
+        <v>0.9958116288540018</v>
       </c>
     </row>
     <row r="174">
@@ -3994,19 +3602,16 @@
         </is>
       </c>
       <c r="B174" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C174" t="n">
         <v>0</v>
       </c>
       <c r="D174" t="n">
-        <v>0.1193259956066753</v>
+        <v>0.2535713239550197</v>
       </c>
       <c r="E174" t="n">
-        <v>0.3945569809761895</v>
-      </c>
-      <c r="F174" t="n">
-        <v>0.4861170234171352</v>
+        <v>0.7464286760449803</v>
       </c>
     </row>
     <row r="175">
@@ -4016,14 +3621,17 @@
         </is>
       </c>
       <c r="B175" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C175" t="n">
-        <v>1</v>
-      </c>
-      <c r="D175" t="inlineStr"/>
-      <c r="E175" t="inlineStr"/>
-      <c r="F175" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="D175" t="n">
+        <v>0.04313764309473456</v>
+      </c>
+      <c r="E175" t="n">
+        <v>0.9568623569052654</v>
+      </c>
     </row>
     <row r="176">
       <c r="A176" s="1" t="inlineStr">
@@ -4032,14 +3640,17 @@
         </is>
       </c>
       <c r="B176" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C176" t="n">
-        <v>1</v>
-      </c>
-      <c r="D176" t="inlineStr"/>
-      <c r="E176" t="inlineStr"/>
-      <c r="F176" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="D176" t="n">
+        <v>0.05472514289977204</v>
+      </c>
+      <c r="E176" t="n">
+        <v>0.945274857100228</v>
+      </c>
     </row>
     <row r="177">
       <c r="A177" s="1" t="inlineStr">
@@ -4048,14 +3659,13 @@
         </is>
       </c>
       <c r="B177" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C177" t="n">
         <v>1</v>
       </c>
       <c r="D177" t="inlineStr"/>
       <c r="E177" t="inlineStr"/>
-      <c r="F177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" s="1" t="inlineStr">
@@ -4064,14 +3674,13 @@
         </is>
       </c>
       <c r="B178" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C178" t="n">
         <v>1</v>
       </c>
       <c r="D178" t="inlineStr"/>
       <c r="E178" t="inlineStr"/>
-      <c r="F178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" s="1" t="inlineStr">
@@ -4080,19 +3689,16 @@
         </is>
       </c>
       <c r="B179" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C179" t="n">
         <v>0</v>
       </c>
       <c r="D179" t="n">
-        <v>0.279853177604698</v>
+        <v>0.4054087467355079</v>
       </c>
       <c r="E179" t="n">
-        <v>0.2916165746323326</v>
-      </c>
-      <c r="F179" t="n">
-        <v>0.4285302477629694</v>
+        <v>0.5945912532644921</v>
       </c>
     </row>
     <row r="180">
@@ -4108,13 +3714,10 @@
         <v>0</v>
       </c>
       <c r="D180" t="n">
-        <v>0.7105372425055266</v>
+        <v>0.676958188446956</v>
       </c>
       <c r="E180" t="n">
-        <v>0.05348750231082362</v>
-      </c>
-      <c r="F180" t="n">
-        <v>0.2359752551836497</v>
+        <v>0.323041811553044</v>
       </c>
     </row>
     <row r="181">
@@ -4130,13 +3733,10 @@
         <v>0</v>
       </c>
       <c r="D181" t="n">
-        <v>0.8920912981271465</v>
+        <v>0.8486385490910808</v>
       </c>
       <c r="E181" t="n">
-        <v>0.01489384997319195</v>
-      </c>
-      <c r="F181" t="n">
-        <v>0.09301485189966149</v>
+        <v>0.1513614509089191</v>
       </c>
     </row>
     <row r="182">
@@ -4152,13 +3752,10 @@
         <v>0</v>
       </c>
       <c r="D182" t="n">
-        <v>0.005871503195385705</v>
+        <v>0.0223395740571255</v>
       </c>
       <c r="E182" t="n">
-        <v>0.4980622291385985</v>
-      </c>
-      <c r="F182" t="n">
-        <v>0.4960662676660159</v>
+        <v>0.9776604259428745</v>
       </c>
     </row>
     <row r="183">
@@ -4168,19 +3765,16 @@
         </is>
       </c>
       <c r="B183" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C183" t="n">
         <v>0</v>
       </c>
       <c r="D183" t="n">
-        <v>0.009570610155345946</v>
+        <v>0.02887215851681979</v>
       </c>
       <c r="E183" t="n">
-        <v>0.4748241597499574</v>
-      </c>
-      <c r="F183" t="n">
-        <v>0.5156052300946966</v>
+        <v>0.9711278414831802</v>
       </c>
     </row>
     <row r="184">
@@ -4196,13 +3790,10 @@
         <v>0</v>
       </c>
       <c r="D184" t="n">
-        <v>0.9572419375400542</v>
+        <v>0.9433615642314135</v>
       </c>
       <c r="E184" t="n">
-        <v>0.004628005795674433</v>
-      </c>
-      <c r="F184" t="n">
-        <v>0.03813005666427149</v>
+        <v>0.05663843576858651</v>
       </c>
     </row>
     <row r="185">
@@ -4212,19 +3803,16 @@
         </is>
       </c>
       <c r="B185" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C185" t="n">
         <v>0</v>
       </c>
       <c r="D185" t="n">
-        <v>0.04522009915667066</v>
+        <v>0.08705677824292746</v>
       </c>
       <c r="E185" t="n">
-        <v>0.3610605316636669</v>
-      </c>
-      <c r="F185" t="n">
-        <v>0.5937193691796624</v>
+        <v>0.9129432217570725</v>
       </c>
     </row>
     <row r="186">
@@ -4234,19 +3822,16 @@
         </is>
       </c>
       <c r="B186" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C186" t="n">
         <v>0</v>
       </c>
       <c r="D186" t="n">
-        <v>0.003771018911563155</v>
+        <v>0.01789785359415774</v>
       </c>
       <c r="E186" t="n">
-        <v>0.4509210662125389</v>
-      </c>
-      <c r="F186" t="n">
-        <v>0.5453079148758979</v>
+        <v>0.9821021464058423</v>
       </c>
     </row>
     <row r="187">
@@ -4256,19 +3841,16 @@
         </is>
       </c>
       <c r="B187" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C187" t="n">
         <v>0</v>
       </c>
       <c r="D187" t="n">
-        <v>0.2496142270949258</v>
+        <v>0.2974764436724004</v>
       </c>
       <c r="E187" t="n">
-        <v>0.1906958198232022</v>
-      </c>
-      <c r="F187" t="n">
-        <v>0.559689953081872</v>
+        <v>0.7025235563275996</v>
       </c>
     </row>
     <row r="188">
@@ -4284,13 +3866,10 @@
         <v>0</v>
       </c>
       <c r="D188" t="n">
-        <v>0.4224018155313388</v>
+        <v>0.5136765592807158</v>
       </c>
       <c r="E188" t="n">
-        <v>0.1652960733629105</v>
-      </c>
-      <c r="F188" t="n">
-        <v>0.4123021111057508</v>
+        <v>0.4863234407192842</v>
       </c>
     </row>
     <row r="189">
@@ -4300,19 +3879,16 @@
         </is>
       </c>
       <c r="B189" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C189" t="n">
         <v>0</v>
       </c>
       <c r="D189" t="n">
-        <v>0.3260461638385658</v>
+        <v>0.3404832425117243</v>
       </c>
       <c r="E189" t="n">
-        <v>0.17835728519124</v>
-      </c>
-      <c r="F189" t="n">
-        <v>0.4955965509701942</v>
+        <v>0.6595167574882757</v>
       </c>
     </row>
     <row r="190">
@@ -4328,13 +3904,10 @@
         <v>0</v>
       </c>
       <c r="D190" t="n">
-        <v>0.00293421979415622</v>
+        <v>0.01083700699586854</v>
       </c>
       <c r="E190" t="n">
-        <v>0.649101293562858</v>
-      </c>
-      <c r="F190" t="n">
-        <v>0.3479644866429858</v>
+        <v>0.9891629930041315</v>
       </c>
     </row>
     <row r="191">
@@ -4344,19 +3917,16 @@
         </is>
       </c>
       <c r="B191" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C191" t="n">
         <v>0</v>
       </c>
       <c r="D191" t="n">
-        <v>0.02483337602375767</v>
+        <v>0.0749135400425146</v>
       </c>
       <c r="E191" t="n">
-        <v>0.4742409277942788</v>
-      </c>
-      <c r="F191" t="n">
-        <v>0.5009256961819635</v>
+        <v>0.9250864599574854</v>
       </c>
     </row>
     <row r="192">
@@ -4369,11 +3939,14 @@
         <v>2</v>
       </c>
       <c r="C192" t="n">
-        <v>1</v>
-      </c>
-      <c r="D192" t="inlineStr"/>
-      <c r="E192" t="inlineStr"/>
-      <c r="F192" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="D192" t="n">
+        <v>0.05241672202181968</v>
+      </c>
+      <c r="E192" t="n">
+        <v>0.9475832779781803</v>
+      </c>
     </row>
     <row r="193">
       <c r="A193" s="1" t="inlineStr">
@@ -4389,7 +3962,6 @@
       </c>
       <c r="D193" t="inlineStr"/>
       <c r="E193" t="inlineStr"/>
-      <c r="F193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" s="1" t="inlineStr">
@@ -4405,7 +3977,6 @@
       </c>
       <c r="D194" t="inlineStr"/>
       <c r="E194" t="inlineStr"/>
-      <c r="F194" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" s="1" t="inlineStr">
@@ -4421,7 +3992,6 @@
       </c>
       <c r="D195" t="inlineStr"/>
       <c r="E195" t="inlineStr"/>
-      <c r="F195" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" s="1" t="inlineStr">
@@ -4430,19 +4000,16 @@
         </is>
       </c>
       <c r="B196" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C196" t="n">
         <v>0</v>
       </c>
       <c r="D196" t="n">
-        <v>0.123113868758581</v>
+        <v>0.1909130433910994</v>
       </c>
       <c r="E196" t="n">
-        <v>0.3296858566761404</v>
-      </c>
-      <c r="F196" t="n">
-        <v>0.5472002745652785</v>
+        <v>0.8090869566089006</v>
       </c>
     </row>
     <row r="197">
@@ -4458,13 +4025,10 @@
         <v>0</v>
       </c>
       <c r="D197" t="n">
-        <v>0.07255065133789687</v>
+        <v>0.1297636908673482</v>
       </c>
       <c r="E197" t="n">
-        <v>0.4742483426525034</v>
-      </c>
-      <c r="F197" t="n">
-        <v>0.4532010060095998</v>
+        <v>0.8702363091326518</v>
       </c>
     </row>
     <row r="198">
@@ -4474,19 +4038,16 @@
         </is>
       </c>
       <c r="B198" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C198" t="n">
         <v>0</v>
       </c>
       <c r="D198" t="n">
-        <v>0.1534898680847904</v>
+        <v>0.1832237724185142</v>
       </c>
       <c r="E198" t="n">
-        <v>0.2407065275021459</v>
-      </c>
-      <c r="F198" t="n">
-        <v>0.6058036044130637</v>
+        <v>0.8167762275814858</v>
       </c>
     </row>
     <row r="199">
@@ -4502,13 +4063,10 @@
         <v>0</v>
       </c>
       <c r="D199" t="n">
-        <v>0.5806276195846464</v>
+        <v>0.5553062079145007</v>
       </c>
       <c r="E199" t="n">
-        <v>0.109791871275276</v>
-      </c>
-      <c r="F199" t="n">
-        <v>0.3095805091400777</v>
+        <v>0.4446937920854993</v>
       </c>
     </row>
     <row r="200">
@@ -4524,13 +4082,10 @@
         <v>0</v>
       </c>
       <c r="D200" t="n">
-        <v>0.5399254708913455</v>
+        <v>0.5218740785651687</v>
       </c>
       <c r="E200" t="n">
-        <v>0.0683120003780279</v>
-      </c>
-      <c r="F200" t="n">
-        <v>0.3917625287306267</v>
+        <v>0.4781259214348313</v>
       </c>
     </row>
     <row r="201">
@@ -4540,19 +4095,16 @@
         </is>
       </c>
       <c r="B201" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C201" t="n">
         <v>0</v>
       </c>
       <c r="D201" t="n">
-        <v>0.09180628850395912</v>
+        <v>0.1152576916551891</v>
       </c>
       <c r="E201" t="n">
-        <v>0.2656104288581034</v>
-      </c>
-      <c r="F201" t="n">
-        <v>0.6425832826379375</v>
+        <v>0.8847423083448109</v>
       </c>
     </row>
     <row r="202">
@@ -4562,19 +4114,16 @@
         </is>
       </c>
       <c r="B202" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C202" t="n">
         <v>0</v>
       </c>
       <c r="D202" t="n">
-        <v>0.1309556879091091</v>
+        <v>0.1476762641213065</v>
       </c>
       <c r="E202" t="n">
-        <v>0.2514995290904372</v>
-      </c>
-      <c r="F202" t="n">
-        <v>0.6175447830004538</v>
+        <v>0.8523237358786935</v>
       </c>
     </row>
     <row r="203">
@@ -4584,19 +4133,16 @@
         </is>
       </c>
       <c r="B203" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C203" t="n">
         <v>0</v>
       </c>
       <c r="D203" t="n">
-        <v>0.254754980198042</v>
+        <v>0.2868337100579363</v>
       </c>
       <c r="E203" t="n">
-        <v>0.2456454710494092</v>
-      </c>
-      <c r="F203" t="n">
-        <v>0.4995995487525487</v>
+        <v>0.7131662899420637</v>
       </c>
     </row>
     <row r="204">
@@ -4606,19 +4152,16 @@
         </is>
       </c>
       <c r="B204" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C204" t="n">
         <v>0</v>
       </c>
       <c r="D204" t="n">
-        <v>0.3283012810952446</v>
+        <v>0.4293657967437858</v>
       </c>
       <c r="E204" t="n">
-        <v>0.295438737005695</v>
-      </c>
-      <c r="F204" t="n">
-        <v>0.3762599818990604</v>
+        <v>0.5706342032562142</v>
       </c>
     </row>
     <row r="205">
@@ -4628,19 +4171,16 @@
         </is>
       </c>
       <c r="B205" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C205" t="n">
         <v>0</v>
       </c>
       <c r="D205" t="n">
-        <v>0.3864794264793991</v>
+        <v>0.7003163033811599</v>
       </c>
       <c r="E205" t="n">
-        <v>0.4410692092408022</v>
-      </c>
-      <c r="F205" t="n">
-        <v>0.1724513642797987</v>
+        <v>0.2996836966188401</v>
       </c>
     </row>
     <row r="206">
@@ -4657,7 +4197,6 @@
       </c>
       <c r="D206" t="inlineStr"/>
       <c r="E206" t="inlineStr"/>
-      <c r="F206" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" s="1" t="inlineStr">
@@ -4666,19 +4205,16 @@
         </is>
       </c>
       <c r="B207" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C207" t="n">
         <v>0</v>
       </c>
       <c r="D207" t="n">
-        <v>0.06207717865421838</v>
+        <v>0.1760517648645006</v>
       </c>
       <c r="E207" t="n">
-        <v>0.3215279553442579</v>
-      </c>
-      <c r="F207" t="n">
-        <v>0.6163948660015236</v>
+        <v>0.8239482351354994</v>
       </c>
     </row>
     <row r="208">
@@ -4688,19 +4224,16 @@
         </is>
       </c>
       <c r="B208" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C208" t="n">
         <v>0</v>
       </c>
       <c r="D208" t="n">
-        <v>0.05352667283457474</v>
+        <v>0.09762793020295435</v>
       </c>
       <c r="E208" t="n">
-        <v>0.3279483437958965</v>
-      </c>
-      <c r="F208" t="n">
-        <v>0.6185249833695287</v>
+        <v>0.9023720697970457</v>
       </c>
     </row>
     <row r="209">
@@ -4710,19 +4243,16 @@
         </is>
       </c>
       <c r="B209" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C209" t="n">
         <v>0</v>
       </c>
       <c r="D209" t="n">
-        <v>0.03677345296803439</v>
+        <v>0.0797659287201764</v>
       </c>
       <c r="E209" t="n">
-        <v>0.4083225644743333</v>
-      </c>
-      <c r="F209" t="n">
-        <v>0.5549039825576322</v>
+        <v>0.9202340712798236</v>
       </c>
     </row>
     <row r="210">
@@ -4732,19 +4262,16 @@
         </is>
       </c>
       <c r="B210" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C210" t="n">
         <v>0</v>
       </c>
       <c r="D210" t="n">
-        <v>0.01559487605615839</v>
+        <v>0.06243791257214948</v>
       </c>
       <c r="E210" t="n">
-        <v>0.4086212037119415</v>
-      </c>
-      <c r="F210" t="n">
-        <v>0.5757839202319002</v>
+        <v>0.9375620874278505</v>
       </c>
     </row>
     <row r="211">
@@ -4754,14 +4281,13 @@
         </is>
       </c>
       <c r="B211" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C211" t="n">
         <v>1</v>
       </c>
       <c r="D211" t="inlineStr"/>
       <c r="E211" t="inlineStr"/>
-      <c r="F211" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" s="1" t="inlineStr">
@@ -4777,7 +4303,6 @@
       </c>
       <c r="D212" t="inlineStr"/>
       <c r="E212" t="inlineStr"/>
-      <c r="F212" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" s="1" t="inlineStr">
@@ -4786,19 +4311,16 @@
         </is>
       </c>
       <c r="B213" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C213" t="n">
         <v>0</v>
       </c>
       <c r="D213" t="n">
-        <v>0.172319158820116</v>
+        <v>0.2351996293428343</v>
       </c>
       <c r="E213" t="n">
-        <v>0.2936779368337709</v>
-      </c>
-      <c r="F213" t="n">
-        <v>0.5340029043461131</v>
+        <v>0.7648003706571657</v>
       </c>
     </row>
     <row r="214">
@@ -4808,19 +4330,16 @@
         </is>
       </c>
       <c r="B214" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C214" t="n">
         <v>0</v>
       </c>
       <c r="D214" t="n">
-        <v>0.09516382340193062</v>
+        <v>0.1317202534448026</v>
       </c>
       <c r="E214" t="n">
-        <v>0.3293585924733091</v>
-      </c>
-      <c r="F214" t="n">
-        <v>0.5754775841247604</v>
+        <v>0.8682797465551974</v>
       </c>
     </row>
     <row r="215">
@@ -4836,13 +4355,10 @@
         <v>0</v>
       </c>
       <c r="D215" t="n">
-        <v>0.1316815272174085</v>
+        <v>0.211704966418335</v>
       </c>
       <c r="E215" t="n">
-        <v>0.4350689827766037</v>
-      </c>
-      <c r="F215" t="n">
-        <v>0.4332494900059877</v>
+        <v>0.788295033581665</v>
       </c>
     </row>
     <row r="216">
@@ -4852,19 +4368,16 @@
         </is>
       </c>
       <c r="B216" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C216" t="n">
         <v>0</v>
       </c>
       <c r="D216" t="n">
-        <v>0.04417047380578389</v>
+        <v>0.1025424157929689</v>
       </c>
       <c r="E216" t="n">
-        <v>0.4544321248001296</v>
-      </c>
-      <c r="F216" t="n">
-        <v>0.5013974013940865</v>
+        <v>0.8974575842070311</v>
       </c>
     </row>
     <row r="217">
@@ -4874,19 +4387,16 @@
         </is>
       </c>
       <c r="B217" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C217" t="n">
         <v>0</v>
       </c>
       <c r="D217" t="n">
-        <v>0.3097169289180479</v>
+        <v>0.3521908815567174</v>
       </c>
       <c r="E217" t="n">
-        <v>0.2835265379368562</v>
-      </c>
-      <c r="F217" t="n">
-        <v>0.4067565331450959</v>
+        <v>0.6478091184432826</v>
       </c>
     </row>
     <row r="218">
@@ -4896,14 +4406,13 @@
         </is>
       </c>
       <c r="B218" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C218" t="n">
         <v>1</v>
       </c>
       <c r="D218" t="inlineStr"/>
       <c r="E218" t="inlineStr"/>
-      <c r="F218" t="inlineStr"/>
     </row>
     <row r="219">
       <c r="A219" s="1" t="inlineStr">
@@ -4918,13 +4427,10 @@
         <v>0</v>
       </c>
       <c r="D219" t="n">
-        <v>0.05580392040463149</v>
+        <v>0.1292380596362631</v>
       </c>
       <c r="E219" t="n">
-        <v>0.5312923306076103</v>
-      </c>
-      <c r="F219" t="n">
-        <v>0.4129037489877583</v>
+        <v>0.8707619403637369</v>
       </c>
     </row>
     <row r="220">
@@ -4940,13 +4446,10 @@
         <v>0</v>
       </c>
       <c r="D220" t="n">
-        <v>0.9954723721375416</v>
+        <v>0.9921253985145718</v>
       </c>
       <c r="E220" t="n">
-        <v>0.002042051227056875</v>
-      </c>
-      <c r="F220" t="n">
-        <v>0.002485576635401477</v>
+        <v>0.007874601485428156</v>
       </c>
     </row>
     <row r="221">
@@ -4962,13 +4465,10 @@
         <v>0</v>
       </c>
       <c r="D221" t="n">
-        <v>0.00343008240876631</v>
+        <v>0.02463723131138429</v>
       </c>
       <c r="E221" t="n">
-        <v>0.7655356573029193</v>
-      </c>
-      <c r="F221" t="n">
-        <v>0.2310342602883145</v>
+        <v>0.9753627686886157</v>
       </c>
     </row>
     <row r="222">
@@ -4978,19 +4478,16 @@
         </is>
       </c>
       <c r="B222" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C222" t="n">
         <v>0</v>
       </c>
       <c r="D222" t="n">
-        <v>0.09946998478892784</v>
+        <v>0.1626443409202182</v>
       </c>
       <c r="E222" t="n">
-        <v>0.4149510132024654</v>
-      </c>
-      <c r="F222" t="n">
-        <v>0.4855790020086068</v>
+        <v>0.8373556590797818</v>
       </c>
     </row>
     <row r="223">
@@ -5006,13 +4503,10 @@
         <v>0</v>
       </c>
       <c r="D223" t="n">
-        <v>0.9819913837691001</v>
+        <v>0.9746234045007063</v>
       </c>
       <c r="E223" t="n">
-        <v>0.008782867979931204</v>
-      </c>
-      <c r="F223" t="n">
-        <v>0.0092257482509687</v>
+        <v>0.02537659549929371</v>
       </c>
     </row>
     <row r="224">
@@ -5022,19 +4516,16 @@
         </is>
       </c>
       <c r="B224" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C224" t="n">
         <v>0</v>
       </c>
       <c r="D224" t="n">
-        <v>0.4416936287134857</v>
+        <v>0.4335071160380685</v>
       </c>
       <c r="E224" t="n">
-        <v>0.1547448631958188</v>
-      </c>
-      <c r="F224" t="n">
-        <v>0.4035615080906955</v>
+        <v>0.5664928839619315</v>
       </c>
     </row>
     <row r="225">
@@ -5044,19 +4535,16 @@
         </is>
       </c>
       <c r="B225" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C225" t="n">
         <v>0</v>
       </c>
       <c r="D225" t="n">
-        <v>0.414853408047691</v>
+        <v>0.4626232203723755</v>
       </c>
       <c r="E225" t="n">
-        <v>0.1772738153453089</v>
-      </c>
-      <c r="F225" t="n">
-        <v>0.4078727766069999</v>
+        <v>0.5373767796276245</v>
       </c>
     </row>
     <row r="226">
@@ -5072,13 +4560,10 @@
         <v>0</v>
       </c>
       <c r="D226" t="n">
-        <v>0.9484666617649317</v>
+        <v>0.9474309792751684</v>
       </c>
       <c r="E226" t="n">
-        <v>0.0281205161394814</v>
-      </c>
-      <c r="F226" t="n">
-        <v>0.02341282209558683</v>
+        <v>0.05256902072483157</v>
       </c>
     </row>
     <row r="227">
@@ -5094,13 +4579,10 @@
         <v>0</v>
       </c>
       <c r="D227" t="n">
-        <v>0.01044217263402622</v>
+        <v>0.06172518644470559</v>
       </c>
       <c r="E227" t="n">
-        <v>0.7506160995853948</v>
-      </c>
-      <c r="F227" t="n">
-        <v>0.238941727780579</v>
+        <v>0.9382748135552944</v>
       </c>
     </row>
     <row r="228">
@@ -5116,13 +4598,10 @@
         <v>0</v>
       </c>
       <c r="D228" t="n">
-        <v>0.003662964625538209</v>
+        <v>0.0204377684331799</v>
       </c>
       <c r="E228" t="n">
-        <v>0.6860584903595133</v>
-      </c>
-      <c r="F228" t="n">
-        <v>0.3102785450149484</v>
+        <v>0.9795622315668201</v>
       </c>
     </row>
     <row r="229">
@@ -5132,19 +4611,16 @@
         </is>
       </c>
       <c r="B229" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C229" t="n">
         <v>0</v>
       </c>
       <c r="D229" t="n">
-        <v>0.5742012291793078</v>
+        <v>0.4376949989047541</v>
       </c>
       <c r="E229" t="n">
-        <v>0.3239448931577482</v>
-      </c>
-      <c r="F229" t="n">
-        <v>0.101853877662944</v>
+        <v>0.5623050010952459</v>
       </c>
     </row>
     <row r="230">
@@ -5160,13 +4636,10 @@
         <v>0</v>
       </c>
       <c r="D230" t="n">
-        <v>0.02058740129726125</v>
+        <v>0.07133460576202777</v>
       </c>
       <c r="E230" t="n">
-        <v>0.5219976911744317</v>
-      </c>
-      <c r="F230" t="n">
-        <v>0.457414907528307</v>
+        <v>0.9286653942379722</v>
       </c>
     </row>
     <row r="231">
@@ -5182,13 +4655,10 @@
         <v>0</v>
       </c>
       <c r="D231" t="n">
-        <v>0.01713956608524491</v>
+        <v>0.04939565932752643</v>
       </c>
       <c r="E231" t="n">
-        <v>0.5762813616300242</v>
-      </c>
-      <c r="F231" t="n">
-        <v>0.4065790722847308</v>
+        <v>0.9506043406724736</v>
       </c>
     </row>
     <row r="232">
@@ -5204,13 +4674,10 @@
         <v>0</v>
       </c>
       <c r="D232" t="n">
-        <v>0.0004803012858747151</v>
+        <v>0.003862926640586961</v>
       </c>
       <c r="E232" t="n">
-        <v>0.6578613847542459</v>
-      </c>
-      <c r="F232" t="n">
-        <v>0.3416583139598794</v>
+        <v>0.996137073359413</v>
       </c>
     </row>
     <row r="233">
@@ -5226,13 +4693,10 @@
         <v>0</v>
       </c>
       <c r="D233" t="n">
-        <v>0.09796870015785934</v>
+        <v>0.438934200368623</v>
       </c>
       <c r="E233" t="n">
-        <v>0.7027683460094356</v>
-      </c>
-      <c r="F233" t="n">
-        <v>0.199262953832705</v>
+        <v>0.561065799631377</v>
       </c>
     </row>
     <row r="234">
@@ -5248,13 +4712,10 @@
         <v>0</v>
       </c>
       <c r="D234" t="n">
-        <v>0.001728152126272874</v>
+        <v>0.008886893593156753</v>
       </c>
       <c r="E234" t="n">
-        <v>0.5412364765813809</v>
-      </c>
-      <c r="F234" t="n">
-        <v>0.4570353712923463</v>
+        <v>0.9911131064068432</v>
       </c>
     </row>
     <row r="235">
@@ -5270,13 +4731,10 @@
         <v>0</v>
       </c>
       <c r="D235" t="n">
-        <v>0.0009763702093701143</v>
+        <v>0.005132980845604984</v>
       </c>
       <c r="E235" t="n">
-        <v>0.6304542705380582</v>
-      </c>
-      <c r="F235" t="n">
-        <v>0.3685693592525715</v>
+        <v>0.994867019154395</v>
       </c>
     </row>
     <row r="236">
@@ -5292,13 +4750,10 @@
         <v>0</v>
       </c>
       <c r="D236" t="n">
-        <v>0.04035020288634447</v>
+        <v>0.07005127857096649</v>
       </c>
       <c r="E236" t="n">
-        <v>0.5024775873355821</v>
-      </c>
-      <c r="F236" t="n">
-        <v>0.4571722097780735</v>
+        <v>0.9299487214290335</v>
       </c>
     </row>
     <row r="237">
@@ -5314,19 +4769,16 @@
         <v>0</v>
       </c>
       <c r="D237" t="n">
-        <v>0.0004702247280142451</v>
+        <v>0.001958961641634671</v>
       </c>
       <c r="E237" t="n">
-        <v>0.6260409157102886</v>
-      </c>
-      <c r="F237" t="n">
-        <v>0.3734888595616971</v>
+        <v>0.9980410383583653</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="B2:F2"/>
-    <mergeCell ref="B1:F1"/>
+    <mergeCell ref="B1:E1"/>
+    <mergeCell ref="B2:E2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
